--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC98D679-8D67-45F5-BE60-2616E50C7D74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA1BECA-4622-40E7-9F5D-5DDCA746BB2C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1045,9 +1045,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1055,6 +1052,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1233,7 +1233,7 @@
     <col min="8" max="8" width="13.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.375" style="22" customWidth="1"/>
+    <col min="11" max="11" width="5.375" style="21" customWidth="1"/>
     <col min="12" max="13" width="6.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="6.625" bestFit="1" customWidth="1"/>
@@ -1262,112 +1262,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="19.5" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="18" t="s">
+      <c r="K1" s="20"/>
+      <c r="L1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="20"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="19"/>
       <c r="AA1" s="16" t="s">
         <v>280</v>
       </c>
       <c r="AB1" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="AD1" s="19" t="s">
+      <c r="AD1" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="AE1" s="19" t="s">
+      <c r="AE1" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="AF1" s="19" t="s">
+      <c r="AF1" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="AG1" s="19" t="s">
+      <c r="AG1" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="AH1" s="19" t="s">
+      <c r="AH1" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="AI1" s="19" t="s">
+      <c r="AI1" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="AJ1" s="19" t="s">
+      <c r="AJ1" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="AK1" s="19" t="s">
+      <c r="AK1" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="AL1" s="19" t="s">
+      <c r="AL1" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="AN1" s="19" t="s">
+      <c r="AN1" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="AO1" s="19" t="s">
+      <c r="AO1" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="AP1" s="19" t="s">
+      <c r="AP1" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="19" t="s">
+      <c r="AQ1" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="AR1" s="19" t="s">
+      <c r="AR1" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="AS1" s="19" t="s">
+      <c r="AS1" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="AT1" s="19" t="s">
+      <c r="AT1" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="AU1" s="19" t="s">
+      <c r="AU1" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="AV1" s="19" t="s">
+      <c r="AV1" s="18" t="s">
         <v>289</v>
       </c>
     </row>
@@ -14694,14 +14694,8 @@
       <c r="W215" s="7"/>
       <c r="X215" s="7"/>
       <c r="Y215" s="7"/>
-      <c r="AA215" s="9">
-        <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-      <c r="AB215" s="9">
-        <f t="shared" si="87"/>
-        <v>-686671</v>
-      </c>
+      <c r="AA215" s="9"/>
+      <c r="AB215" s="9"/>
     </row>
     <row r="216" spans="1:48" s="2" customFormat="1" ht="15">
       <c r="A216" s="1" t="s">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D4E9C6-84CD-44D2-8B3E-9FF4DE0BBAF7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DE07E8-D55C-4221-92AB-DC620AE59E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="72675" yWindow="225" windowWidth="34545" windowHeight="20130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Notes" sheetId="2" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="308">
   <si>
     <t>губ</t>
   </si>
@@ -855,9 +861,6 @@
     <t>Итого в Сибири</t>
   </si>
   <si>
-    <t>Акмолинская</t>
-  </si>
-  <si>
     <t>Закаспийская область</t>
   </si>
   <si>
@@ -928,13 +931,40 @@
   </si>
   <si>
     <t>Итого во всей Империи</t>
+  </si>
+  <si>
+    <t>Акмолинская область</t>
+  </si>
+  <si>
+    <t>за вычетом нескольких незначительных расхождений.</t>
+  </si>
+  <si>
+    <t>Число жителей часто расходится, и значительно.</t>
+  </si>
+  <si>
+    <t>Числа рождений и смертей по отдельным территориям в целом сходятся по контрольным суммам,</t>
+  </si>
+  <si>
+    <t>Ряды итого расходятся по сумме рождений и смертей для земских губерний.</t>
+  </si>
+  <si>
+    <t>Причина расхождения неясна.</t>
+  </si>
+  <si>
+    <t>Аналогичное расхождение для Сибири и Средней Азии связано с невключением некоторых областей в сумму.</t>
+  </si>
+  <si>
+    <t>Для поступательного расчёта в конечном итого важны только ряды рождений и смертей по отдельным территориям.</t>
+  </si>
+  <si>
+    <t>Исправленные опечатки помечены синим фоном.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -953,8 +983,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -984,6 +1019,18 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -997,7 +1044,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1047,7 +1094,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1075,10 +1121,17 @@
     <xf numFmtId="3" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,48 +1297,99 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C511C11-9BF8-4959-A781-52FB8B4BE706}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="30" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="30" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="30" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="30" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="30" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="30" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="30" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="30" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="30" t="s">
+        <v>306</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV269"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:AW269"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="29.25" style="21" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="21" customWidth="1"/>
-    <col min="3" max="4" width="8" style="21" customWidth="1"/>
-    <col min="5" max="5" width="10" style="21" customWidth="1"/>
-    <col min="6" max="6" width="8.375" style="21" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="21" customWidth="1"/>
-    <col min="8" max="8" width="13.625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="13.25" style="21" customWidth="1"/>
-    <col min="10" max="10" width="13.125" style="21" customWidth="1"/>
-    <col min="11" max="11" width="5.375" style="21" customWidth="1"/>
-    <col min="12" max="13" width="6.625" style="21" customWidth="1"/>
-    <col min="14" max="14" width="8" style="21" customWidth="1"/>
-    <col min="15" max="15" width="6.625" style="21" customWidth="1"/>
-    <col min="16" max="16" width="8" style="21" customWidth="1"/>
-    <col min="17" max="21" width="6.625" style="21" customWidth="1"/>
-    <col min="22" max="22" width="8" style="21" customWidth="1"/>
-    <col min="23" max="25" width="6.625" style="21" customWidth="1"/>
-    <col min="27" max="27" width="13.25" style="21" customWidth="1"/>
-    <col min="28" max="28" width="12.25" style="21" customWidth="1"/>
-    <col min="30" max="30" width="9.875" style="21" customWidth="1"/>
-    <col min="31" max="31" width="8.25" style="21" customWidth="1"/>
-    <col min="32" max="32" width="8.125" style="21" customWidth="1"/>
-    <col min="33" max="33" width="13.25" style="21" customWidth="1"/>
-    <col min="34" max="34" width="11.5" style="21" customWidth="1"/>
-    <col min="35" max="35" width="11.375" style="21" customWidth="1"/>
-    <col min="36" max="36" width="16.75" style="21" customWidth="1"/>
-    <col min="37" max="37" width="16.375" style="21" customWidth="1"/>
-    <col min="38" max="38" width="16.25" style="21" customWidth="1"/>
-    <col min="40" max="40" width="11.625" style="21" customWidth="1"/>
-    <col min="43" max="43" width="15.125" style="21" customWidth="1"/>
-    <col min="44" max="44" width="15.375" style="21" customWidth="1"/>
-    <col min="45" max="45" width="13.375" style="21" customWidth="1"/>
-    <col min="46" max="46" width="18.75" style="21" customWidth="1"/>
-    <col min="47" max="47" width="21.375" style="21" customWidth="1"/>
-    <col min="48" max="48" width="17.5" style="21" customWidth="1"/>
+    <col min="1" max="1" width="30.734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.62890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.62890625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1015625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.47265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.3671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5234375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.15625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.05078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.3671875" customWidth="1"/>
+    <col min="12" max="25" width="7.15625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.68359375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.26171875" customWidth="1"/>
+    <col min="29" max="29" width="12.26171875" customWidth="1"/>
+    <col min="31" max="31" width="10.62890625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="8.62890625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.05078125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.3125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.20703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.05078125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.68359375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.3125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.62890625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.47265625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.89453125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.05078125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.89453125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.734375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17.3671875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.26171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="21" customFormat="1" ht="28.7" customHeight="1">
+    <row r="1" spans="1:49" ht="28.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1317,85 +1421,86 @@
         <v>9</v>
       </c>
       <c r="K1" s="19"/>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="16" t="s">
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="17" t="s">
+      <c r="AC1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="AD1" s="20" t="s">
+      <c r="AE1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="AE1" s="20" t="s">
+      <c r="AF1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="AF1" s="20" t="s">
+      <c r="AG1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="AG1" s="20" t="s">
+      <c r="AH1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="AH1" s="20" t="s">
+      <c r="AI1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="AI1" s="20" t="s">
+      <c r="AJ1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="20" t="s">
+      <c r="AK1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="20" t="s">
+      <c r="AL1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="20" t="s">
+      <c r="AM1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="20" t="s">
+      <c r="AO1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="AO1" s="20" t="s">
+      <c r="AP1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="AP1" s="20" t="s">
+      <c r="AQ1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="AQ1" s="20" t="s">
+      <c r="AR1" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="AR1" s="20" t="s">
+      <c r="AS1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="AS1" s="20" t="s">
+      <c r="AT1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="AT1" s="20" t="s">
+      <c r="AU1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="AU1" s="20" t="s">
+      <c r="AV1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="AV1" s="20" t="s">
+      <c r="AW1" s="20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:48" s="8" customFormat="1" ht="15">
+    <row r="2" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
@@ -1457,16 +1562,16 @@
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
-      <c r="AA2" s="9">
-        <f t="shared" ref="AA2:AA37" si="0">SUM(L2:Y2)</f>
+      <c r="AB2" s="9">
+        <f>SUM(L2:Z2)</f>
         <v>354411</v>
       </c>
-      <c r="AB2" s="9">
-        <f>AA2-B2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC2" s="9">
+        <f>AB2-B2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -1510,16 +1615,16 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
-      <c r="AA3" s="5">
-        <f t="shared" si="0"/>
+      <c r="AB3" s="9">
+        <f>SUM(L3:Z3)</f>
         <v>13729</v>
       </c>
-      <c r="AB3" s="5">
-        <f>C2-AA3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC3" s="5">
+        <f>C2-AB3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
@@ -1563,16 +1668,16 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
-      <c r="AA4" s="5">
-        <f t="shared" si="0"/>
+      <c r="AB4" s="9">
+        <f>SUM(L4:Z4)</f>
         <v>10318</v>
       </c>
-      <c r="AB4" s="5">
-        <f>AA4-D2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC4" s="5">
+        <f>AB4-D2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6" t="s">
         <v>34</v>
       </c>
@@ -1632,16 +1737,16 @@
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
-      <c r="AA5" s="9">
-        <f t="shared" si="0"/>
+      <c r="AB5" s="9">
+        <f t="shared" ref="AB5:AB37" si="0">SUM(L5:Z5)</f>
         <v>878991</v>
       </c>
-      <c r="AB5" s="9">
-        <f>AA5-B5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC5" s="9">
+        <f>AB5-B5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -1683,16 +1788,16 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
-      <c r="AA6" s="5">
+      <c r="AB6" s="9">
         <f t="shared" si="0"/>
         <v>29427</v>
       </c>
-      <c r="AB6" s="5">
-        <f>C5-AA6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC6" s="5">
+        <f>C5-AB6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>37</v>
       </c>
@@ -1734,16 +1839,16 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
-      <c r="AA7" s="5">
+      <c r="AB7" s="9">
         <f t="shared" si="0"/>
         <v>21582</v>
       </c>
-      <c r="AB7" s="5">
-        <f>AA7-D5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC7" s="5">
+        <f>AB7-D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
         <v>38</v>
       </c>
@@ -1803,16 +1908,16 @@
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
-      <c r="AA8" s="9">
+      <c r="AB8" s="9">
         <f t="shared" si="0"/>
         <v>1361820</v>
       </c>
-      <c r="AB8" s="9">
-        <f>AA8-B8</f>
+      <c r="AC8" s="9">
+        <f>AB8-B8</f>
         <v>-30</v>
       </c>
     </row>
-    <row r="9" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="9" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
@@ -1854,16 +1959,16 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
-      <c r="AA9" s="5">
+      <c r="AB9" s="9">
         <f t="shared" si="0"/>
         <v>58709</v>
       </c>
-      <c r="AB9" s="5">
-        <f>C8-AA9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC9" s="5">
+        <f>C8-AB9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
@@ -1905,16 +2010,16 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
-      <c r="AA10" s="5">
+      <c r="AB10" s="9">
         <f t="shared" si="0"/>
         <v>32542</v>
       </c>
-      <c r="AB10" s="5">
-        <f>AA10-D8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC10" s="5">
+        <f>AB10-D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6" t="s">
         <v>41</v>
       </c>
@@ -1982,16 +2087,16 @@
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
-      <c r="AA11" s="9">
+      <c r="AB11" s="9">
         <f t="shared" si="0"/>
         <v>1364473</v>
       </c>
-      <c r="AB11" s="9">
-        <f>AA11-B11</f>
+      <c r="AC11" s="9">
+        <f>AB11-B11</f>
         <v>-5000</v>
       </c>
     </row>
-    <row r="12" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="12" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
@@ -2041,16 +2146,16 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-      <c r="AA12" s="5">
+      <c r="AB12" s="9">
         <f t="shared" si="0"/>
         <v>58044</v>
       </c>
-      <c r="AB12" s="5">
-        <f>C11-AA12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC12" s="5">
+        <f>C11-AB12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>43</v>
       </c>
@@ -2100,16 +2205,16 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
-      <c r="AA13" s="5">
+      <c r="AB13" s="9">
         <f t="shared" si="0"/>
         <v>34465</v>
       </c>
-      <c r="AB13" s="5">
-        <f>AA13-D11</f>
+      <c r="AC13" s="5">
+        <f>AB13-D11</f>
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:48" s="8" customFormat="1" ht="15">
+    <row r="14" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
         <v>44</v>
       </c>
@@ -2179,16 +2284,16 @@
       </c>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
-      <c r="AA14" s="9">
+      <c r="AB14" s="9">
         <f t="shared" si="0"/>
         <v>2395608</v>
       </c>
-      <c r="AB14" s="9">
-        <f>AA14-B14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC14" s="9">
+        <f>AB14-B14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -2240,16 +2345,16 @@
       </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
-      <c r="AA15" s="5">
+      <c r="AB15" s="9">
         <f t="shared" si="0"/>
         <v>121124</v>
       </c>
-      <c r="AB15" s="5">
-        <f>C14-AA15</f>
+      <c r="AC15" s="5">
+        <f>C14-AB15</f>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="16" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -2301,16 +2406,16 @@
       </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-      <c r="AA16" s="5">
+      <c r="AB16" s="9">
         <f t="shared" si="0"/>
         <v>76050</v>
       </c>
-      <c r="AB16" s="5">
-        <f>AA16-D14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC16" s="5">
+        <f>AB16-D14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6" t="s">
         <v>47</v>
       </c>
@@ -2374,16 +2479,16 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
-      <c r="AA17" s="9">
+      <c r="AB17" s="9">
         <f t="shared" si="0"/>
         <v>1483518</v>
       </c>
-      <c r="AB17" s="9">
-        <f>AA17-B17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC17" s="9">
+        <f>AB17-B17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -2429,16 +2534,16 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
-      <c r="AA18" s="5">
+      <c r="AB18" s="9">
         <f t="shared" si="0"/>
         <v>60982</v>
       </c>
-      <c r="AB18" s="5">
-        <f>C17-AA18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC18" s="5">
+        <f>C17-AB18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,16 +2589,16 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-      <c r="AA19" s="5">
+      <c r="AB19" s="9">
         <f t="shared" si="0"/>
         <v>42063</v>
       </c>
-      <c r="AB19" s="5">
-        <f>AA19-D17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC19" s="5">
+        <f>AB19-D17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
         <v>50</v>
       </c>
@@ -2563,16 +2668,16 @@
       </c>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
-      <c r="AA20" s="9">
+      <c r="AB20" s="9">
         <f t="shared" si="0"/>
         <v>3139937</v>
       </c>
-      <c r="AB20" s="9">
-        <f>AA20-B20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC20" s="9">
+        <f>AB20-B20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
@@ -2624,16 +2729,16 @@
       </c>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
-      <c r="AA21" s="5">
+      <c r="AB21" s="9">
         <f t="shared" si="0"/>
         <v>157126</v>
       </c>
-      <c r="AB21" s="5">
-        <f>C20-AA21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC21" s="5">
+        <f>C20-AB21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -2685,16 +2790,16 @@
       </c>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
-      <c r="AA22" s="5">
+      <c r="AB22" s="9">
         <f t="shared" si="0"/>
         <v>105987</v>
       </c>
-      <c r="AB22" s="5">
-        <f>AA22-D20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC22" s="5">
+        <f>AB22-D20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6" t="s">
         <v>53</v>
       </c>
@@ -2754,16 +2859,16 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
-      <c r="AA23" s="9">
+      <c r="AB23" s="9">
         <f t="shared" si="0"/>
         <v>1587582</v>
       </c>
-      <c r="AB23" s="9">
-        <f>AA23-B23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC23" s="9">
+        <f>AB23-B23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
@@ -2805,16 +2910,16 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
-      <c r="AA24" s="5">
+      <c r="AB24" s="9">
         <f t="shared" si="0"/>
         <v>55872</v>
       </c>
-      <c r="AB24" s="5">
-        <f>C23-AA24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC24" s="5">
+        <f>C23-AB24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -2856,16 +2961,16 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
-      <c r="AA25" s="5">
+      <c r="AB25" s="9">
         <f t="shared" si="0"/>
         <v>35912</v>
       </c>
-      <c r="AB25" s="5">
-        <f>AA25-D23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC25" s="5">
+        <f>AB25-D23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="6" t="s">
         <v>56</v>
       </c>
@@ -2929,16 +3034,16 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
-      <c r="AA26" s="9">
+      <c r="AB26" s="9">
         <f t="shared" si="0"/>
         <v>1794560</v>
       </c>
-      <c r="AB26" s="9">
-        <f>AA26-B26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC26" s="9">
+        <f>AB26-B26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>57</v>
       </c>
@@ -2984,16 +3089,16 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
-      <c r="AA27" s="5">
+      <c r="AB27" s="9">
         <f t="shared" si="0"/>
         <v>84804</v>
       </c>
-      <c r="AB27" s="5">
-        <f>C26-AA27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC27" s="5">
+        <f>C26-AB27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>58</v>
       </c>
@@ -3039,16 +3144,16 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
-      <c r="AA28" s="5">
+      <c r="AB28" s="9">
         <f t="shared" si="0"/>
         <v>49170</v>
       </c>
-      <c r="AB28" s="5">
-        <f>AA28-D26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC28" s="5">
+        <f>AB28-D26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6" t="s">
         <v>59</v>
       </c>
@@ -3116,16 +3221,16 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
-      <c r="AA29" s="9">
+      <c r="AB29" s="9">
         <f t="shared" si="0"/>
         <v>1425258</v>
       </c>
-      <c r="AB29" s="9">
-        <f>AA29-B29</f>
+      <c r="AC29" s="9">
+        <f>AB29-B29</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="30" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="30" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>60</v>
       </c>
@@ -3175,16 +3280,16 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
-      <c r="AA30" s="5">
+      <c r="AB30" s="9">
         <f t="shared" si="0"/>
         <v>69583</v>
       </c>
-      <c r="AB30" s="5">
-        <f>C29-AA30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC30" s="5">
+        <f>C29-AB30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -3234,16 +3339,16 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
-      <c r="AA31" s="5">
+      <c r="AB31" s="9">
         <f t="shared" si="0"/>
         <v>40393</v>
       </c>
-      <c r="AB31" s="5">
-        <f>AA31-D29</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC31" s="5">
+        <f>AB31-D29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="6" t="s">
         <v>62</v>
       </c>
@@ -3299,16 +3404,16 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
-      <c r="AA32" s="9">
+      <c r="AB32" s="9">
         <f t="shared" si="0"/>
         <v>1377944</v>
       </c>
-      <c r="AB32" s="9">
-        <f>AA32-B32</f>
+      <c r="AC32" s="9">
+        <f>AB32-B32</f>
         <v>-3000</v>
       </c>
     </row>
-    <row r="33" spans="1:46" s="2" customFormat="1" ht="15">
+    <row r="33" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>63</v>
       </c>
@@ -3346,16 +3451,16 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
-      <c r="AA33" s="5">
+      <c r="AB33" s="9">
         <f t="shared" si="0"/>
         <v>81294</v>
       </c>
-      <c r="AB33" s="5">
-        <f>C32-AA33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC33" s="5">
+        <f>C32-AB33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>64</v>
       </c>
@@ -3393,16 +3498,16 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
-      <c r="AA34" s="5">
+      <c r="AB34" s="9">
         <f t="shared" si="0"/>
         <v>60350</v>
       </c>
-      <c r="AB34" s="5">
-        <f>AA34-D32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:46" s="8" customFormat="1" ht="15">
+      <c r="AC34" s="5">
+        <f>AB34-D32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6" t="s">
         <v>65</v>
       </c>
@@ -3472,16 +3577,16 @@
       </c>
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
-      <c r="AA35" s="9">
+      <c r="AB35" s="9">
         <f t="shared" si="0"/>
         <v>2617253</v>
       </c>
-      <c r="AB35" s="9">
-        <f>AA35-B35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC35" s="9">
+        <f>AB35-B35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>66</v>
       </c>
@@ -3533,16 +3638,16 @@
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
-      <c r="AA36" s="5">
+      <c r="AB36" s="9">
         <f t="shared" si="0"/>
         <v>120433</v>
       </c>
-      <c r="AB36" s="5">
-        <f>C35-AA36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC36" s="5">
+        <f>C35-AB36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>67</v>
       </c>
@@ -3594,16 +3699,16 @@
       </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
-      <c r="AA37" s="5">
+      <c r="AB37" s="9">
         <f t="shared" si="0"/>
         <v>79121</v>
       </c>
-      <c r="AB37" s="5">
-        <f>AA37-D35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:46" s="13" customFormat="1" ht="15">
+      <c r="AC37" s="5">
+        <f>AB37-D35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:47" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="11" t="s">
         <v>68</v>
       </c>
@@ -3649,51 +3754,47 @@
       <c r="W38" s="12"/>
       <c r="X38" s="12"/>
       <c r="Y38" s="12"/>
-      <c r="AA38" s="14"/>
       <c r="AB38" s="14"/>
-      <c r="AD38" s="14">
-        <f t="shared" ref="AD38:AL38" si="1">SUM(B2:B37)</f>
+      <c r="AC38" s="14"/>
+      <c r="AE38" s="14">
+        <f t="shared" ref="AE38:AM38" si="1">SUM(B2:B37)</f>
         <v>19779385</v>
       </c>
-      <c r="AE38" s="14">
+      <c r="AF38" s="14">
         <f t="shared" si="1"/>
         <v>911131</v>
       </c>
-      <c r="AF38" s="14">
+      <c r="AG38" s="14">
         <f t="shared" si="1"/>
         <v>587950</v>
       </c>
-      <c r="AG38" s="14">
+      <c r="AH38" s="14">
         <f t="shared" si="1"/>
         <v>2154653</v>
       </c>
-      <c r="AH38" s="14">
+      <c r="AI38" s="14">
         <f t="shared" si="1"/>
         <v>71108</v>
       </c>
-      <c r="AI38" s="14">
+      <c r="AJ38" s="14">
         <f t="shared" si="1"/>
         <v>52699</v>
       </c>
-      <c r="AJ38" s="14">
+      <c r="AK38" s="14">
         <f t="shared" si="1"/>
         <v>18899646</v>
       </c>
-      <c r="AK38" s="14">
+      <c r="AL38" s="14">
         <f t="shared" si="1"/>
         <v>889248</v>
       </c>
-      <c r="AL38" s="14">
+      <c r="AM38" s="14">
         <f t="shared" si="1"/>
         <v>553178</v>
       </c>
-      <c r="AN38" s="14">
-        <f t="shared" ref="AN38:AT38" si="2">AD38-B38</f>
+      <c r="AO38" s="14">
+        <f t="shared" ref="AO38:AU38" si="2">AE38-B38</f>
         <v>5000</v>
-      </c>
-      <c r="AO38" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="AP38" s="14">
         <f t="shared" si="2"/>
@@ -3701,22 +3802,26 @@
       </c>
       <c r="AQ38" s="14">
         <f t="shared" si="2"/>
-        <v>28715</v>
+        <v>0</v>
       </c>
       <c r="AR38" s="14">
         <f t="shared" si="2"/>
-        <v>947</v>
+        <v>28715</v>
       </c>
       <c r="AS38" s="14">
         <f t="shared" si="2"/>
-        <v>922</v>
+        <v>947</v>
       </c>
       <c r="AT38" s="14">
         <f t="shared" si="2"/>
+        <v>922</v>
+      </c>
+      <c r="AU38" s="14">
+        <f t="shared" si="2"/>
         <v>-20966</v>
       </c>
     </row>
-    <row r="39" spans="1:46" s="8" customFormat="1" ht="15">
+    <row r="39" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="6" t="s">
         <v>69</v>
       </c>
@@ -3762,10 +3867,10 @@
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
-      <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
-    </row>
-    <row r="40" spans="1:46" s="8" customFormat="1" ht="15">
+      <c r="AC39" s="9"/>
+    </row>
+    <row r="40" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="6" t="s">
         <v>70</v>
       </c>
@@ -3835,16 +3940,16 @@
       </c>
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
-      <c r="AA40" s="9">
-        <f t="shared" ref="AA40:AA69" si="3">SUM(L40:Y40)</f>
+      <c r="AB40" s="9">
+        <f t="shared" ref="AB40:AB42" si="3">SUM(L40:Z40)</f>
         <v>1043412</v>
       </c>
-      <c r="AB40" s="9">
-        <f>AA40-B40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC40" s="9">
+        <f>AB40-B40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
         <v>71</v>
       </c>
@@ -3896,16 +4001,16 @@
       </c>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
-      <c r="AA41" s="5">
+      <c r="AB41" s="9">
         <f t="shared" si="3"/>
         <v>41044</v>
       </c>
-      <c r="AB41" s="5">
-        <f>C40-AA41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC41" s="5">
+        <f>C40-AB41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
         <v>72</v>
       </c>
@@ -3957,16 +4062,16 @@
       </c>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
-      <c r="AA42" s="5">
+      <c r="AB42" s="9">
         <f t="shared" si="3"/>
         <v>26410</v>
       </c>
-      <c r="AB42" s="5">
-        <f>AA42-D40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:46" s="8" customFormat="1" ht="15">
+      <c r="AC42" s="5">
+        <f>AB42-D40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="6" t="s">
         <v>73</v>
       </c>
@@ -4028,16 +4133,16 @@
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
-      <c r="AA43" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB43" s="9">
+        <f t="shared" ref="AB43:AB69" si="4">SUM(L43:Z43)</f>
         <v>881798</v>
       </c>
-      <c r="AB43" s="9">
-        <f>AA43-B43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC43" s="9">
+        <f t="shared" ref="AC43" si="5">AB43-B43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
         <v>74</v>
       </c>
@@ -4081,16 +4186,16 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
-      <c r="AA44" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB44" s="9">
+        <f t="shared" si="4"/>
         <v>35951</v>
       </c>
-      <c r="AB44" s="5">
-        <f>C43-AA44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC44" s="5">
+        <f t="shared" ref="AC44" si="6">C43-AB44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
         <v>75</v>
       </c>
@@ -4134,16 +4239,16 @@
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
-      <c r="AA45" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB45" s="9">
+        <f t="shared" si="4"/>
         <v>20553</v>
       </c>
-      <c r="AB45" s="5">
-        <f>AA45-D43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:46" s="8" customFormat="1" ht="15">
+      <c r="AC45" s="5">
+        <f t="shared" ref="AC45" si="7">AB45-D43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="6" t="s">
         <v>76</v>
       </c>
@@ -4203,16 +4308,16 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
-      <c r="AA46" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB46" s="9">
+        <f t="shared" si="4"/>
         <v>737663</v>
       </c>
-      <c r="AB46" s="9">
-        <f>AA46-B46</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC46" s="9">
+        <f t="shared" ref="AC46" si="8">AB46-B46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
         <v>77</v>
       </c>
@@ -4254,16 +4359,16 @@
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
-      <c r="AA47" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB47" s="9">
+        <f t="shared" si="4"/>
         <v>27847</v>
       </c>
-      <c r="AB47" s="5">
-        <f>C46-AA47</f>
+      <c r="AC47" s="5">
+        <f t="shared" ref="AC47" si="9">C46-AB47</f>
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:46" s="2" customFormat="1" ht="15">
+    <row r="48" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
         <v>78</v>
       </c>
@@ -4305,16 +4410,16 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
-      <c r="AA48" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB48" s="9">
+        <f t="shared" si="4"/>
         <v>17978</v>
       </c>
-      <c r="AB48" s="5">
-        <f>AA48-D46</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC48" s="5">
+        <f t="shared" ref="AC48" si="10">AB48-D46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="6" t="s">
         <v>79</v>
       </c>
@@ -4376,16 +4481,16 @@
       <c r="W49" s="7"/>
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
-      <c r="AA49" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB49" s="9">
+        <f t="shared" si="4"/>
         <v>643795</v>
       </c>
-      <c r="AB49" s="9">
-        <f>AA49-B49</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC49" s="9">
+        <f t="shared" ref="AC49" si="11">AB49-B49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
         <v>80</v>
       </c>
@@ -4429,16 +4534,16 @@
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
-      <c r="AA50" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB50" s="9">
+        <f t="shared" si="4"/>
         <v>25903</v>
       </c>
-      <c r="AB50" s="5">
-        <f>C49-AA50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC50" s="5">
+        <f t="shared" ref="AC50" si="12">C49-AB50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
         <v>81</v>
       </c>
@@ -4482,16 +4587,16 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
-      <c r="AA51" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB51" s="9">
+        <f t="shared" si="4"/>
         <v>18319</v>
       </c>
-      <c r="AB51" s="5">
-        <f>AA51-D49</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC51" s="5">
+        <f t="shared" ref="AC51" si="13">AB51-D49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="6" t="s">
         <v>82</v>
       </c>
@@ -4557,16 +4662,16 @@
       <c r="W52" s="7"/>
       <c r="X52" s="7"/>
       <c r="Y52" s="7"/>
-      <c r="AA52" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB52" s="9">
+        <f t="shared" si="4"/>
         <v>1059959</v>
       </c>
-      <c r="AB52" s="9">
-        <f>AA52-B52</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC52" s="9">
+        <f t="shared" ref="AC52" si="14">AB52-B52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>83</v>
       </c>
@@ -4614,16 +4719,16 @@
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
-      <c r="AA53" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB53" s="9">
+        <f t="shared" si="4"/>
         <v>43814</v>
       </c>
-      <c r="AB53" s="5">
-        <f>C52-AA53</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC53" s="5">
+        <f t="shared" ref="AC53" si="15">C52-AB53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>84</v>
       </c>
@@ -4671,16 +4776,16 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
-      <c r="AA54" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB54" s="9">
+        <f t="shared" si="4"/>
         <v>26245</v>
       </c>
-      <c r="AB54" s="5">
-        <f>AA54-D52</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC54" s="5">
+        <f t="shared" ref="AC54" si="16">AB54-D52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="6" t="s">
         <v>85</v>
       </c>
@@ -4742,16 +4847,16 @@
       <c r="W55" s="7"/>
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
-      <c r="AA55" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB55" s="9">
+        <f t="shared" si="4"/>
         <v>1200197</v>
       </c>
-      <c r="AB55" s="9">
-        <f>AA55-B55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC55" s="9">
+        <f t="shared" ref="AC55" si="17">AB55-B55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>86</v>
       </c>
@@ -4795,16 +4900,16 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-      <c r="AA56" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB56" s="9">
+        <f t="shared" si="4"/>
         <v>47337</v>
       </c>
-      <c r="AB56" s="5">
-        <f>C55-AA56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC56" s="5">
+        <f t="shared" ref="AC56" si="18">C55-AB56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>87</v>
       </c>
@@ -4848,16 +4953,16 @@
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
-      <c r="AA57" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB57" s="9">
+        <f t="shared" si="4"/>
         <v>27567</v>
       </c>
-      <c r="AB57" s="5">
-        <f>AA57-D55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC57" s="5">
+        <f t="shared" ref="AC57" si="19">AB57-D55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="6" t="s">
         <v>88</v>
       </c>
@@ -4919,16 +5024,16 @@
       <c r="W58" s="7"/>
       <c r="X58" s="7"/>
       <c r="Y58" s="7"/>
-      <c r="AA58" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB58" s="9">
+        <f t="shared" si="4"/>
         <v>660457</v>
       </c>
-      <c r="AB58" s="9">
-        <f>AA58-B58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC58" s="9">
+        <f t="shared" ref="AC58" si="20">AB58-B58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>89</v>
       </c>
@@ -4972,16 +5077,16 @@
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
-      <c r="AA59" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB59" s="9">
+        <f t="shared" si="4"/>
         <v>26392</v>
       </c>
-      <c r="AB59" s="5">
-        <f>C58-AA59</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC59" s="5">
+        <f t="shared" ref="AC59" si="21">C58-AB59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>90</v>
       </c>
@@ -5025,16 +5130,16 @@
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
-      <c r="AA60" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB60" s="9">
+        <f t="shared" si="4"/>
         <v>17902</v>
       </c>
-      <c r="AB60" s="5">
-        <f>AA60-D58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC60" s="5">
+        <f t="shared" ref="AC60" si="22">AB60-D58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="6" t="s">
         <v>91</v>
       </c>
@@ -5094,16 +5199,16 @@
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
-      <c r="AA61" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB61" s="9">
+        <f t="shared" si="4"/>
         <v>769229</v>
       </c>
-      <c r="AB61" s="9">
-        <f>AA61-B61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC61" s="9">
+        <f t="shared" ref="AC61" si="23">AB61-B61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>92</v>
       </c>
@@ -5145,16 +5250,16 @@
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
-      <c r="AA62" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB62" s="9">
+        <f t="shared" si="4"/>
         <v>29099</v>
       </c>
-      <c r="AB62" s="5">
-        <f>C61-AA62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC62" s="5">
+        <f t="shared" ref="AC62" si="24">C61-AB62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>93</v>
       </c>
@@ -5196,21 +5301,21 @@
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
-      <c r="AA63" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB63" s="9">
+        <f t="shared" si="4"/>
         <v>18240</v>
       </c>
-      <c r="AB63" s="5">
-        <f>AA63-D61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC63" s="5">
+        <f t="shared" ref="AC63" si="25">AB63-D61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B64" s="7">
-        <v>693904</v>
+        <v>695904</v>
       </c>
       <c r="C64" s="7">
         <v>20045</v>
@@ -5265,16 +5370,16 @@
       <c r="W64" s="7"/>
       <c r="X64" s="7"/>
       <c r="Y64" s="7"/>
-      <c r="AA64" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB64" s="9">
+        <f t="shared" si="4"/>
         <v>695904</v>
       </c>
-      <c r="AB64" s="9">
-        <f>AA64-B64</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC64" s="9">
+        <f t="shared" ref="AC64" si="26">AB64-B64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>95</v>
       </c>
@@ -5316,16 +5421,16 @@
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
-      <c r="AA65" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB65" s="9">
+        <f t="shared" si="4"/>
         <v>20045</v>
       </c>
-      <c r="AB65" s="5">
-        <f>C64-AA65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC65" s="5">
+        <f t="shared" ref="AC65" si="27">C64-AB65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>96</v>
       </c>
@@ -5367,16 +5472,16 @@
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
-      <c r="AA66" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB66" s="9">
+        <f t="shared" si="4"/>
         <v>13906</v>
       </c>
-      <c r="AB66" s="5">
-        <f>AA66-D64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:46" s="8" customFormat="1" ht="15">
+      <c r="AC66" s="5">
+        <f t="shared" ref="AC66" si="28">AB66-D64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="6" t="s">
         <v>97</v>
       </c>
@@ -5440,16 +5545,16 @@
       <c r="W67" s="7"/>
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
-      <c r="AA67" s="9">
-        <f t="shared" si="3"/>
+      <c r="AB67" s="9">
+        <f t="shared" si="4"/>
         <v>752152</v>
       </c>
-      <c r="AB67" s="9">
-        <f>AA67-B67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC67" s="9">
+        <f t="shared" ref="AC67" si="29">AB67-B67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>98</v>
       </c>
@@ -5495,16 +5600,16 @@
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
-      <c r="AA68" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB68" s="9">
+        <f t="shared" si="4"/>
         <v>30906</v>
       </c>
-      <c r="AB68" s="5">
-        <f>C67-AA68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC68" s="5">
+        <f t="shared" ref="AC68" si="30">C67-AB68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>99</v>
       </c>
@@ -5550,16 +5655,16 @@
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
-      <c r="AA69" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB69" s="9">
+        <f t="shared" si="4"/>
         <v>16039</v>
       </c>
-      <c r="AB69" s="5">
-        <f>AA69-D67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:46" s="13" customFormat="1" ht="15">
+      <c r="AC69" s="5">
+        <f t="shared" ref="AC69" si="31">AB69-D67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:47" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="11" t="s">
         <v>100</v>
       </c>
@@ -5605,74 +5710,74 @@
       <c r="W70" s="12"/>
       <c r="X70" s="12"/>
       <c r="Y70" s="12"/>
-      <c r="AA70" s="14"/>
       <c r="AB70" s="14"/>
-      <c r="AD70" s="14">
-        <f t="shared" ref="AD70:AL70" si="4">SUM(B39:B68)</f>
-        <v>8898418</v>
-      </c>
+      <c r="AC70" s="14"/>
       <c r="AE70" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AE70:AM70" si="32">SUM(B39:B68)</f>
+        <v>8900418</v>
+      </c>
+      <c r="AF70" s="14">
+        <f t="shared" si="32"/>
         <v>349117</v>
       </c>
-      <c r="AF70" s="14">
-        <f t="shared" si="4"/>
+      <c r="AG70" s="14">
+        <f t="shared" si="32"/>
         <v>216461</v>
       </c>
-      <c r="AG70" s="14">
-        <f t="shared" si="4"/>
+      <c r="AH70" s="14">
+        <f t="shared" si="32"/>
         <v>780012</v>
       </c>
-      <c r="AH70" s="14">
-        <f t="shared" si="4"/>
+      <c r="AI70" s="14">
+        <f t="shared" si="32"/>
         <v>27612</v>
       </c>
-      <c r="AI70" s="14">
-        <f t="shared" si="4"/>
+      <c r="AJ70" s="14">
+        <f t="shared" si="32"/>
         <v>18285</v>
       </c>
-      <c r="AJ70" s="14">
-        <f t="shared" si="4"/>
+      <c r="AK70" s="14">
+        <f t="shared" si="32"/>
         <v>8556734</v>
       </c>
-      <c r="AK70" s="14">
-        <f t="shared" si="4"/>
+      <c r="AL70" s="14">
+        <f t="shared" si="32"/>
         <v>334134</v>
       </c>
-      <c r="AL70" s="14">
-        <f t="shared" si="4"/>
+      <c r="AM70" s="14">
+        <f t="shared" si="32"/>
         <v>204022</v>
       </c>
-      <c r="AN70" s="14">
-        <f t="shared" ref="AN70:AT70" si="5">AD70-B70</f>
-        <v>-8000</v>
-      </c>
       <c r="AO70" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AO70:AU70" si="33">AE70-B70</f>
+        <v>-6000</v>
+      </c>
+      <c r="AP70" s="14">
+        <f t="shared" si="33"/>
         <v>2</v>
       </c>
-      <c r="AP70" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AQ70" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AR70" s="14">
+        <f t="shared" si="33"/>
         <v>-345403</v>
       </c>
-      <c r="AR70" s="14">
-        <f t="shared" si="5"/>
+      <c r="AS70" s="14">
+        <f t="shared" si="33"/>
         <v>-16778</v>
       </c>
-      <c r="AS70" s="14">
-        <f t="shared" si="5"/>
+      <c r="AT70" s="14">
+        <f t="shared" si="33"/>
         <v>-10544</v>
       </c>
-      <c r="AT70" s="14">
-        <f t="shared" si="5"/>
+      <c r="AU70" s="14">
+        <f t="shared" si="33"/>
         <v>40895</v>
       </c>
     </row>
-    <row r="71" spans="1:46" s="8" customFormat="1" ht="15">
+    <row r="71" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="6" t="s">
         <v>101</v>
       </c>
@@ -5720,7 +5825,7 @@
         <v>72190</v>
       </c>
       <c r="Q71" s="7">
-        <v>51740</v>
+        <v>51710</v>
       </c>
       <c r="R71" s="7">
         <v>81500</v>
@@ -5738,16 +5843,16 @@
       <c r="W71" s="7"/>
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
-      <c r="AA71" s="9">
-        <f t="shared" ref="AA71:AA79" si="6">SUM(L71:Y71)</f>
-        <v>712730</v>
-      </c>
       <c r="AB71" s="9">
-        <f>AA71-B71</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="1:46" s="2" customFormat="1" ht="15">
+        <f t="shared" ref="AB71:AB79" si="34">SUM(L71:Z71)</f>
+        <v>712700</v>
+      </c>
+      <c r="AC71" s="9">
+        <f t="shared" ref="AC71" si="35">AB71-B71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>102</v>
       </c>
@@ -5795,16 +5900,16 @@
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
-      <c r="AA72" s="5">
-        <f t="shared" si="6"/>
+      <c r="AB72" s="9">
+        <f t="shared" si="34"/>
         <v>19825</v>
       </c>
-      <c r="AB72" s="5">
-        <f>C71-AA72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC72" s="5">
+        <f t="shared" ref="AC72" si="36">C71-AB72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>103</v>
       </c>
@@ -5852,16 +5957,16 @@
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
-      <c r="AA73" s="5">
-        <f t="shared" si="6"/>
+      <c r="AB73" s="9">
+        <f t="shared" si="34"/>
         <v>12125</v>
       </c>
-      <c r="AB73" s="5">
-        <f>AA73-D71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:46" s="8" customFormat="1" ht="15">
+      <c r="AC73" s="5">
+        <f t="shared" ref="AC73" si="37">AB73-D71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="6" t="s">
         <v>104</v>
       </c>
@@ -5925,16 +6030,16 @@
       <c r="W74" s="7"/>
       <c r="X74" s="7"/>
       <c r="Y74" s="7"/>
-      <c r="AA74" s="9">
-        <f t="shared" si="6"/>
+      <c r="AB74" s="9">
+        <f t="shared" si="34"/>
         <v>1260653</v>
       </c>
-      <c r="AB74" s="9">
-        <f>AA74-B74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC74" s="9">
+        <f t="shared" ref="AC74" si="38">AB74-B74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>105</v>
       </c>
@@ -5980,16 +6085,16 @@
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
-      <c r="AA75" s="5">
-        <f t="shared" si="6"/>
+      <c r="AB75" s="9">
+        <f t="shared" si="34"/>
         <v>36361</v>
       </c>
-      <c r="AB75" s="5">
-        <f>C74-AA75</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC75" s="5">
+        <f t="shared" ref="AC75" si="39">C74-AB75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
         <v>106</v>
       </c>
@@ -6035,16 +6140,16 @@
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
-      <c r="AA76" s="5">
-        <f t="shared" si="6"/>
+      <c r="AB76" s="9">
+        <f t="shared" si="34"/>
         <v>25016</v>
       </c>
-      <c r="AB76" s="5">
-        <f>AA76-D74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:46" s="8" customFormat="1" ht="15">
+      <c r="AC76" s="5">
+        <f t="shared" ref="AC76" si="40">AB76-D74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="6" t="s">
         <v>107</v>
       </c>
@@ -6098,16 +6203,16 @@
       <c r="W77" s="7"/>
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
-      <c r="AA77" s="9">
-        <f t="shared" si="6"/>
+      <c r="AB77" s="9">
+        <f t="shared" si="34"/>
         <v>404709</v>
       </c>
-      <c r="AB77" s="9">
-        <f>AA77-B77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC77" s="9">
+        <f t="shared" ref="AC77" si="41">AB77-B77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>108</v>
       </c>
@@ -6143,16 +6248,16 @@
       <c r="W78" s="3"/>
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
-      <c r="AA78" s="5">
-        <f t="shared" si="6"/>
+      <c r="AB78" s="9">
+        <f t="shared" si="34"/>
         <v>11872</v>
       </c>
-      <c r="AB78" s="5">
-        <f>C77-AA78</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:46" s="2" customFormat="1" ht="15">
+      <c r="AC78" s="5">
+        <f t="shared" ref="AC78" si="42">C77-AB78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>109</v>
       </c>
@@ -6188,16 +6293,16 @@
       <c r="W79" s="3"/>
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
-      <c r="AA79" s="5">
-        <f t="shared" si="6"/>
+      <c r="AB79" s="9">
+        <f t="shared" si="34"/>
         <v>7255</v>
       </c>
-      <c r="AB79" s="5">
-        <f>AA79-D77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:46" s="13" customFormat="1" ht="15">
+      <c r="AC79" s="5">
+        <f t="shared" ref="AC79" si="43">AB79-D77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:47" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="11" t="s">
         <v>110</v>
       </c>
@@ -6243,74 +6348,74 @@
       <c r="W80" s="12"/>
       <c r="X80" s="12"/>
       <c r="Y80" s="12"/>
-      <c r="AA80" s="14"/>
       <c r="AB80" s="14"/>
-      <c r="AD80" s="14">
-        <f t="shared" ref="AD80:AL80" si="7">SUM(B71:B79)</f>
+      <c r="AC80" s="14"/>
+      <c r="AE80" s="14">
+        <f t="shared" ref="AE80:AM80" si="44">SUM(B71:B79)</f>
         <v>2378062</v>
       </c>
-      <c r="AE80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AF80" s="14">
+        <f t="shared" si="44"/>
         <v>68058</v>
       </c>
-      <c r="AF80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AG80" s="14">
+        <f t="shared" si="44"/>
         <v>44396</v>
       </c>
-      <c r="AG80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AH80" s="14">
+        <f t="shared" si="44"/>
         <v>421251</v>
       </c>
-      <c r="AH80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AI80" s="14">
+        <f t="shared" si="44"/>
         <v>13690</v>
       </c>
-      <c r="AI80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AJ80" s="14">
+        <f t="shared" si="44"/>
         <v>10609</v>
       </c>
-      <c r="AJ80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AK80" s="14">
+        <f t="shared" si="44"/>
         <v>2325958</v>
       </c>
-      <c r="AK80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AL80" s="14">
+        <f t="shared" si="44"/>
         <v>67607</v>
       </c>
-      <c r="AL80" s="14">
-        <f t="shared" si="7"/>
+      <c r="AM80" s="14">
+        <f t="shared" si="44"/>
         <v>47534</v>
       </c>
-      <c r="AN80" s="14">
-        <f t="shared" ref="AN80:AT80" si="8">AD80-B80</f>
-        <v>0</v>
-      </c>
       <c r="AO80" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="AO80:AU80" si="45">AE80-B80</f>
         <v>0</v>
       </c>
       <c r="AP80" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AQ80" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AR80" s="14">
+        <f t="shared" si="45"/>
         <v>600</v>
       </c>
-      <c r="AR80" s="14">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="AS80" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AT80" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AU80" s="14">
+        <f t="shared" si="45"/>
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:28" s="8" customFormat="1" ht="15">
+    <row r="81" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="6" t="s">
         <v>111</v>
       </c>
@@ -6372,16 +6477,16 @@
       <c r="W81" s="7"/>
       <c r="X81" s="7"/>
       <c r="Y81" s="7"/>
-      <c r="AA81" s="9">
-        <f t="shared" ref="AA81:AA112" si="9">SUM(L81:Y81)</f>
+      <c r="AB81" s="9">
+        <f>SUM(L81:Z81)</f>
         <v>1579766</v>
       </c>
-      <c r="AB81" s="9">
-        <f>AA81-B81</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC81" s="9">
+        <f>AB81-B81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>112</v>
       </c>
@@ -6417,7 +6522,7 @@
         <v>11144</v>
       </c>
       <c r="S82" s="3">
-        <v>8024</v>
+        <v>8021</v>
       </c>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
@@ -6425,16 +6530,16 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-      <c r="AA82" s="5">
-        <f t="shared" si="9"/>
-        <v>74647</v>
-      </c>
-      <c r="AB82" s="5">
-        <f>C81-AA82</f>
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB82" s="9">
+        <f>SUM(L82:Z82)</f>
+        <v>74644</v>
+      </c>
+      <c r="AC82" s="5">
+        <f>C81-AB82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>113</v>
       </c>
@@ -6478,16 +6583,16 @@
       <c r="W83" s="3"/>
       <c r="X83" s="3"/>
       <c r="Y83" s="3"/>
-      <c r="AA83" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB83" s="9">
+        <f>SUM(L83:Z83)</f>
         <v>50841</v>
       </c>
-      <c r="AB83" s="5">
-        <f>AA83-D81</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC83" s="5">
+        <f>AB83-D81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="6" t="s">
         <v>114</v>
       </c>
@@ -6559,16 +6664,16 @@
         <v>106843</v>
       </c>
       <c r="Y84" s="7"/>
-      <c r="AA84" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB84" s="9">
+        <f t="shared" ref="AB84" si="46">SUM(L84:Y84)</f>
         <v>1511926</v>
       </c>
-      <c r="AB84" s="9">
-        <f>AA84-B84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC84" s="9">
+        <f>AB84-B84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>115</v>
       </c>
@@ -6586,7 +6691,7 @@
         <v>7765</v>
       </c>
       <c r="M85" s="3">
-        <v>4014</v>
+        <v>4011</v>
       </c>
       <c r="N85" s="3">
         <v>4684</v>
@@ -6598,7 +6703,7 @@
         <v>6098</v>
       </c>
       <c r="Q85" s="3">
-        <v>9580</v>
+        <v>7580</v>
       </c>
       <c r="R85" s="3">
         <v>6933</v>
@@ -6622,16 +6727,16 @@
         <v>5517</v>
       </c>
       <c r="Y85" s="3"/>
-      <c r="AA85" s="5">
-        <f t="shared" si="9"/>
-        <v>80777</v>
-      </c>
       <c r="AB85" s="5">
-        <f>C84-AA85</f>
-        <v>-2003</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" ref="AB85:AB111" si="47">SUM(L85:Y85)</f>
+        <v>78774</v>
+      </c>
+      <c r="AC85" s="5">
+        <f>C84-AB85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>116</v>
       </c>
@@ -6685,16 +6790,16 @@
         <v>4677</v>
       </c>
       <c r="Y86" s="3"/>
-      <c r="AA86" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB86" s="5">
+        <f t="shared" si="47"/>
         <v>65493</v>
       </c>
-      <c r="AB86" s="5">
-        <f>AA86-D84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC86" s="5">
+        <f>AB86-D84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="6" t="s">
         <v>117</v>
       </c>
@@ -6760,16 +6865,16 @@
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
-      <c r="AA87" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB87" s="9">
+        <f t="shared" si="47"/>
         <v>1282886</v>
       </c>
-      <c r="AB87" s="9">
-        <f>AA87-B87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC87" s="9">
+        <f>AB87-B87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>118</v>
       </c>
@@ -6817,16 +6922,16 @@
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
-      <c r="AA88" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB88" s="5">
+        <f t="shared" si="47"/>
         <v>56538</v>
       </c>
-      <c r="AB88" s="5">
-        <f>C87-AA88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC88" s="5">
+        <f>C87-AB88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>119</v>
       </c>
@@ -6874,16 +6979,16 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
       <c r="Y89" s="3"/>
-      <c r="AA89" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB89" s="5">
+        <f t="shared" si="47"/>
         <v>43009</v>
       </c>
-      <c r="AB89" s="5">
-        <f>AA89-D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC89" s="5">
+        <f>AB89-D87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="6" t="s">
         <v>120</v>
       </c>
@@ -6953,16 +7058,16 @@
       </c>
       <c r="X90" s="7"/>
       <c r="Y90" s="7"/>
-      <c r="AA90" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB90" s="9">
+        <f t="shared" si="47"/>
         <v>2689790</v>
       </c>
-      <c r="AB90" s="9">
-        <f>AA90-B90</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC90" s="9">
+        <f>AB90-B90</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>121</v>
       </c>
@@ -7014,16 +7119,16 @@
       </c>
       <c r="X91" s="3"/>
       <c r="Y91" s="3"/>
-      <c r="AA91" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB91" s="5">
+        <f t="shared" si="47"/>
         <v>134898</v>
       </c>
-      <c r="AB91" s="5">
-        <f>C90-AA91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC91" s="5">
+        <f>C90-AB91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>122</v>
       </c>
@@ -7075,16 +7180,16 @@
       </c>
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
-      <c r="AA92" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB92" s="5">
+        <f t="shared" si="47"/>
         <v>107953</v>
       </c>
-      <c r="AB92" s="5">
-        <f>AA92-D90</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC92" s="5">
+        <f>AB92-D90</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="6" t="s">
         <v>123</v>
       </c>
@@ -7135,7 +7240,7 @@
         <v>217497</v>
       </c>
       <c r="R93" s="7">
-        <v>224102</v>
+        <v>221102</v>
       </c>
       <c r="S93" s="7">
         <v>368611</v>
@@ -7152,16 +7257,16 @@
       <c r="W93" s="7"/>
       <c r="X93" s="7"/>
       <c r="Y93" s="7"/>
-      <c r="AA93" s="9">
-        <f t="shared" si="9"/>
-        <v>3008795</v>
-      </c>
       <c r="AB93" s="9">
-        <f>AA93-B93</f>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" si="47"/>
+        <v>3005795</v>
+      </c>
+      <c r="AC93" s="9">
+        <f>AB93-B93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>124</v>
       </c>
@@ -7211,16 +7316,16 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
-      <c r="AA94" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB94" s="5">
+        <f t="shared" si="47"/>
         <v>158150</v>
       </c>
-      <c r="AB94" s="5">
-        <f>C93-AA94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC94" s="5">
+        <f>C93-AB94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>125</v>
       </c>
@@ -7270,16 +7375,16 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-      <c r="AA95" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB95" s="5">
+        <f t="shared" si="47"/>
         <v>140937</v>
       </c>
-      <c r="AB95" s="5">
-        <f>AA95-D93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC95" s="5">
+        <f>AB95-D93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="6" t="s">
         <v>126</v>
       </c>
@@ -7341,16 +7446,16 @@
       <c r="W96" s="7"/>
       <c r="X96" s="7"/>
       <c r="Y96" s="7"/>
-      <c r="AA96" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB96" s="9">
+        <f t="shared" si="47"/>
         <v>1653543</v>
       </c>
-      <c r="AB96" s="9">
-        <f>AA96-B96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC96" s="9">
+        <f>AB96-B96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>127</v>
       </c>
@@ -7380,13 +7485,13 @@
         <v>11720</v>
       </c>
       <c r="Q97" s="3">
-        <v>12418</v>
+        <v>12118</v>
       </c>
       <c r="R97" s="3">
         <v>11719</v>
       </c>
       <c r="S97" s="3">
-        <v>9729</v>
+        <v>7729</v>
       </c>
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
@@ -7394,16 +7499,16 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
       <c r="Y97" s="3"/>
-      <c r="AA97" s="5">
-        <f t="shared" si="9"/>
-        <v>93273</v>
-      </c>
       <c r="AB97" s="5">
-        <f>C96-AA97</f>
-        <v>-2301</v>
-      </c>
-    </row>
-    <row r="98" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" si="47"/>
+        <v>90973</v>
+      </c>
+      <c r="AC97" s="5">
+        <f>C96-AB97</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>128</v>
       </c>
@@ -7447,16 +7552,16 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
-      <c r="AA98" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB98" s="5">
+        <f t="shared" si="47"/>
         <v>64854</v>
       </c>
-      <c r="AB98" s="5">
-        <f>AA98-D96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC98" s="5">
+        <f>AB98-D96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="6" t="s">
         <v>129</v>
       </c>
@@ -7526,16 +7631,16 @@
       </c>
       <c r="X99" s="7"/>
       <c r="Y99" s="7"/>
-      <c r="AA99" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB99" s="9">
+        <f t="shared" si="47"/>
         <v>2195414</v>
       </c>
-      <c r="AB99" s="9">
-        <f>AA99-B99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC99" s="9">
+        <f>AB99-B99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>130</v>
       </c>
@@ -7587,16 +7692,16 @@
       </c>
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
-      <c r="AA100" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB100" s="5">
+        <f t="shared" si="47"/>
         <v>102519</v>
       </c>
-      <c r="AB100" s="5">
-        <f>C99-AA100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC100" s="5">
+        <f>C99-AB100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>131</v>
       </c>
@@ -7648,16 +7753,16 @@
       </c>
       <c r="X101" s="3"/>
       <c r="Y101" s="3"/>
-      <c r="AA101" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB101" s="5">
+        <f t="shared" si="47"/>
         <v>76454</v>
       </c>
-      <c r="AB101" s="5">
-        <f>AA101-D99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC101" s="5">
+        <f>AB101-D99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="6" t="s">
         <v>132</v>
       </c>
@@ -7725,16 +7830,16 @@
       <c r="W102" s="7"/>
       <c r="X102" s="7"/>
       <c r="Y102" s="7"/>
-      <c r="AA102" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB102" s="9">
+        <f t="shared" si="47"/>
         <v>1244018</v>
       </c>
-      <c r="AB102" s="9">
-        <f>AA102-B102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC102" s="9">
+        <f>AB102-B102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>133</v>
       </c>
@@ -7784,16 +7889,16 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
       <c r="Y103" s="3"/>
-      <c r="AA103" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB103" s="5">
+        <f t="shared" si="47"/>
         <v>61106</v>
       </c>
-      <c r="AB103" s="5">
-        <f>C102-AA103</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC103" s="5">
+        <f>C102-AB103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>134</v>
       </c>
@@ -7843,16 +7948,16 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
-      <c r="AA104" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB104" s="5">
+        <f t="shared" si="47"/>
         <v>50620</v>
       </c>
-      <c r="AB104" s="5">
-        <f>AA104-D102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC104" s="5">
+        <f>AB104-D102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="6" t="s">
         <v>135</v>
       </c>
@@ -7922,16 +8027,16 @@
       </c>
       <c r="X105" s="7"/>
       <c r="Y105" s="7"/>
-      <c r="AA105" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB105" s="9">
+        <f t="shared" si="47"/>
         <v>1394572</v>
       </c>
-      <c r="AB105" s="9">
-        <f>AA105-B105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC105" s="9">
+        <f>AB105-B105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>136</v>
       </c>
@@ -7983,16 +8088,16 @@
       </c>
       <c r="X106" s="3"/>
       <c r="Y106" s="3"/>
-      <c r="AA106" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB106" s="5">
+        <f t="shared" si="47"/>
         <v>66118</v>
       </c>
-      <c r="AB106" s="5">
-        <f>C105-AA106</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC106" s="5">
+        <f>C105-AB106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>137</v>
       </c>
@@ -8044,16 +8149,16 @@
       </c>
       <c r="X107" s="3"/>
       <c r="Y107" s="3"/>
-      <c r="AA107" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB107" s="5">
+        <f t="shared" si="47"/>
         <v>53333</v>
       </c>
-      <c r="AB107" s="5">
-        <f>AA107-D105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC107" s="5">
+        <f>AB107-D105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="6" t="s">
         <v>138</v>
       </c>
@@ -8127,19 +8232,20 @@
       <c r="Y108" s="7">
         <v>139143</v>
       </c>
-      <c r="Z108" s="22">
+      <c r="Z108" s="32">
         <v>154214</v>
       </c>
-      <c r="AA108" s="9">
-        <f t="shared" si="9"/>
-        <v>2406817</v>
-      </c>
+      <c r="AA108" s="32"/>
       <c r="AB108" s="9">
-        <f>AA108-B108</f>
-        <v>-154214</v>
-      </c>
-    </row>
-    <row r="109" spans="1:28" s="2" customFormat="1" ht="15">
+        <f>SUM(L108:Z108)</f>
+        <v>2561031</v>
+      </c>
+      <c r="AC108" s="9">
+        <f>AB108-B108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>139</v>
       </c>
@@ -8195,19 +8301,20 @@
       <c r="Y109" s="3">
         <v>5740</v>
       </c>
-      <c r="Z109" s="22">
+      <c r="Z109" s="21">
         <v>7403</v>
       </c>
-      <c r="AA109" s="5">
-        <f t="shared" si="9"/>
-        <v>106281</v>
-      </c>
-      <c r="AB109" s="5">
-        <f>C108-AA109</f>
-        <v>7403</v>
-      </c>
-    </row>
-    <row r="110" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AA109" s="21"/>
+      <c r="AB109" s="9">
+        <f>SUM(L109:Z109)</f>
+        <v>113684</v>
+      </c>
+      <c r="AC109" s="5">
+        <f>C108-AB109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>140</v>
       </c>
@@ -8263,19 +8370,20 @@
       <c r="Y110" s="3">
         <v>4521</v>
       </c>
-      <c r="Z110" s="22">
+      <c r="Z110" s="21">
         <v>6569</v>
       </c>
-      <c r="AA110" s="5">
-        <f t="shared" si="9"/>
-        <v>82676</v>
-      </c>
-      <c r="AB110" s="5">
-        <f>AA110-D108</f>
-        <v>-6569</v>
-      </c>
-    </row>
-    <row r="111" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AA110" s="21"/>
+      <c r="AB110" s="9">
+        <f>SUM(L110:Z110)</f>
+        <v>89245</v>
+      </c>
+      <c r="AC110" s="5">
+        <f>AB110-D108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="6" t="s">
         <v>141</v>
       </c>
@@ -8286,7 +8394,7 @@
         <v>69504</v>
       </c>
       <c r="D111" s="7">
-        <v>63336</v>
+        <v>63386</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>36</v>
@@ -8347,16 +8455,16 @@
         <v>136785</v>
       </c>
       <c r="Y111" s="7"/>
-      <c r="AA111" s="9">
-        <f t="shared" si="9"/>
+      <c r="AB111" s="9">
+        <f t="shared" si="47"/>
         <v>1507674</v>
       </c>
-      <c r="AB111" s="9">
-        <f>AA111-B111</f>
+      <c r="AC111" s="9">
+        <f>AB111-B111</f>
         <v>-6118</v>
       </c>
     </row>
-    <row r="112" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="112" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>142</v>
       </c>
@@ -8410,16 +8518,16 @@
         <v>5028</v>
       </c>
       <c r="Y112" s="3"/>
-      <c r="AA112" s="5">
-        <f t="shared" si="9"/>
+      <c r="AB112" s="9">
+        <f>SUM(L112:Z112)</f>
         <v>69504</v>
       </c>
-      <c r="AB112" s="5">
-        <f>C111-AA112</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC112" s="5">
+        <f>C111-AB112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>143</v>
       </c>
@@ -8473,16 +8581,16 @@
         <v>4589</v>
       </c>
       <c r="Y113" s="3"/>
-      <c r="AA113" s="5">
-        <f t="shared" ref="AA113:AA143" si="10">SUM(L113:Y113)</f>
+      <c r="AB113" s="9">
+        <f>SUM(L113:Z113)</f>
         <v>63186</v>
       </c>
-      <c r="AB113" s="5">
-        <f>AA113-D111</f>
-        <v>-150</v>
-      </c>
-    </row>
-    <row r="114" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC113" s="5">
+        <f>AB113-D111</f>
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="114" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="6" t="s">
         <v>144</v>
       </c>
@@ -8550,16 +8658,16 @@
       <c r="W114" s="7"/>
       <c r="X114" s="7"/>
       <c r="Y114" s="7"/>
-      <c r="AA114" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB114" s="9">
+        <f t="shared" ref="AB114" si="48">SUM(L114:Y114)</f>
         <v>1551450</v>
       </c>
-      <c r="AB114" s="9">
-        <f>AA114-B114</f>
+      <c r="AC114" s="9">
+        <f>AB114-B114</f>
         <v>-8</v>
       </c>
     </row>
-    <row r="115" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="115" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>145</v>
       </c>
@@ -8609,16 +8717,16 @@
       <c r="W115" s="3"/>
       <c r="X115" s="3"/>
       <c r="Y115" s="3"/>
-      <c r="AA115" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB115" s="5">
+        <f t="shared" ref="AB115:AB143" si="49">SUM(L115:Y115)</f>
         <v>82265</v>
       </c>
-      <c r="AB115" s="5">
-        <f>C114-AA115</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC115" s="5">
+        <f>C114-AB115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>146</v>
       </c>
@@ -8668,21 +8776,21 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
       <c r="Y116" s="3"/>
-      <c r="AA116" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB116" s="5">
+        <f t="shared" si="49"/>
         <v>69179</v>
       </c>
-      <c r="AB116" s="5">
-        <f>AA116-D114</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC116" s="5">
+        <f>AB116-D114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="6" t="s">
         <v>147</v>
       </c>
       <c r="B117" s="7">
-        <v>1290507</v>
+        <v>1299507</v>
       </c>
       <c r="C117" s="7">
         <v>55572</v>
@@ -8745,16 +8853,16 @@
       <c r="W117" s="7"/>
       <c r="X117" s="7"/>
       <c r="Y117" s="7"/>
-      <c r="AA117" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB117" s="9">
+        <f t="shared" si="49"/>
         <v>1276110</v>
       </c>
-      <c r="AB117" s="9">
-        <f>AA117-B117</f>
-        <v>-14397</v>
-      </c>
-    </row>
-    <row r="118" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC117" s="9">
+        <f>AB117-B117</f>
+        <v>-23397</v>
+      </c>
+    </row>
+    <row r="118" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1" t="s">
         <v>148</v>
       </c>
@@ -8804,16 +8912,16 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
       <c r="Y118" s="3"/>
-      <c r="AA118" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB118" s="5">
+        <f t="shared" si="49"/>
         <v>55572</v>
       </c>
-      <c r="AB118" s="5">
-        <f>C117-AA118</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC118" s="5">
+        <f>C117-AB118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1" t="s">
         <v>149</v>
       </c>
@@ -8863,16 +8971,16 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
       <c r="Y119" s="3"/>
-      <c r="AA119" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB119" s="5">
+        <f t="shared" si="49"/>
         <v>41175</v>
       </c>
-      <c r="AB119" s="5">
-        <f>AA119-D117</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC119" s="5">
+        <f>AB119-D117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="6" t="s">
         <v>150</v>
       </c>
@@ -8932,16 +9040,16 @@
       <c r="W120" s="7"/>
       <c r="X120" s="7"/>
       <c r="Y120" s="7"/>
-      <c r="AA120" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB120" s="9">
+        <f t="shared" si="49"/>
         <v>362131</v>
       </c>
-      <c r="AB120" s="9">
-        <f>AA120-B120</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC120" s="9">
+        <f>AB120-B120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="1" t="s">
         <v>151</v>
       </c>
@@ -8983,16 +9091,16 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
       <c r="Y121" s="3"/>
-      <c r="AA121" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB121" s="5">
+        <f t="shared" si="49"/>
         <v>17367</v>
       </c>
-      <c r="AB121" s="5">
-        <f>C120-AA121</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC121" s="5">
+        <f>C120-AB121</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1" t="s">
         <v>152</v>
       </c>
@@ -9034,16 +9142,16 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
       <c r="Y122" s="3"/>
-      <c r="AA122" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB122" s="5">
+        <f t="shared" si="49"/>
         <v>12258</v>
       </c>
-      <c r="AB122" s="5">
-        <f>AA122-D120</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC122" s="5">
+        <f>AB122-D120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="6" t="s">
         <v>153</v>
       </c>
@@ -9113,16 +9221,16 @@
       </c>
       <c r="X123" s="7"/>
       <c r="Y123" s="7"/>
-      <c r="AA123" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB123" s="9">
+        <f t="shared" si="49"/>
         <v>2107442</v>
       </c>
-      <c r="AB123" s="9">
-        <f>AA123-B123</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC123" s="9">
+        <f>AB123-B123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1" t="s">
         <v>154</v>
       </c>
@@ -9174,16 +9282,16 @@
       </c>
       <c r="X124" s="3"/>
       <c r="Y124" s="3"/>
-      <c r="AA124" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB124" s="5">
+        <f t="shared" si="49"/>
         <v>106674</v>
       </c>
-      <c r="AB124" s="5">
-        <f>C123-AA124</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC124" s="5">
+        <f>C123-AB124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1" t="s">
         <v>155</v>
       </c>
@@ -9235,16 +9343,16 @@
       </c>
       <c r="X125" s="3"/>
       <c r="Y125" s="3"/>
-      <c r="AA125" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB125" s="5">
+        <f t="shared" si="49"/>
         <v>84709</v>
       </c>
-      <c r="AB125" s="5">
-        <f>AA125-D123</f>
+      <c r="AC125" s="5">
+        <f>AB125-D123</f>
         <v>-900</v>
       </c>
     </row>
-    <row r="126" spans="1:28" s="8" customFormat="1" ht="15">
+    <row r="126" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="6" t="s">
         <v>156</v>
       </c>
@@ -9310,16 +9418,16 @@
       <c r="W126" s="7"/>
       <c r="X126" s="7"/>
       <c r="Y126" s="7"/>
-      <c r="AA126" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB126" s="9">
+        <f t="shared" si="49"/>
         <v>1601457</v>
       </c>
-      <c r="AB126" s="9">
-        <f>AA126-B126</f>
+      <c r="AC126" s="9">
+        <f>AB126-B126</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="127" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="127" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="1" t="s">
         <v>157</v>
       </c>
@@ -9367,16 +9475,16 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
       <c r="Y127" s="3"/>
-      <c r="AA127" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB127" s="5">
+        <f t="shared" si="49"/>
         <v>80120</v>
       </c>
-      <c r="AB127" s="5">
-        <f>C126-AA127</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC127" s="5">
+        <f>C126-AB127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="1" t="s">
         <v>158</v>
       </c>
@@ -9424,16 +9532,16 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
       <c r="Y128" s="3"/>
-      <c r="AA128" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB128" s="5">
+        <f t="shared" si="49"/>
         <v>64064</v>
       </c>
-      <c r="AB128" s="5">
-        <f>AA128-D126</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC128" s="5">
+        <f>AB128-D126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="6" t="s">
         <v>159</v>
       </c>
@@ -9503,16 +9611,16 @@
       </c>
       <c r="X129" s="7"/>
       <c r="Y129" s="7"/>
-      <c r="AA129" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB129" s="9">
+        <f t="shared" si="49"/>
         <v>2779837</v>
       </c>
-      <c r="AB129" s="9">
-        <f>AA129-B129</f>
+      <c r="AC129" s="9">
+        <f>AB129-B129</f>
         <v>-15085</v>
       </c>
     </row>
-    <row r="130" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="130" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="1" t="s">
         <v>160</v>
       </c>
@@ -9564,16 +9672,16 @@
       </c>
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
-      <c r="AA130" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB130" s="5">
+        <f t="shared" si="49"/>
         <v>152416</v>
       </c>
-      <c r="AB130" s="5">
-        <f>C129-AA130</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC130" s="5">
+        <f>C129-AB130</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="1" t="s">
         <v>161</v>
       </c>
@@ -9625,16 +9733,16 @@
       </c>
       <c r="X131" s="3"/>
       <c r="Y131" s="3"/>
-      <c r="AA131" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB131" s="5">
+        <f t="shared" si="49"/>
         <v>136331</v>
       </c>
-      <c r="AB131" s="5">
-        <f>AA131-D129</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC131" s="5">
+        <f>AB131-D129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="6" t="s">
         <v>162</v>
       </c>
@@ -9708,19 +9816,20 @@
       <c r="Y132" s="7">
         <v>208986</v>
       </c>
-      <c r="Z132" s="22">
+      <c r="Z132" s="32">
         <v>171568</v>
       </c>
-      <c r="AA132" s="9">
-        <f t="shared" si="10"/>
-        <v>2722527</v>
-      </c>
+      <c r="AA132" s="32"/>
       <c r="AB132" s="9">
-        <f>AA132-B132</f>
-        <v>-171568</v>
-      </c>
-    </row>
-    <row r="133" spans="1:28" s="2" customFormat="1" ht="15">
+        <f>SUM(L132:Z132)</f>
+        <v>2894095</v>
+      </c>
+      <c r="AC132" s="9">
+        <f>AB132-B132</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1" t="s">
         <v>163</v>
       </c>
@@ -9776,19 +9885,20 @@
       <c r="Y133" s="3">
         <v>8109</v>
       </c>
-      <c r="Z133" s="22">
+      <c r="Z133" s="21">
         <v>8337</v>
       </c>
-      <c r="AA133" s="5">
-        <f t="shared" si="10"/>
-        <v>119219</v>
-      </c>
-      <c r="AB133" s="5">
-        <f>C132-AA133</f>
-        <v>8337</v>
-      </c>
-    </row>
-    <row r="134" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AA133" s="21"/>
+      <c r="AB133" s="9">
+        <f>SUM(L133:Z133)</f>
+        <v>127556</v>
+      </c>
+      <c r="AC133" s="5">
+        <f>C132-AB133</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="1" t="s">
         <v>164</v>
       </c>
@@ -9844,19 +9954,20 @@
       <c r="Y134" s="3">
         <v>5395</v>
       </c>
-      <c r="Z134" s="22">
+      <c r="Z134" s="21">
         <v>5842</v>
       </c>
-      <c r="AA134" s="5">
-        <f t="shared" si="10"/>
-        <v>88142</v>
-      </c>
-      <c r="AB134" s="5">
-        <f>AA134-D132</f>
-        <v>-5842</v>
-      </c>
-    </row>
-    <row r="135" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AA134" s="21"/>
+      <c r="AB134" s="9">
+        <f>SUM(L134:Z134)</f>
+        <v>93984</v>
+      </c>
+      <c r="AC134" s="5">
+        <f>AB134-D132</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="6" t="s">
         <v>165</v>
       </c>
@@ -9918,16 +10029,16 @@
       <c r="W135" s="7"/>
       <c r="X135" s="7"/>
       <c r="Y135" s="7"/>
-      <c r="AA135" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB135" s="9">
+        <f t="shared" si="49"/>
         <v>1029053</v>
       </c>
-      <c r="AB135" s="9">
-        <f>AA135-B135</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC135" s="9">
+        <f>AB135-B135</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="1" t="s">
         <v>166</v>
       </c>
@@ -9971,16 +10082,16 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
       <c r="Y136" s="3"/>
-      <c r="AA136" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB136" s="5">
+        <f t="shared" si="49"/>
         <v>50312</v>
       </c>
-      <c r="AB136" s="5">
-        <f>C135-AA136</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC136" s="5">
+        <f>C135-AB136</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="1" t="s">
         <v>167</v>
       </c>
@@ -10024,16 +10135,16 @@
       <c r="W137" s="3"/>
       <c r="X137" s="3"/>
       <c r="Y137" s="3"/>
-      <c r="AA137" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB137" s="5">
+        <f t="shared" si="49"/>
         <v>32442</v>
       </c>
-      <c r="AB137" s="5">
-        <f>AA137-D135</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC137" s="5">
+        <f>AB137-D135</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="6" t="s">
         <v>168</v>
       </c>
@@ -10103,16 +10214,16 @@
       </c>
       <c r="X138" s="7"/>
       <c r="Y138" s="7"/>
-      <c r="AA138" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB138" s="9">
+        <f t="shared" si="49"/>
         <v>1928786</v>
       </c>
-      <c r="AB138" s="9">
-        <f>AA138-B138</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC138" s="9">
+        <f>AB138-B138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="1" t="s">
         <v>169</v>
       </c>
@@ -10164,16 +10275,16 @@
       </c>
       <c r="X139" s="3"/>
       <c r="Y139" s="3"/>
-      <c r="AA139" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB139" s="5">
+        <f t="shared" si="49"/>
         <v>94449</v>
       </c>
-      <c r="AB139" s="5">
-        <f>C138-AA139</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC139" s="5">
+        <f>C138-AB139</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1" t="s">
         <v>170</v>
       </c>
@@ -10225,16 +10336,16 @@
       </c>
       <c r="X140" s="3"/>
       <c r="Y140" s="3"/>
-      <c r="AA140" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB140" s="5">
+        <f t="shared" si="49"/>
         <v>70488</v>
       </c>
-      <c r="AB140" s="5">
-        <f>AA140-D138</f>
+      <c r="AC140" s="5">
+        <f>AB140-D138</f>
         <v>-4</v>
       </c>
     </row>
-    <row r="141" spans="1:28" s="8" customFormat="1" ht="15">
+    <row r="141" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="6" t="s">
         <v>171</v>
       </c>
@@ -10294,16 +10405,16 @@
       <c r="W141" s="7"/>
       <c r="X141" s="7"/>
       <c r="Y141" s="7"/>
-      <c r="AA141" s="9">
-        <f t="shared" si="10"/>
+      <c r="AB141" s="9">
+        <f t="shared" si="49"/>
         <v>2610405</v>
       </c>
-      <c r="AB141" s="9">
-        <f>AA141-B141</f>
+      <c r="AC141" s="9">
+        <f>AB141-B141</f>
         <v>-47206</v>
       </c>
     </row>
-    <row r="142" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="142" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1" t="s">
         <v>172</v>
       </c>
@@ -10345,16 +10456,16 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
       <c r="Y142" s="3"/>
-      <c r="AA142" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB142" s="5">
+        <f t="shared" si="49"/>
         <v>149962</v>
       </c>
-      <c r="AB142" s="5">
-        <f>C141-AA142</f>
+      <c r="AC142" s="5">
+        <f>C141-AB142</f>
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="143" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="1" t="s">
         <v>173</v>
       </c>
@@ -10396,16 +10507,16 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
       <c r="Y143" s="3"/>
-      <c r="AA143" s="5">
-        <f t="shared" si="10"/>
+      <c r="AB143" s="5">
+        <f t="shared" si="49"/>
         <v>106766</v>
       </c>
-      <c r="AB143" s="5">
-        <f>AA143-D141</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC143" s="5">
+        <f>AB143-D141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="6" t="s">
         <v>174</v>
       </c>
@@ -10451,10 +10562,10 @@
       <c r="W144" s="7"/>
       <c r="X144" s="7"/>
       <c r="Y144" s="7"/>
-      <c r="AA144" s="9"/>
       <c r="AB144" s="9"/>
-    </row>
-    <row r="145" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC144" s="9"/>
+    </row>
+    <row r="145" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="6" t="s">
         <v>175</v>
       </c>
@@ -10500,10 +10611,10 @@
       <c r="W145" s="7"/>
       <c r="X145" s="7"/>
       <c r="Y145" s="7"/>
-      <c r="AA145" s="9"/>
       <c r="AB145" s="9"/>
-    </row>
-    <row r="146" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC145" s="9"/>
+    </row>
+    <row r="146" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="6" t="s">
         <v>176</v>
       </c>
@@ -10565,16 +10676,16 @@
       <c r="W146" s="7"/>
       <c r="X146" s="7"/>
       <c r="Y146" s="7"/>
-      <c r="AA146" s="9">
-        <f t="shared" ref="AA146:AA160" si="11">SUM(L146:Y146)</f>
+      <c r="AB146" s="9">
+        <f t="shared" ref="AB146:AB148" si="50">SUM(L146:Y146)</f>
         <v>679176</v>
       </c>
-      <c r="AB146" s="9">
-        <f>AA146-B146</f>
+      <c r="AC146" s="9">
+        <f>AB146-B146</f>
         <v>-155142</v>
       </c>
     </row>
-    <row r="147" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="147" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="1" t="s">
         <v>177</v>
       </c>
@@ -10618,16 +10729,16 @@
       <c r="W147" s="3"/>
       <c r="X147" s="3"/>
       <c r="Y147" s="3"/>
-      <c r="AA147" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB147" s="5">
+        <f t="shared" si="50"/>
         <v>30505</v>
       </c>
-      <c r="AB147" s="5">
-        <f>C146-AA147</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC147" s="5">
+        <f>C146-AB147</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1" t="s">
         <v>178</v>
       </c>
@@ -10671,16 +10782,16 @@
       <c r="W148" s="3"/>
       <c r="X148" s="3"/>
       <c r="Y148" s="3"/>
-      <c r="AA148" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB148" s="5">
+        <f t="shared" si="50"/>
         <v>25031</v>
       </c>
-      <c r="AB148" s="5">
-        <f>AA148-D146</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC148" s="5">
+        <f>AB148-D146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="6" t="s">
         <v>179</v>
       </c>
@@ -10746,16 +10857,16 @@
       <c r="W149" s="7"/>
       <c r="X149" s="7"/>
       <c r="Y149" s="7"/>
-      <c r="AA149" s="9">
-        <f t="shared" si="11"/>
+      <c r="AB149" s="9">
+        <f t="shared" ref="AB149:AB178" si="51">SUM(L149:Z149)</f>
         <v>2428445</v>
       </c>
-      <c r="AB149" s="9">
-        <f>AA149-B149</f>
+      <c r="AC149" s="9">
+        <f t="shared" ref="AC149" si="52">AB149-B149</f>
         <v>-5000</v>
       </c>
     </row>
-    <row r="150" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="150" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="1" t="s">
         <v>180</v>
       </c>
@@ -10803,16 +10914,16 @@
       <c r="W150" s="3"/>
       <c r="X150" s="3"/>
       <c r="Y150" s="3"/>
-      <c r="AA150" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB150" s="9">
+        <f t="shared" si="51"/>
         <v>125198</v>
       </c>
-      <c r="AB150" s="5">
-        <f>C149-AA150</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC150" s="5">
+        <f t="shared" ref="AC150" si="53">C149-AB150</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="1" t="s">
         <v>181</v>
       </c>
@@ -10860,16 +10971,16 @@
       <c r="W151" s="3"/>
       <c r="X151" s="3"/>
       <c r="Y151" s="3"/>
-      <c r="AA151" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB151" s="9">
+        <f t="shared" si="51"/>
         <v>95643</v>
       </c>
-      <c r="AB151" s="5">
-        <f>AA151-D149</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC151" s="5">
+        <f t="shared" ref="AC151" si="54">AB151-D149</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="6" t="s">
         <v>182</v>
       </c>
@@ -10931,16 +11042,16 @@
       <c r="W152" s="7"/>
       <c r="X152" s="7"/>
       <c r="Y152" s="7"/>
-      <c r="AA152" s="9">
-        <f t="shared" si="11"/>
+      <c r="AB152" s="9">
+        <f t="shared" si="51"/>
         <v>1526608</v>
       </c>
-      <c r="AB152" s="9">
-        <f>AA152-B152</f>
+      <c r="AC152" s="9">
+        <f t="shared" ref="AC152" si="55">AB152-B152</f>
         <v>-111603</v>
       </c>
     </row>
-    <row r="153" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="153" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="1" t="s">
         <v>183</v>
       </c>
@@ -10984,16 +11095,16 @@
       <c r="W153" s="3"/>
       <c r="X153" s="3"/>
       <c r="Y153" s="3"/>
-      <c r="AA153" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB153" s="9">
+        <f t="shared" si="51"/>
         <v>76638</v>
       </c>
-      <c r="AB153" s="5">
-        <f>C152-AA153</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC153" s="5">
+        <f t="shared" ref="AC153" si="56">C152-AB153</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="1" t="s">
         <v>184</v>
       </c>
@@ -11037,16 +11148,16 @@
       <c r="W154" s="3"/>
       <c r="X154" s="3"/>
       <c r="Y154" s="3"/>
-      <c r="AA154" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB154" s="9">
+        <f t="shared" si="51"/>
         <v>64533</v>
       </c>
-      <c r="AB154" s="5">
-        <f>AA154-D152</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC154" s="5">
+        <f t="shared" ref="AC154" si="57">AB154-D152</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="6" t="s">
         <v>185</v>
       </c>
@@ -11116,16 +11227,16 @@
       </c>
       <c r="X155" s="7"/>
       <c r="Y155" s="7"/>
-      <c r="AA155" s="9">
-        <f t="shared" si="11"/>
+      <c r="AB155" s="9">
+        <f t="shared" si="51"/>
         <v>1432371</v>
       </c>
-      <c r="AB155" s="9">
-        <f>AA155-B155</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC155" s="9">
+        <f t="shared" ref="AC155" si="58">AB155-B155</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="1" t="s">
         <v>186</v>
       </c>
@@ -11177,16 +11288,16 @@
       </c>
       <c r="X156" s="3"/>
       <c r="Y156" s="3"/>
-      <c r="AA156" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB156" s="9">
+        <f t="shared" si="51"/>
         <v>77397</v>
       </c>
-      <c r="AB156" s="5">
-        <f>C155-AA156</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC156" s="5">
+        <f t="shared" ref="AC156" si="59">C155-AB156</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="1" t="s">
         <v>187</v>
       </c>
@@ -11238,16 +11349,16 @@
       </c>
       <c r="X157" s="3"/>
       <c r="Y157" s="3"/>
-      <c r="AA157" s="5">
-        <f t="shared" si="11"/>
+      <c r="AB157" s="9">
+        <f t="shared" si="51"/>
         <v>57188</v>
       </c>
-      <c r="AB157" s="5">
-        <f>AA157-D155</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC157" s="5">
+        <f t="shared" ref="AC157" si="60">AB157-D155</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="6" t="s">
         <v>188</v>
       </c>
@@ -11309,16 +11420,16 @@
       <c r="W158" s="7"/>
       <c r="X158" s="7"/>
       <c r="Y158" s="7"/>
-      <c r="AA158" s="9">
-        <f t="shared" si="11"/>
+      <c r="AB158" s="9">
+        <f t="shared" si="51"/>
         <v>1114612</v>
       </c>
-      <c r="AB158" s="9">
-        <f>AA158-B158</f>
+      <c r="AC158" s="9">
+        <f t="shared" ref="AC158" si="61">AB158-B158</f>
         <v>-27139</v>
       </c>
     </row>
-    <row r="159" spans="1:28" s="2" customFormat="1" ht="15">
+    <row r="159" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="1" t="s">
         <v>189</v>
       </c>
@@ -11356,22 +11467,24 @@
       <c r="S159" s="3">
         <v>2110</v>
       </c>
-      <c r="T159" s="3"/>
+      <c r="T159" s="3">
+        <v>1920</v>
+      </c>
       <c r="U159" s="3"/>
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
       <c r="X159" s="3"/>
       <c r="Y159" s="3"/>
-      <c r="AA159" s="5">
-        <f t="shared" si="11"/>
-        <v>57602</v>
-      </c>
-      <c r="AB159" s="5">
-        <f>C158-AA159</f>
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="160" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB159" s="9">
+        <f t="shared" si="51"/>
+        <v>59522</v>
+      </c>
+      <c r="AC159" s="5">
+        <f t="shared" ref="AC159" si="62">C158-AB159</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="1" t="s">
         <v>190</v>
       </c>
@@ -11409,22 +11522,24 @@
       <c r="S160" s="3">
         <v>1071</v>
       </c>
-      <c r="T160" s="3"/>
+      <c r="T160" s="3">
+        <v>1145</v>
+      </c>
       <c r="U160" s="3"/>
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
       <c r="X160" s="3"/>
       <c r="Y160" s="3"/>
-      <c r="AA160" s="5">
-        <f t="shared" si="11"/>
-        <v>33773</v>
-      </c>
-      <c r="AB160" s="5">
-        <f>AA160-D158</f>
-        <v>-1145</v>
-      </c>
-    </row>
-    <row r="161" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB160" s="9">
+        <f t="shared" si="51"/>
+        <v>34918</v>
+      </c>
+      <c r="AC160" s="5">
+        <f t="shared" ref="AC160" si="63">AB160-D158</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="6" t="s">
         <v>191</v>
       </c>
@@ -11494,13 +11609,16 @@
       </c>
       <c r="X161" s="7"/>
       <c r="Y161" s="7"/>
-      <c r="AA161" s="9"/>
       <c r="AB161" s="9">
-        <f>AA161-B161</f>
-        <v>-2900646</v>
-      </c>
-    </row>
-    <row r="162" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" si="51"/>
+        <v>2871526</v>
+      </c>
+      <c r="AC161" s="9">
+        <f t="shared" ref="AC161" si="64">AB161-B161</f>
+        <v>-29120</v>
+      </c>
+    </row>
+    <row r="162" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="1" t="s">
         <v>192</v>
       </c>
@@ -11552,13 +11670,16 @@
       </c>
       <c r="X162" s="3"/>
       <c r="Y162" s="3"/>
-      <c r="AA162" s="5"/>
-      <c r="AB162" s="5">
-        <f>C161-AA162</f>
+      <c r="AB162" s="9">
+        <f t="shared" si="51"/>
         <v>133938</v>
       </c>
-    </row>
-    <row r="163" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC162" s="5">
+        <f t="shared" ref="AC162" si="65">C161-AB162</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="1" t="s">
         <v>193</v>
       </c>
@@ -11610,13 +11731,16 @@
       </c>
       <c r="X163" s="3"/>
       <c r="Y163" s="3"/>
-      <c r="AA163" s="5"/>
-      <c r="AB163" s="5">
-        <f>AA163-D161</f>
-        <v>-105819</v>
-      </c>
-    </row>
-    <row r="164" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB163" s="9">
+        <f t="shared" si="51"/>
+        <v>105719</v>
+      </c>
+      <c r="AC163" s="5">
+        <f t="shared" ref="AC163" si="66">AB163-D161</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="164" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="6" t="s">
         <v>194</v>
       </c>
@@ -11686,13 +11810,16 @@
       </c>
       <c r="X164" s="7"/>
       <c r="Y164" s="7"/>
-      <c r="AA164" s="9"/>
       <c r="AB164" s="9">
-        <f>AA164-B164</f>
-        <v>-1851150</v>
-      </c>
-    </row>
-    <row r="165" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" si="51"/>
+        <v>1851150</v>
+      </c>
+      <c r="AC164" s="9">
+        <f t="shared" ref="AC164" si="67">AB164-B164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="1" t="s">
         <v>195</v>
       </c>
@@ -11744,13 +11871,16 @@
       </c>
       <c r="X165" s="3"/>
       <c r="Y165" s="3"/>
-      <c r="AA165" s="5"/>
-      <c r="AB165" s="5">
-        <f>C164-AA165</f>
+      <c r="AB165" s="9">
+        <f t="shared" si="51"/>
         <v>85187</v>
       </c>
-    </row>
-    <row r="166" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC165" s="5">
+        <f t="shared" ref="AC165" si="68">C164-AB165</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="1" t="s">
         <v>196</v>
       </c>
@@ -11802,13 +11932,16 @@
       </c>
       <c r="X166" s="3"/>
       <c r="Y166" s="3"/>
-      <c r="AA166" s="5"/>
-      <c r="AB166" s="5">
-        <f>AA166-D164</f>
-        <v>-62036</v>
-      </c>
-    </row>
-    <row r="167" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB166" s="9">
+        <f t="shared" si="51"/>
+        <v>62036</v>
+      </c>
+      <c r="AC166" s="5">
+        <f t="shared" ref="AC166" si="69">AB166-D164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="6" t="s">
         <v>197</v>
       </c>
@@ -11878,13 +12011,16 @@
       </c>
       <c r="X167" s="7"/>
       <c r="Y167" s="7"/>
-      <c r="AA167" s="9"/>
       <c r="AB167" s="9">
-        <f>AA167-B167</f>
-        <v>-1515881</v>
-      </c>
-    </row>
-    <row r="168" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" si="51"/>
+        <v>1515881</v>
+      </c>
+      <c r="AC167" s="9">
+        <f t="shared" ref="AC167" si="70">AB167-B167</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="1" t="s">
         <v>198</v>
       </c>
@@ -11936,13 +12072,16 @@
       </c>
       <c r="X168" s="3"/>
       <c r="Y168" s="3"/>
-      <c r="AA168" s="5"/>
-      <c r="AB168" s="5">
-        <f>C167-AA168</f>
+      <c r="AB168" s="9">
+        <f t="shared" si="51"/>
         <v>79257</v>
       </c>
-    </row>
-    <row r="169" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC168" s="5">
+        <f t="shared" ref="AC168" si="71">C167-AB168</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="1" t="s">
         <v>199</v>
       </c>
@@ -11994,13 +12133,16 @@
       </c>
       <c r="X169" s="3"/>
       <c r="Y169" s="3"/>
-      <c r="AA169" s="5"/>
-      <c r="AB169" s="5">
-        <f>AA169-D167</f>
-        <v>-60358</v>
-      </c>
-    </row>
-    <row r="170" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB169" s="9">
+        <f t="shared" si="51"/>
+        <v>60358</v>
+      </c>
+      <c r="AC169" s="5">
+        <f t="shared" ref="AC169" si="72">AB169-D167</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="6" t="s">
         <v>200</v>
       </c>
@@ -12058,13 +12200,16 @@
       <c r="W170" s="7"/>
       <c r="X170" s="7"/>
       <c r="Y170" s="7"/>
-      <c r="AA170" s="9"/>
       <c r="AB170" s="9">
-        <f>AA170-B170</f>
-        <v>-2057807</v>
-      </c>
-    </row>
-    <row r="171" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" si="51"/>
+        <v>2051093</v>
+      </c>
+      <c r="AC170" s="9">
+        <f t="shared" ref="AC170" si="73">AB170-B170</f>
+        <v>-6714</v>
+      </c>
+    </row>
+    <row r="171" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="1" t="s">
         <v>201</v>
       </c>
@@ -12104,13 +12249,16 @@
       <c r="W171" s="3"/>
       <c r="X171" s="3"/>
       <c r="Y171" s="3"/>
-      <c r="AA171" s="5"/>
-      <c r="AB171" s="5">
-        <f>C170-AA171</f>
-        <v>98722</v>
-      </c>
-    </row>
-    <row r="172" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB171" s="9">
+        <f t="shared" si="51"/>
+        <v>98723</v>
+      </c>
+      <c r="AC171" s="5">
+        <f t="shared" ref="AC171" si="74">C170-AB171</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="1" t="s">
         <v>202</v>
       </c>
@@ -12150,13 +12298,16 @@
       <c r="W172" s="3"/>
       <c r="X172" s="3"/>
       <c r="Y172" s="3"/>
-      <c r="AA172" s="5"/>
-      <c r="AB172" s="5">
-        <f>AA172-D170</f>
-        <v>-6300</v>
-      </c>
-    </row>
-    <row r="173" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB172" s="9">
+        <f t="shared" si="51"/>
+        <v>57329</v>
+      </c>
+      <c r="AC172" s="5">
+        <f t="shared" ref="AC172" si="75">AB172-D170</f>
+        <v>51029</v>
+      </c>
+    </row>
+    <row r="173" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="6" t="s">
         <v>203</v>
       </c>
@@ -12224,13 +12375,16 @@
       <c r="W173" s="7"/>
       <c r="X173" s="7"/>
       <c r="Y173" s="7"/>
-      <c r="AA173" s="9"/>
       <c r="AB173" s="9">
-        <f>AA173-B173</f>
-        <v>-2465668</v>
-      </c>
-    </row>
-    <row r="174" spans="1:28" s="2" customFormat="1" ht="15">
+        <f t="shared" si="51"/>
+        <v>2465668</v>
+      </c>
+      <c r="AC173" s="9">
+        <f t="shared" ref="AC173" si="76">AB173-B173</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="1" t="s">
         <v>204</v>
       </c>
@@ -12280,13 +12434,16 @@
       <c r="W174" s="3"/>
       <c r="X174" s="3"/>
       <c r="Y174" s="3"/>
-      <c r="AA174" s="5"/>
-      <c r="AB174" s="5">
-        <f>C173-AA174</f>
+      <c r="AB174" s="9">
+        <f t="shared" si="51"/>
         <v>118718</v>
       </c>
-    </row>
-    <row r="175" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AC174" s="5">
+        <f t="shared" ref="AC174" si="77">C173-AB174</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="1" t="s">
         <v>205</v>
       </c>
@@ -12336,13 +12493,16 @@
       <c r="W175" s="3"/>
       <c r="X175" s="3"/>
       <c r="Y175" s="3"/>
-      <c r="AA175" s="5"/>
-      <c r="AB175" s="5">
-        <f>AA175-D173</f>
-        <v>-93117</v>
-      </c>
-    </row>
-    <row r="176" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB175" s="9">
+        <f t="shared" si="51"/>
+        <v>93117</v>
+      </c>
+      <c r="AC175" s="5">
+        <f t="shared" ref="AC175" si="78">AB175-D173</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="6" t="s">
         <v>206</v>
       </c>
@@ -12400,13 +12560,16 @@
       <c r="W176" s="7"/>
       <c r="X176" s="7"/>
       <c r="Y176" s="7"/>
-      <c r="AA176" s="9"/>
       <c r="AB176" s="9">
-        <f>AA176-B176</f>
-        <v>-1849664</v>
-      </c>
-    </row>
-    <row r="177" spans="1:48" s="2" customFormat="1" ht="15">
+        <f t="shared" si="51"/>
+        <v>1849664</v>
+      </c>
+      <c r="AC176" s="9">
+        <f t="shared" ref="AC176" si="79">AB176-B176</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="1" t="s">
         <v>207</v>
       </c>
@@ -12446,13 +12609,16 @@
       <c r="W177" s="3"/>
       <c r="X177" s="3"/>
       <c r="Y177" s="3"/>
-      <c r="AA177" s="5"/>
-      <c r="AB177" s="5">
-        <f>C176-AA177</f>
+      <c r="AB177" s="9">
+        <f t="shared" si="51"/>
         <v>97498</v>
       </c>
-    </row>
-    <row r="178" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC177" s="5">
+        <f t="shared" ref="AC177" si="80">C176-AB177</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="1" t="s">
         <v>208</v>
       </c>
@@ -12492,13 +12658,16 @@
       <c r="W178" s="3"/>
       <c r="X178" s="3"/>
       <c r="Y178" s="3"/>
-      <c r="AA178" s="5"/>
-      <c r="AB178" s="5">
-        <f>AA178-D176</f>
-        <v>-60257</v>
-      </c>
-    </row>
-    <row r="179" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AB178" s="9">
+        <f t="shared" si="51"/>
+        <v>60257</v>
+      </c>
+      <c r="AC178" s="5">
+        <f t="shared" ref="AC178" si="81">AB178-D176</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="6" t="s">
         <v>209</v>
       </c>
@@ -12572,16 +12741,20 @@
       <c r="Y179" s="7">
         <v>166979</v>
       </c>
-      <c r="Z179" s="22">
+      <c r="Z179" s="32">
         <v>178770</v>
       </c>
-      <c r="AA179" s="9"/>
+      <c r="AA179" s="32"/>
       <c r="AB179" s="9">
-        <f>AA179-B179</f>
-        <v>-2244377</v>
-      </c>
-    </row>
-    <row r="180" spans="1:48" s="2" customFormat="1" ht="15">
+        <f t="shared" ref="AB179:AB184" si="82">SUM(L179:Z179)</f>
+        <v>2284377</v>
+      </c>
+      <c r="AC179" s="9">
+        <f>AB179-B179</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="180" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="1" t="s">
         <v>210</v>
       </c>
@@ -12637,16 +12810,20 @@
       <c r="Y180" s="3">
         <v>6973</v>
       </c>
-      <c r="Z180" s="22">
+      <c r="Z180" s="21">
         <v>9107</v>
       </c>
-      <c r="AA180" s="5"/>
-      <c r="AB180" s="5">
-        <f>C179-AA180</f>
+      <c r="AA180" s="21"/>
+      <c r="AB180" s="9">
+        <f t="shared" si="82"/>
         <v>105242</v>
       </c>
-    </row>
-    <row r="181" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC180" s="5">
+        <f>C179-AB180</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="1" t="s">
         <v>211</v>
       </c>
@@ -12702,16 +12879,20 @@
       <c r="Y181" s="3">
         <v>4525</v>
       </c>
-      <c r="Z181" s="22">
+      <c r="Z181" s="21">
         <v>5338</v>
       </c>
-      <c r="AA181" s="5"/>
-      <c r="AB181" s="5">
-        <f>AA181-D179</f>
-        <v>-77254</v>
-      </c>
-    </row>
-    <row r="182" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AA181" s="21"/>
+      <c r="AB181" s="9">
+        <f t="shared" si="82"/>
+        <v>77254</v>
+      </c>
+      <c r="AC181" s="5">
+        <f>AB181-D179</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="6" t="s">
         <v>212</v>
       </c>
@@ -12777,13 +12958,16 @@
       <c r="W182" s="7"/>
       <c r="X182" s="7"/>
       <c r="Y182" s="7"/>
-      <c r="AA182" s="9"/>
       <c r="AB182" s="9">
-        <f>AA182-B182</f>
-        <v>-1198269</v>
-      </c>
-    </row>
-    <row r="183" spans="1:48" s="2" customFormat="1" ht="15">
+        <f t="shared" si="82"/>
+        <v>1168192</v>
+      </c>
+      <c r="AC182" s="9">
+        <f>AB182-B182</f>
+        <v>-30077</v>
+      </c>
+    </row>
+    <row r="183" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="1" t="s">
         <v>213</v>
       </c>
@@ -12831,13 +13015,16 @@
       <c r="W183" s="3"/>
       <c r="X183" s="3"/>
       <c r="Y183" s="3"/>
-      <c r="AA183" s="5"/>
-      <c r="AB183" s="5">
-        <f>C182-AA183</f>
+      <c r="AB183" s="9">
+        <f t="shared" si="82"/>
         <v>44232</v>
       </c>
-    </row>
-    <row r="184" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC183" s="5">
+        <f>C182-AB183</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="1" t="s">
         <v>214</v>
       </c>
@@ -12885,13 +13072,16 @@
       <c r="W184" s="3"/>
       <c r="X184" s="3"/>
       <c r="Y184" s="3"/>
-      <c r="AA184" s="5"/>
-      <c r="AB184" s="5">
-        <f>AA184-D182</f>
-        <v>-39027</v>
-      </c>
-    </row>
-    <row r="185" spans="1:48" s="13" customFormat="1" ht="15">
+      <c r="AB184" s="9">
+        <f t="shared" si="82"/>
+        <v>39027</v>
+      </c>
+      <c r="AC184" s="5">
+        <f>AB184-D182</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:49" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="11" t="s">
         <v>215</v>
       </c>
@@ -12937,82 +13127,82 @@
       <c r="W185" s="12"/>
       <c r="X185" s="12"/>
       <c r="Y185" s="12"/>
-      <c r="AA185" s="14"/>
       <c r="AB185" s="14"/>
-      <c r="AD185" s="14">
-        <f t="shared" ref="AD185:AL185" si="12">SUM(B81:B184)</f>
-        <v>64271390</v>
-      </c>
+      <c r="AC185" s="14"/>
       <c r="AE185" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="AE185:AM185" si="83">SUM(B81:B184)</f>
+        <v>64280390</v>
+      </c>
+      <c r="AF185" s="14">
+        <f t="shared" si="83"/>
         <v>3119996</v>
       </c>
-      <c r="AF185" s="14">
-        <f t="shared" si="12"/>
-        <v>2356748</v>
-      </c>
       <c r="AG185" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="83"/>
+        <v>2356798</v>
+      </c>
+      <c r="AH185" s="14">
+        <f t="shared" si="83"/>
         <v>4240997</v>
       </c>
-      <c r="AH185" s="14">
-        <f t="shared" si="12"/>
+      <c r="AI185" s="14">
+        <f t="shared" si="83"/>
         <v>158807</v>
       </c>
-      <c r="AI185" s="14">
-        <f t="shared" si="12"/>
+      <c r="AJ185" s="14">
+        <f t="shared" si="83"/>
         <v>133707</v>
       </c>
-      <c r="AJ185" s="14">
-        <f t="shared" si="12"/>
+      <c r="AK185" s="14">
+        <f t="shared" si="83"/>
         <v>62434631</v>
       </c>
-      <c r="AK185" s="14">
-        <f t="shared" si="12"/>
+      <c r="AL185" s="14">
+        <f t="shared" si="83"/>
         <v>3104370</v>
       </c>
-      <c r="AL185" s="14">
-        <f t="shared" si="12"/>
+      <c r="AM185" s="14">
+        <f t="shared" si="83"/>
         <v>2159337</v>
       </c>
-      <c r="AN185" s="14">
-        <f t="shared" ref="AN185:AV185" si="13">AD185-B185</f>
-        <v>-398206</v>
-      </c>
       <c r="AO185" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="AO185:AW185" si="84">AE185-B185</f>
+        <v>-389206</v>
+      </c>
+      <c r="AP185" s="14">
+        <f t="shared" si="84"/>
         <v>-15226</v>
       </c>
-      <c r="AP185" s="14">
-        <f t="shared" si="13"/>
-        <v>-72656</v>
-      </c>
       <c r="AQ185" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="84"/>
+        <v>-72606</v>
+      </c>
+      <c r="AR185" s="14">
+        <f t="shared" si="84"/>
         <v>-2232049</v>
       </c>
-      <c r="AR185" s="14">
-        <f t="shared" si="13"/>
+      <c r="AS185" s="14">
+        <f t="shared" si="84"/>
         <v>-78855</v>
       </c>
-      <c r="AS185" s="14">
-        <f t="shared" si="13"/>
+      <c r="AT185" s="14">
+        <f t="shared" si="84"/>
         <v>-67085</v>
       </c>
-      <c r="AT185" s="14">
-        <f t="shared" si="13"/>
+      <c r="AU185" s="14">
+        <f t="shared" si="84"/>
         <v>-315984</v>
       </c>
-      <c r="AU185" s="14">
-        <f t="shared" si="13"/>
+      <c r="AV185" s="14">
+        <f t="shared" si="84"/>
         <v>-10148</v>
       </c>
-      <c r="AV185" s="14">
-        <f t="shared" si="13"/>
+      <c r="AW185" s="14">
+        <f t="shared" si="84"/>
         <v>-3290</v>
       </c>
     </row>
-    <row r="186" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="186" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="1" t="s">
         <v>216</v>
       </c>
@@ -13076,13 +13266,16 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="3"/>
-      <c r="AA186" s="5"/>
-      <c r="AB186" s="5">
-        <f>AA186-B186</f>
-        <v>-2078878</v>
-      </c>
-    </row>
-    <row r="187" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB186" s="9">
+        <f>SUM(L186:Z186)</f>
+        <v>2078778</v>
+      </c>
+      <c r="AC186" s="9">
+        <f>AB186-B186</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="1" t="s">
         <v>217</v>
       </c>
@@ -13128,13 +13321,16 @@
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
       <c r="Y187" s="3"/>
-      <c r="AA187" s="5"/>
-      <c r="AB187" s="5">
-        <f>C186-AA187</f>
-        <v>116779</v>
-      </c>
-    </row>
-    <row r="188" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB187" s="9">
+        <f>SUM(L187:Z187)</f>
+        <v>116879</v>
+      </c>
+      <c r="AC187" s="5">
+        <f>C186-AB187</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="188" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="1" t="s">
         <v>218</v>
       </c>
@@ -13180,13 +13376,16 @@
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
       <c r="Y188" s="3"/>
-      <c r="AA188" s="5"/>
-      <c r="AB188" s="5">
-        <f>AA188-D186</f>
-        <v>-69145</v>
-      </c>
-    </row>
-    <row r="189" spans="1:48" s="13" customFormat="1" ht="15">
+      <c r="AB188" s="9">
+        <f>SUM(L188:Z188)</f>
+        <v>69145</v>
+      </c>
+      <c r="AC188" s="5">
+        <f>AB188-D186</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:49" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="11" t="s">
         <v>219</v>
       </c>
@@ -13232,82 +13431,82 @@
       <c r="W189" s="12"/>
       <c r="X189" s="12"/>
       <c r="Y189" s="12"/>
-      <c r="AA189" s="14"/>
       <c r="AB189" s="14"/>
-      <c r="AD189" s="14">
-        <f t="shared" ref="AD189:AL189" si="14">SUM(AD38:AD185)</f>
-        <v>95327255</v>
-      </c>
+      <c r="AC189" s="14"/>
       <c r="AE189" s="14">
-        <f t="shared" si="14"/>
-        <v>4448302</v>
+        <f>SUM(AE38:AE185)+AB186</f>
+        <v>97417033</v>
       </c>
       <c r="AF189" s="14">
-        <f t="shared" si="14"/>
-        <v>3205555</v>
+        <f>SUM(AF38:AF185)+AB187</f>
+        <v>4565181</v>
       </c>
       <c r="AG189" s="14">
-        <f t="shared" si="14"/>
+        <f>SUM(AG38:AG185)+AB188</f>
+        <v>3274750</v>
+      </c>
+      <c r="AH189" s="14">
+        <f t="shared" ref="AH189:AM189" si="85">SUM(AH38:AH185)</f>
         <v>7596913</v>
       </c>
-      <c r="AH189" s="14">
-        <f t="shared" si="14"/>
+      <c r="AI189" s="14">
+        <f t="shared" si="85"/>
         <v>271217</v>
       </c>
-      <c r="AI189" s="14">
-        <f t="shared" si="14"/>
+      <c r="AJ189" s="14">
+        <f t="shared" si="85"/>
         <v>215300</v>
       </c>
-      <c r="AJ189" s="14">
-        <f t="shared" si="14"/>
+      <c r="AK189" s="14">
+        <f t="shared" si="85"/>
         <v>92216969</v>
       </c>
-      <c r="AK189" s="14">
-        <f t="shared" si="14"/>
+      <c r="AL189" s="14">
+        <f t="shared" si="85"/>
         <v>4395359</v>
       </c>
-      <c r="AL189" s="14">
-        <f t="shared" si="14"/>
+      <c r="AM189" s="14">
+        <f t="shared" si="85"/>
         <v>2964071</v>
       </c>
-      <c r="AN189" s="14">
-        <f t="shared" ref="AN189:AV189" si="15">AD189-B189</f>
-        <v>-2480084</v>
-      </c>
       <c r="AO189" s="14">
-        <f t="shared" si="15"/>
-        <v>-132003</v>
+        <f t="shared" ref="AO189:AW189" si="86">AE189-B189</f>
+        <v>-390306</v>
       </c>
       <c r="AP189" s="14">
-        <f t="shared" si="15"/>
-        <v>-141801</v>
+        <f t="shared" si="86"/>
+        <v>-15124</v>
       </c>
       <c r="AQ189" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="86"/>
+        <v>-72606</v>
+      </c>
+      <c r="AR189" s="14">
+        <f t="shared" si="86"/>
         <v>-2548146</v>
       </c>
-      <c r="AR189" s="14">
-        <f t="shared" si="15"/>
+      <c r="AS189" s="14">
+        <f t="shared" si="86"/>
         <v>-94686</v>
       </c>
-      <c r="AS189" s="14">
-        <f t="shared" si="15"/>
+      <c r="AT189" s="14">
+        <f t="shared" si="86"/>
         <v>-76707</v>
       </c>
-      <c r="AT189" s="14">
-        <f t="shared" si="15"/>
+      <c r="AU189" s="14">
+        <f t="shared" si="86"/>
         <v>-2156682</v>
       </c>
-      <c r="AU189" s="14">
-        <f t="shared" si="15"/>
+      <c r="AV189" s="14">
+        <f t="shared" si="86"/>
         <v>-115162</v>
       </c>
-      <c r="AV189" s="14">
-        <f t="shared" si="15"/>
+      <c r="AW189" s="14">
+        <f t="shared" si="86"/>
         <v>260696</v>
       </c>
     </row>
-    <row r="190" spans="1:48" s="8" customFormat="1" ht="15">
+    <row r="190" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="6" t="s">
         <v>220</v>
       </c>
@@ -13367,10 +13566,10 @@
       <c r="W190" s="7"/>
       <c r="X190" s="7"/>
       <c r="Y190" s="7"/>
-      <c r="AA190" s="9"/>
       <c r="AB190" s="9"/>
-    </row>
-    <row r="191" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC190" s="9"/>
+    </row>
+    <row r="191" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="1" t="s">
         <v>221</v>
       </c>
@@ -13412,10 +13611,16 @@
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
       <c r="Y191" s="3"/>
-      <c r="AA191" s="5"/>
-      <c r="AB191" s="5"/>
-    </row>
-    <row r="192" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB191" s="9">
+        <f t="shared" ref="AB191:AB192" si="87">SUM(L191:Z191)</f>
+        <v>22979</v>
+      </c>
+      <c r="AC191" s="5">
+        <f t="shared" ref="AC191" si="88">C190-AB191</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="1" t="s">
         <v>222</v>
       </c>
@@ -13457,10 +13662,16 @@
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
-      <c r="AA192" s="5"/>
-      <c r="AB192" s="5"/>
-    </row>
-    <row r="193" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB192" s="9">
+        <f t="shared" si="87"/>
+        <v>19460</v>
+      </c>
+      <c r="AC192" s="5">
+        <f t="shared" ref="AC192" si="89">AB192-D190</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="6" t="s">
         <v>223</v>
       </c>
@@ -13526,10 +13737,16 @@
       <c r="W193" s="7"/>
       <c r="X193" s="7"/>
       <c r="Y193" s="7"/>
-      <c r="AA193" s="9"/>
-      <c r="AB193" s="9"/>
-    </row>
-    <row r="194" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB193" s="9">
+        <f t="shared" ref="AB193" si="90">SUM(L193:Y193)</f>
+        <v>661444</v>
+      </c>
+      <c r="AC193" s="9">
+        <f t="shared" ref="AC193" si="91">AB193-B193</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="1" t="s">
         <v>224</v>
       </c>
@@ -13577,10 +13794,16 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
-      <c r="AA194" s="5"/>
-      <c r="AB194" s="5"/>
-    </row>
-    <row r="195" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB194" s="9">
+        <f t="shared" ref="AB194:AB195" si="92">SUM(L194:Z194)</f>
+        <v>16183</v>
+      </c>
+      <c r="AC194" s="5">
+        <f t="shared" ref="AC194" si="93">C193-AB194</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="1" t="s">
         <v>225</v>
       </c>
@@ -13628,10 +13851,16 @@
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
       <c r="Y195" s="3"/>
-      <c r="AA195" s="5"/>
-      <c r="AB195" s="5"/>
-    </row>
-    <row r="196" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB195" s="9">
+        <f t="shared" si="92"/>
+        <v>14489</v>
+      </c>
+      <c r="AC195" s="5">
+        <f t="shared" ref="AC195" si="94">AB195-D193</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="6" t="s">
         <v>226</v>
       </c>
@@ -13693,10 +13922,16 @@
       <c r="W196" s="7"/>
       <c r="X196" s="7"/>
       <c r="Y196" s="7"/>
-      <c r="AA196" s="9"/>
-      <c r="AB196" s="9"/>
-    </row>
-    <row r="197" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB196" s="9">
+        <f t="shared" ref="AB196" si="95">SUM(L196:Y196)</f>
+        <v>767126</v>
+      </c>
+      <c r="AC196" s="9">
+        <f t="shared" ref="AC196" si="96">AB196-B196</f>
+        <v>-83497</v>
+      </c>
+    </row>
+    <row r="197" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="1" t="s">
         <v>227</v>
       </c>
@@ -13740,10 +13975,16 @@
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
       <c r="Y197" s="3"/>
-      <c r="AA197" s="5"/>
-      <c r="AB197" s="5"/>
-    </row>
-    <row r="198" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB197" s="9">
+        <f t="shared" ref="AB197:AB198" si="97">SUM(L197:Z197)</f>
+        <v>21326</v>
+      </c>
+      <c r="AC197" s="5">
+        <f t="shared" ref="AC197" si="98">C196-AB197</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="1" t="s">
         <v>228</v>
       </c>
@@ -13787,10 +14028,16 @@
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
       <c r="Y198" s="3"/>
-      <c r="AA198" s="5"/>
-      <c r="AB198" s="5"/>
-    </row>
-    <row r="199" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB198" s="9">
+        <f t="shared" si="97"/>
+        <v>15726</v>
+      </c>
+      <c r="AC198" s="5">
+        <f t="shared" ref="AC198" si="99">AB198-D196</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="6" t="s">
         <v>229</v>
       </c>
@@ -13836,10 +14083,10 @@
       <c r="W199" s="7"/>
       <c r="X199" s="7"/>
       <c r="Y199" s="7"/>
-      <c r="AA199" s="9"/>
       <c r="AB199" s="9"/>
-    </row>
-    <row r="200" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AC199" s="9"/>
+    </row>
+    <row r="200" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="6" t="s">
         <v>230</v>
       </c>
@@ -13901,10 +14148,16 @@
       <c r="W200" s="7"/>
       <c r="X200" s="7"/>
       <c r="Y200" s="7"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-    </row>
-    <row r="201" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB200" s="9">
+        <f t="shared" ref="AB200:AB205" si="100">SUM(L200:Z200)</f>
+        <v>1482889</v>
+      </c>
+      <c r="AC200" s="9">
+        <f>AB200-B200</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="1" t="s">
         <v>231</v>
       </c>
@@ -13948,10 +14201,16 @@
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
       <c r="Y201" s="3"/>
-      <c r="AA201" s="5"/>
-      <c r="AB201" s="5"/>
-    </row>
-    <row r="202" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB201" s="9">
+        <f t="shared" si="100"/>
+        <v>90231</v>
+      </c>
+      <c r="AC201" s="5">
+        <f>C200-AB201</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="1" t="s">
         <v>232</v>
       </c>
@@ -13995,10 +14254,16 @@
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
       <c r="Y202" s="3"/>
-      <c r="AA202" s="5"/>
-      <c r="AB202" s="5"/>
-    </row>
-    <row r="203" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB202" s="9">
+        <f t="shared" si="100"/>
+        <v>63243</v>
+      </c>
+      <c r="AC202" s="5">
+        <f>AB202-D200</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="6" t="s">
         <v>233</v>
       </c>
@@ -14064,10 +14329,16 @@
       <c r="W203" s="7"/>
       <c r="X203" s="7"/>
       <c r="Y203" s="7"/>
-      <c r="AA203" s="9"/>
-      <c r="AB203" s="9"/>
-    </row>
-    <row r="204" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB203" s="9">
+        <f t="shared" si="100"/>
+        <v>953870</v>
+      </c>
+      <c r="AC203" s="9">
+        <f>AB203-B203</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="1" t="s">
         <v>234</v>
       </c>
@@ -14115,10 +14386,16 @@
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
       <c r="Y204" s="3"/>
-      <c r="AA204" s="5"/>
-      <c r="AB204" s="5"/>
-    </row>
-    <row r="205" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB204" s="9">
+        <f t="shared" si="100"/>
+        <v>30108</v>
+      </c>
+      <c r="AC204" s="5">
+        <f>C203-AB204</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="1" t="s">
         <v>235</v>
       </c>
@@ -14166,10 +14443,16 @@
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="3"/>
-      <c r="AA205" s="5"/>
-      <c r="AB205" s="5"/>
-    </row>
-    <row r="206" spans="1:28" s="8" customFormat="1" ht="15">
+      <c r="AB205" s="9">
+        <f t="shared" si="100"/>
+        <v>18909</v>
+      </c>
+      <c r="AC205" s="5">
+        <f>AB205-D203</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="6" t="s">
         <v>236</v>
       </c>
@@ -14225,10 +14508,16 @@
       <c r="W206" s="7"/>
       <c r="X206" s="7"/>
       <c r="Y206" s="7"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-    </row>
-    <row r="207" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB206" s="9">
+        <f t="shared" ref="AB206:AB217" si="101">SUM(L206:Z206)</f>
+        <v>685943</v>
+      </c>
+      <c r="AC206" s="9">
+        <f t="shared" ref="AC206" si="102">AB206-B206</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="1" t="s">
         <v>237</v>
       </c>
@@ -14266,10 +14555,16 @@
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="3"/>
-      <c r="AA207" s="5"/>
-      <c r="AB207" s="5"/>
-    </row>
-    <row r="208" spans="1:28" s="2" customFormat="1" ht="15">
+      <c r="AB207" s="9">
+        <f t="shared" si="101"/>
+        <v>45449</v>
+      </c>
+      <c r="AC207" s="5">
+        <f t="shared" ref="AC207" si="103">C206-AB207</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="1" t="s">
         <v>238</v>
       </c>
@@ -14307,10 +14602,16 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="3"/>
-      <c r="AA208" s="5"/>
-      <c r="AB208" s="5"/>
-    </row>
-    <row r="209" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AB208" s="9">
+        <f t="shared" si="101"/>
+        <v>31437</v>
+      </c>
+      <c r="AC208" s="5">
+        <f t="shared" ref="AC208" si="104">AB208-D206</f>
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="209" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="6" t="s">
         <v>239</v>
       </c>
@@ -14370,10 +14671,16 @@
       <c r="W209" s="7"/>
       <c r="X209" s="7"/>
       <c r="Y209" s="7"/>
-      <c r="AA209" s="9"/>
-      <c r="AB209" s="9"/>
-    </row>
-    <row r="210" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB209" s="9">
+        <f t="shared" si="101"/>
+        <v>775978</v>
+      </c>
+      <c r="AC209" s="9">
+        <f t="shared" ref="AC209" si="105">AB209-B209</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="1" t="s">
         <v>240</v>
       </c>
@@ -14415,10 +14722,16 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="3"/>
-      <c r="AA210" s="5"/>
-      <c r="AB210" s="5"/>
-    </row>
-    <row r="211" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB210" s="9">
+        <f t="shared" si="101"/>
+        <v>26995</v>
+      </c>
+      <c r="AC210" s="5">
+        <f t="shared" ref="AC210" si="106">C209-AB210</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="1" t="s">
         <v>241</v>
       </c>
@@ -14460,10 +14773,16 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="3"/>
-      <c r="AA211" s="5"/>
-      <c r="AB211" s="5"/>
-    </row>
-    <row r="212" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AB211" s="9">
+        <f t="shared" si="101"/>
+        <v>18098</v>
+      </c>
+      <c r="AC211" s="5">
+        <f t="shared" ref="AC211" si="107">AB211-D209</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="6" t="s">
         <v>242</v>
       </c>
@@ -14527,10 +14846,16 @@
       <c r="W212" s="7"/>
       <c r="X212" s="7"/>
       <c r="Y212" s="7"/>
-      <c r="AA212" s="9"/>
-      <c r="AB212" s="9"/>
-    </row>
-    <row r="213" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB212" s="9">
+        <f t="shared" si="101"/>
+        <v>800875</v>
+      </c>
+      <c r="AC212" s="9">
+        <f t="shared" ref="AC212" si="108">AB212-B212</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="1" t="s">
         <v>243</v>
       </c>
@@ -14576,10 +14901,16 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="3"/>
-      <c r="AA213" s="5"/>
-      <c r="AB213" s="5"/>
-    </row>
-    <row r="214" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB213" s="9">
+        <f t="shared" si="101"/>
+        <v>26999</v>
+      </c>
+      <c r="AC213" s="5">
+        <f t="shared" ref="AC213" si="109">C212-AB213</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="1" t="s">
         <v>244</v>
       </c>
@@ -14625,10 +14956,16 @@
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="3"/>
-      <c r="AA214" s="5"/>
-      <c r="AB214" s="5"/>
-    </row>
-    <row r="215" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AB214" s="9">
+        <f t="shared" si="101"/>
+        <v>19113</v>
+      </c>
+      <c r="AC214" s="5">
+        <f t="shared" ref="AC214" si="110">AB214-D212</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="6" t="s">
         <v>245</v>
       </c>
@@ -14688,10 +15025,13 @@
       <c r="W215" s="7"/>
       <c r="X215" s="7"/>
       <c r="Y215" s="7"/>
-      <c r="AA215" s="9"/>
-      <c r="AB215" s="9"/>
-    </row>
-    <row r="216" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB215" s="9">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="AC215" s="9"/>
+    </row>
+    <row r="216" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="1" t="s">
         <v>246</v>
       </c>
@@ -14733,10 +15073,16 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="3"/>
-      <c r="AA216" s="5"/>
-      <c r="AB216" s="5"/>
-    </row>
-    <row r="217" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AB216" s="9">
+        <f t="shared" si="101"/>
+        <v>22717</v>
+      </c>
+      <c r="AC216" s="5">
+        <f t="shared" ref="AC216" si="111">C215-AB216</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="1" t="s">
         <v>247</v>
       </c>
@@ -14778,10 +15124,16 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="3"/>
-      <c r="AA217" s="5"/>
-      <c r="AB217" s="5"/>
-    </row>
-    <row r="218" spans="1:48" s="13" customFormat="1" ht="15">
+      <c r="AB217" s="9">
+        <f t="shared" si="101"/>
+        <v>13537</v>
+      </c>
+      <c r="AC217" s="5">
+        <f t="shared" ref="AC217" si="112">AB217-D215</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:49" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="11" t="s">
         <v>248</v>
       </c>
@@ -14827,110 +15179,110 @@
       <c r="W218" s="12"/>
       <c r="X218" s="12"/>
       <c r="Y218" s="12"/>
-      <c r="AA218" s="14"/>
       <c r="AB218" s="14"/>
-      <c r="AD218" s="14">
-        <f t="shared" ref="AD218:AL218" si="16">SUM(B190:B217)</f>
+      <c r="AC218" s="14"/>
+      <c r="AE218" s="14">
+        <f t="shared" ref="AE218:AM218" si="113">SUM(B190:B217)</f>
         <v>7955715</v>
       </c>
-      <c r="AE218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AF218" s="14">
+        <f t="shared" si="113"/>
         <v>306791</v>
       </c>
-      <c r="AF218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AG218" s="14">
+        <f t="shared" si="113"/>
         <v>215413</v>
       </c>
-      <c r="AG218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AH218" s="14">
+        <f t="shared" si="113"/>
         <v>652622</v>
       </c>
-      <c r="AH218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AI218" s="14">
+        <f t="shared" si="113"/>
         <v>25351</v>
       </c>
-      <c r="AI218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AJ218" s="14">
+        <f t="shared" si="113"/>
         <v>19294</v>
       </c>
-      <c r="AJ218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AK218" s="14">
+        <f t="shared" si="113"/>
         <v>7330167</v>
       </c>
-      <c r="AK218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AL218" s="14">
+        <f t="shared" si="113"/>
         <v>275898</v>
       </c>
-      <c r="AL218" s="14">
-        <f t="shared" si="16"/>
+      <c r="AM218" s="14">
+        <f t="shared" si="113"/>
         <v>182225</v>
       </c>
-      <c r="AN218" s="14">
-        <f t="shared" ref="AN218:AV218" si="17">AD218-B218</f>
+      <c r="AO218" s="14">
+        <f t="shared" ref="AO218:AW218" si="114">AE218-B218</f>
         <v>-10</v>
       </c>
-      <c r="AO218" s="14">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
       <c r="AP218" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="114"/>
+        <v>0</v>
+      </c>
+      <c r="AQ218" s="14">
+        <f t="shared" si="114"/>
         <v>5</v>
       </c>
-      <c r="AQ218" s="14">
-        <f t="shared" si="17"/>
+      <c r="AR218" s="14">
+        <f t="shared" si="114"/>
         <v>-530</v>
       </c>
-      <c r="AR218" s="14">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
       <c r="AS218" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="AT218" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="114"/>
+        <v>0</v>
+      </c>
+      <c r="AU218" s="14">
+        <f t="shared" si="114"/>
         <v>-230097</v>
       </c>
-      <c r="AU218" s="14">
-        <f t="shared" si="17"/>
+      <c r="AV218" s="14">
+        <f t="shared" si="114"/>
         <v>-92304</v>
       </c>
-      <c r="AV218" s="14">
-        <f t="shared" si="17"/>
+      <c r="AW218" s="14">
+        <f t="shared" si="114"/>
         <v>4888</v>
       </c>
     </row>
-    <row r="219" spans="1:48" s="8" customFormat="1" ht="15">
-      <c r="A219" s="23" t="s">
+    <row r="219" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A219" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="B219" s="24">
+      <c r="B219" s="23">
         <v>63221</v>
       </c>
-      <c r="C219" s="25" t="s">
+      <c r="C219" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D219" s="25" t="s">
+      <c r="D219" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E219" s="25" t="s">
+      <c r="E219" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F219" s="25" t="s">
+      <c r="F219" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G219" s="25" t="s">
+      <c r="G219" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="H219" s="25" t="s">
+      <c r="H219" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="I219" s="25" t="s">
+      <c r="I219" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="J219" s="25" t="s">
+      <c r="J219" s="24" t="s">
         <v>36</v>
       </c>
       <c r="K219" s="4"/>
@@ -14948,57 +15300,57 @@
       <c r="W219" s="7"/>
       <c r="X219" s="7"/>
       <c r="Y219" s="7"/>
-      <c r="AA219" s="9"/>
       <c r="AB219" s="9"/>
-    </row>
-    <row r="220" spans="1:48" s="8" customFormat="1" ht="15">
-      <c r="A220" s="23" t="s">
+      <c r="AC219" s="9"/>
+    </row>
+    <row r="220" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A220" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="B220" s="24">
+      <c r="B220" s="23">
         <v>480546</v>
       </c>
-      <c r="C220" s="24">
+      <c r="C220" s="23">
         <v>22847</v>
       </c>
-      <c r="D220" s="24">
+      <c r="D220" s="23">
         <v>17185</v>
       </c>
-      <c r="E220" s="24">
+      <c r="E220" s="23">
         <v>39822</v>
       </c>
-      <c r="F220" s="24">
+      <c r="F220" s="23">
         <v>1923</v>
       </c>
-      <c r="G220" s="24">
+      <c r="G220" s="23">
         <v>1960</v>
       </c>
-      <c r="H220" s="24">
+      <c r="H220" s="23">
         <v>468898</v>
       </c>
-      <c r="I220" s="24">
+      <c r="I220" s="23">
         <v>23300</v>
       </c>
-      <c r="J220" s="24">
+      <c r="J220" s="23">
         <v>17587</v>
       </c>
       <c r="K220" s="3"/>
-      <c r="L220" s="24">
+      <c r="L220" s="23">
         <v>86548</v>
       </c>
-      <c r="M220" s="24">
+      <c r="M220" s="23">
         <v>85989</v>
       </c>
-      <c r="N220" s="24">
+      <c r="N220" s="23">
         <v>67534</v>
       </c>
-      <c r="O220" s="24">
+      <c r="O220" s="23">
         <v>79027</v>
       </c>
-      <c r="P220" s="24">
+      <c r="P220" s="23">
         <v>132358</v>
       </c>
-      <c r="Q220" s="24">
+      <c r="Q220" s="23">
         <v>9223</v>
       </c>
       <c r="R220" s="7"/>
@@ -15009,17 +15361,17 @@
       <c r="W220" s="7"/>
       <c r="X220" s="7"/>
       <c r="Y220" s="7"/>
-      <c r="AA220" s="9">
-        <f t="shared" ref="AA220:AA243" si="18">SUM(L220:Y220)</f>
+      <c r="AB220" s="9">
+        <f t="shared" ref="AB220:AB243" si="115">SUM(L220:Z220)</f>
         <v>460679</v>
       </c>
-      <c r="AB220" s="9">
-        <f>AA220-B220</f>
+      <c r="AC220" s="9">
+        <f t="shared" ref="AC220" si="116">AB220-B220</f>
         <v>-19867</v>
       </c>
     </row>
-    <row r="221" spans="1:48" s="2" customFormat="1" ht="15">
-      <c r="A221" s="26" t="s">
+    <row r="221" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A221" s="25" t="s">
         <v>251</v>
       </c>
       <c r="B221" s="3"/>
@@ -15032,22 +15384,22 @@
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
-      <c r="L221" s="27">
+      <c r="L221" s="26">
         <v>3747</v>
       </c>
-      <c r="M221" s="27">
+      <c r="M221" s="26">
         <v>4660</v>
       </c>
-      <c r="N221" s="27">
+      <c r="N221" s="26">
         <v>2939</v>
       </c>
-      <c r="O221" s="27">
+      <c r="O221" s="26">
         <v>3539</v>
       </c>
-      <c r="P221" s="27">
+      <c r="P221" s="26">
         <v>7721</v>
       </c>
-      <c r="Q221" s="27">
+      <c r="Q221" s="26">
         <v>241</v>
       </c>
       <c r="R221" s="3"/>
@@ -15058,17 +15410,17 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="3"/>
-      <c r="AA221" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB221" s="9">
+        <f t="shared" si="115"/>
         <v>22847</v>
       </c>
-      <c r="AB221" s="5">
-        <f>C220-AA221</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:48" s="2" customFormat="1" ht="15">
-      <c r="A222" s="26" t="s">
+      <c r="AC221" s="5">
+        <f t="shared" ref="AC221" si="117">C220-AB221</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A222" s="25" t="s">
         <v>252</v>
       </c>
       <c r="B222" s="3"/>
@@ -15081,22 +15433,22 @@
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
-      <c r="L222" s="27">
+      <c r="L222" s="26">
         <v>3263</v>
       </c>
-      <c r="M222" s="27">
+      <c r="M222" s="26">
         <v>3497</v>
       </c>
-      <c r="N222" s="27">
+      <c r="N222" s="26">
         <v>2431</v>
       </c>
-      <c r="O222" s="27">
+      <c r="O222" s="26">
         <v>2366</v>
       </c>
-      <c r="P222" s="27">
+      <c r="P222" s="26">
         <v>5615</v>
       </c>
-      <c r="Q222" s="27">
+      <c r="Q222" s="26">
         <v>213</v>
       </c>
       <c r="R222" s="3"/>
@@ -15107,69 +15459,69 @@
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="3"/>
-      <c r="AA222" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB222" s="9">
+        <f t="shared" si="115"/>
         <v>17385</v>
       </c>
-      <c r="AB222" s="5">
-        <f>AA222-D220</f>
+      <c r="AC222" s="5">
+        <f t="shared" ref="AC222" si="118">AB222-D220</f>
         <v>200</v>
       </c>
     </row>
-    <row r="223" spans="1:48" s="8" customFormat="1" ht="15">
-      <c r="A223" s="23" t="s">
+    <row r="223" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A223" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="B223" s="24">
+      <c r="B223" s="23">
         <v>565477</v>
       </c>
-      <c r="C223" s="24">
+      <c r="C223" s="23">
         <v>16344</v>
       </c>
-      <c r="D223" s="24">
+      <c r="D223" s="23">
         <v>14410</v>
       </c>
-      <c r="E223" s="25" t="s">
+      <c r="E223" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F223" s="25" t="s">
+      <c r="F223" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G223" s="25" t="s">
+      <c r="G223" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="H223" s="24">
+      <c r="H223" s="23">
         <v>512727</v>
       </c>
-      <c r="I223" s="24">
+      <c r="I223" s="23">
         <v>19157</v>
       </c>
-      <c r="J223" s="24">
+      <c r="J223" s="23">
         <v>13832</v>
       </c>
       <c r="K223" s="3"/>
-      <c r="L223" s="24">
+      <c r="L223" s="23">
         <v>114632</v>
       </c>
-      <c r="M223" s="24">
+      <c r="M223" s="23">
         <v>28179</v>
       </c>
-      <c r="N223" s="24">
+      <c r="N223" s="23">
         <v>19994</v>
       </c>
-      <c r="O223" s="24">
+      <c r="O223" s="23">
         <v>145476</v>
       </c>
-      <c r="P223" s="24">
+      <c r="P223" s="23">
         <v>72438</v>
       </c>
-      <c r="Q223" s="24">
+      <c r="Q223" s="23">
         <v>61112</v>
       </c>
-      <c r="R223" s="24">
+      <c r="R223" s="23">
         <v>94124</v>
       </c>
-      <c r="S223" s="24">
+      <c r="S223" s="23">
         <v>29522</v>
       </c>
       <c r="T223" s="7"/>
@@ -15178,17 +15530,17 @@
       <c r="W223" s="7"/>
       <c r="X223" s="7"/>
       <c r="Y223" s="7"/>
-      <c r="AA223" s="9">
-        <f t="shared" si="18"/>
+      <c r="AB223" s="9">
+        <f t="shared" si="115"/>
         <v>565477</v>
       </c>
-      <c r="AB223" s="9">
-        <f>AA223-B223</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:48" s="2" customFormat="1" ht="15">
-      <c r="A224" s="26" t="s">
+      <c r="AC223" s="9">
+        <f t="shared" ref="AC223" si="119">AB223-B223</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A224" s="25" t="s">
         <v>254</v>
       </c>
       <c r="B224" s="3"/>
@@ -15201,28 +15553,28 @@
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
-      <c r="L224" s="27">
+      <c r="L224" s="26">
         <v>4078</v>
       </c>
-      <c r="M224" s="27">
+      <c r="M224" s="26">
         <v>1021</v>
       </c>
-      <c r="N224" s="27">
+      <c r="N224" s="26">
         <v>569</v>
       </c>
-      <c r="O224" s="28" t="s">
+      <c r="O224" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="P224" s="27">
+      <c r="P224" s="26">
         <v>3654</v>
       </c>
-      <c r="Q224" s="27">
+      <c r="Q224" s="26">
         <v>2870</v>
       </c>
-      <c r="R224" s="27">
+      <c r="R224" s="26">
         <v>4183</v>
       </c>
-      <c r="S224" s="27">
+      <c r="S224" s="26">
         <v>969</v>
       </c>
       <c r="T224" s="3"/>
@@ -15231,17 +15583,17 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="3"/>
-      <c r="AA224" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB224" s="9">
+        <f t="shared" si="115"/>
         <v>17344</v>
       </c>
-      <c r="AB224" s="5">
-        <f>C223-AA224</f>
+      <c r="AC224" s="5">
+        <f t="shared" ref="AC224" si="120">C223-AB224</f>
         <v>-1000</v>
       </c>
     </row>
-    <row r="225" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A225" s="26" t="s">
+    <row r="225" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A225" s="25" t="s">
         <v>255</v>
       </c>
       <c r="B225" s="3"/>
@@ -15254,28 +15606,28 @@
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
-      <c r="L225" s="27">
+      <c r="L225" s="26">
         <v>1167</v>
       </c>
-      <c r="M225" s="27">
+      <c r="M225" s="26">
         <v>320</v>
       </c>
-      <c r="N225" s="27">
+      <c r="N225" s="26">
         <v>860</v>
       </c>
-      <c r="O225" s="27">
+      <c r="O225" s="26">
         <v>2011</v>
       </c>
-      <c r="P225" s="27">
+      <c r="P225" s="26">
         <v>8150</v>
       </c>
-      <c r="Q225" s="27">
+      <c r="Q225" s="26">
         <v>672</v>
       </c>
-      <c r="R225" s="27">
+      <c r="R225" s="26">
         <v>360</v>
       </c>
-      <c r="S225" s="27">
+      <c r="S225" s="26">
         <v>870</v>
       </c>
       <c r="T225" s="3"/>
@@ -15284,60 +15636,60 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="3"/>
-      <c r="AA225" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB225" s="9">
+        <f t="shared" si="115"/>
         <v>14410</v>
       </c>
-      <c r="AB225" s="5">
-        <f>AA225-D223</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:28" s="8" customFormat="1" ht="15">
-      <c r="A226" s="23" t="s">
+      <c r="AC225" s="5">
+        <f t="shared" ref="AC225" si="121">AB225-D223</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A226" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="B226" s="24">
+      <c r="B226" s="23">
         <v>444704</v>
       </c>
-      <c r="C226" s="24">
+      <c r="C226" s="23">
         <v>20131</v>
       </c>
-      <c r="D226" s="24">
+      <c r="D226" s="23">
         <v>14077</v>
       </c>
-      <c r="E226" s="24">
+      <c r="E226" s="23">
         <v>58190</v>
       </c>
-      <c r="F226" s="24">
+      <c r="F226" s="23">
         <v>2112</v>
       </c>
-      <c r="G226" s="24">
+      <c r="G226" s="23">
         <v>1976</v>
       </c>
-      <c r="H226" s="24">
+      <c r="H226" s="23">
         <v>427879</v>
       </c>
-      <c r="I226" s="24">
+      <c r="I226" s="23">
         <v>20377</v>
       </c>
-      <c r="J226" s="24">
+      <c r="J226" s="23">
         <v>17073</v>
       </c>
       <c r="K226" s="3"/>
-      <c r="L226" s="24">
+      <c r="L226" s="23">
         <v>146915</v>
       </c>
-      <c r="M226" s="24">
+      <c r="M226" s="23">
         <v>128600</v>
       </c>
-      <c r="N226" s="24">
+      <c r="N226" s="23">
         <v>64470</v>
       </c>
-      <c r="O226" s="24">
+      <c r="O226" s="23">
         <v>49026</v>
       </c>
-      <c r="P226" s="24">
+      <c r="P226" s="23">
         <v>55693</v>
       </c>
       <c r="Q226" s="7"/>
@@ -15349,17 +15701,17 @@
       <c r="W226" s="7"/>
       <c r="X226" s="7"/>
       <c r="Y226" s="7"/>
-      <c r="AA226" s="9">
-        <f t="shared" si="18"/>
+      <c r="AB226" s="9">
+        <f t="shared" si="115"/>
         <v>444704</v>
       </c>
-      <c r="AB226" s="9">
-        <f>AA226-B226</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A227" s="26" t="s">
+      <c r="AC226" s="9">
+        <f t="shared" ref="AC226" si="122">AB226-B226</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A227" s="25" t="s">
         <v>257</v>
       </c>
       <c r="B227" s="3"/>
@@ -15372,19 +15724,19 @@
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
-      <c r="L227" s="27">
+      <c r="L227" s="26">
         <v>5971</v>
       </c>
-      <c r="M227" s="27">
+      <c r="M227" s="26">
         <v>5459</v>
       </c>
-      <c r="N227" s="27">
+      <c r="N227" s="26">
         <v>3096</v>
       </c>
-      <c r="O227" s="27">
+      <c r="O227" s="26">
         <v>2340</v>
       </c>
-      <c r="P227" s="27">
+      <c r="P227" s="26">
         <v>3265</v>
       </c>
       <c r="Q227" s="3"/>
@@ -15396,17 +15748,17 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="3"/>
-      <c r="AA227" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB227" s="9">
+        <f t="shared" si="115"/>
         <v>20131</v>
       </c>
-      <c r="AB227" s="5">
-        <f>C226-AA227</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A228" s="26" t="s">
+      <c r="AC227" s="5">
+        <f t="shared" ref="AC227" si="123">C226-AB227</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A228" s="25" t="s">
         <v>258</v>
       </c>
       <c r="B228" s="3"/>
@@ -15419,19 +15771,19 @@
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
-      <c r="L228" s="27">
+      <c r="L228" s="26">
         <v>4375</v>
       </c>
-      <c r="M228" s="27">
+      <c r="M228" s="26">
         <v>3994</v>
       </c>
-      <c r="N228" s="27">
+      <c r="N228" s="26">
         <v>1879</v>
       </c>
-      <c r="O228" s="27">
+      <c r="O228" s="26">
         <v>1366</v>
       </c>
-      <c r="P228" s="27">
+      <c r="P228" s="26">
         <v>2463</v>
       </c>
       <c r="Q228" s="3"/>
@@ -15443,72 +15795,72 @@
       <c r="W228" s="3"/>
       <c r="X228" s="3"/>
       <c r="Y228" s="3"/>
-      <c r="AA228" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB228" s="9">
+        <f t="shared" si="115"/>
         <v>14077</v>
       </c>
-      <c r="AB228" s="5">
-        <f>AA228-D226</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:28" s="8" customFormat="1" ht="15">
-      <c r="A229" s="23" t="s">
+      <c r="AC228" s="5">
+        <f t="shared" ref="AC228" si="124">AB228-D226</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A229" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="B229" s="24">
+      <c r="B229" s="23">
         <v>119744</v>
       </c>
-      <c r="C229" s="24">
+      <c r="C229" s="23">
         <v>3311</v>
       </c>
-      <c r="D229" s="24">
+      <c r="D229" s="23">
         <v>1769</v>
       </c>
-      <c r="E229" s="25" t="s">
+      <c r="E229" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F229" s="25" t="s">
+      <c r="F229" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G229" s="25" t="s">
+      <c r="G229" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="H229" s="24">
+      <c r="H229" s="23">
         <v>102857</v>
       </c>
-      <c r="I229" s="24">
+      <c r="I229" s="23">
         <v>2962</v>
       </c>
-      <c r="J229" s="24">
+      <c r="J229" s="23">
         <v>1840</v>
       </c>
       <c r="K229" s="3"/>
-      <c r="L229" s="24">
+      <c r="L229" s="23">
         <v>14606</v>
       </c>
-      <c r="M229" s="24">
+      <c r="M229" s="23">
         <v>10350</v>
       </c>
-      <c r="N229" s="24">
+      <c r="N229" s="23">
         <v>5399</v>
       </c>
-      <c r="O229" s="24">
+      <c r="O229" s="23">
         <v>675</v>
       </c>
-      <c r="P229" s="24">
+      <c r="P229" s="23">
         <v>9561</v>
       </c>
-      <c r="Q229" s="24">
+      <c r="Q229" s="23">
         <v>4040</v>
       </c>
-      <c r="R229" s="24">
+      <c r="R229" s="23">
         <v>6644</v>
       </c>
-      <c r="S229" s="24">
+      <c r="S229" s="23">
         <v>6460</v>
       </c>
-      <c r="T229" s="24">
+      <c r="T229" s="23">
         <v>62009</v>
       </c>
       <c r="U229" s="7"/>
@@ -15516,17 +15868,17 @@
       <c r="W229" s="7"/>
       <c r="X229" s="7"/>
       <c r="Y229" s="7"/>
-      <c r="AA229" s="9">
-        <f t="shared" si="18"/>
+      <c r="AB229" s="9">
+        <f t="shared" si="115"/>
         <v>119744</v>
       </c>
-      <c r="AB229" s="9">
-        <f>AA229-B229</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A230" s="26" t="s">
+      <c r="AC229" s="9">
+        <f t="shared" ref="AC229" si="125">AB229-B229</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A230" s="25" t="s">
         <v>260</v>
       </c>
       <c r="B230" s="3"/>
@@ -15539,31 +15891,31 @@
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
-      <c r="L230" s="27">
+      <c r="L230" s="26">
         <v>538</v>
       </c>
-      <c r="M230" s="28" t="s">
+      <c r="M230" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="N230" s="27">
+      <c r="N230" s="26">
         <v>24</v>
       </c>
-      <c r="O230" s="27">
+      <c r="O230" s="26">
         <v>26</v>
       </c>
-      <c r="P230" s="27">
+      <c r="P230" s="26">
         <v>192</v>
       </c>
-      <c r="Q230" s="27">
+      <c r="Q230" s="26">
         <v>122</v>
       </c>
-      <c r="R230" s="27">
+      <c r="R230" s="26">
         <v>197</v>
       </c>
-      <c r="S230" s="27">
+      <c r="S230" s="26">
         <v>284</v>
       </c>
-      <c r="T230" s="27">
+      <c r="T230" s="26">
         <v>1928</v>
       </c>
       <c r="U230" s="3"/>
@@ -15571,17 +15923,17 @@
       <c r="W230" s="3"/>
       <c r="X230" s="3"/>
       <c r="Y230" s="3"/>
-      <c r="AA230" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB230" s="9">
+        <f t="shared" si="115"/>
         <v>3311</v>
       </c>
-      <c r="AB230" s="5">
-        <f>C229-AA230</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A231" s="26" t="s">
+      <c r="AC230" s="5">
+        <f t="shared" ref="AC230" si="126">C229-AB230</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A231" s="25" t="s">
         <v>261</v>
       </c>
       <c r="B231" s="3"/>
@@ -15594,31 +15946,31 @@
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
-      <c r="L231" s="27">
+      <c r="L231" s="26">
         <v>222</v>
       </c>
-      <c r="M231" s="28" t="s">
+      <c r="M231" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="N231" s="27">
+      <c r="N231" s="26">
         <v>26</v>
       </c>
-      <c r="O231" s="27">
+      <c r="O231" s="26">
         <v>14</v>
       </c>
-      <c r="P231" s="27">
+      <c r="P231" s="26">
         <v>179</v>
       </c>
-      <c r="Q231" s="27">
+      <c r="Q231" s="26">
         <v>164</v>
       </c>
-      <c r="R231" s="27">
+      <c r="R231" s="26">
         <v>86</v>
       </c>
-      <c r="S231" s="27">
+      <c r="S231" s="26">
         <v>128</v>
       </c>
-      <c r="T231" s="27">
+      <c r="T231" s="26">
         <v>950</v>
       </c>
       <c r="U231" s="3"/>
@@ -15626,92 +15978,92 @@
       <c r="W231" s="3"/>
       <c r="X231" s="3"/>
       <c r="Y231" s="3"/>
-      <c r="AA231" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB231" s="9">
+        <f t="shared" si="115"/>
         <v>1769</v>
       </c>
-      <c r="AB231" s="5">
-        <f>AA231-D229</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:28" s="8" customFormat="1" ht="15">
-      <c r="A232" s="23" t="s">
+      <c r="AC231" s="5">
+        <f t="shared" ref="AC231" si="127">AB231-D229</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A232" s="22" t="s">
         <v>262</v>
       </c>
-      <c r="B232" s="24">
+      <c r="B232" s="23">
         <v>1411475</v>
       </c>
-      <c r="C232" s="24">
+      <c r="C232" s="23">
         <v>73772</v>
       </c>
-      <c r="D232" s="24">
+      <c r="D232" s="23">
         <v>58271</v>
       </c>
-      <c r="E232" s="24">
+      <c r="E232" s="23">
         <v>99804</v>
       </c>
-      <c r="F232" s="24">
+      <c r="F232" s="23">
         <v>2262</v>
       </c>
-      <c r="G232" s="24">
+      <c r="G232" s="23">
         <v>2550</v>
       </c>
-      <c r="H232" s="24">
+      <c r="H232" s="23">
         <v>1393432</v>
       </c>
-      <c r="I232" s="24">
+      <c r="I232" s="23">
         <v>76165</v>
       </c>
-      <c r="J232" s="24">
+      <c r="J232" s="23">
         <v>61052</v>
       </c>
       <c r="K232" s="3"/>
-      <c r="L232" s="24">
+      <c r="L232" s="23">
         <v>126707</v>
       </c>
-      <c r="M232" s="24">
+      <c r="M232" s="23">
         <v>31452</v>
       </c>
-      <c r="N232" s="24">
+      <c r="N232" s="23">
         <v>274400</v>
       </c>
-      <c r="O232" s="24">
+      <c r="O232" s="23">
         <v>266295</v>
       </c>
-      <c r="P232" s="24">
+      <c r="P232" s="23">
         <v>8544</v>
       </c>
-      <c r="Q232" s="24">
+      <c r="Q232" s="23">
         <v>148902</v>
       </c>
-      <c r="R232" s="24">
+      <c r="R232" s="23">
         <v>71444</v>
       </c>
-      <c r="S232" s="24">
+      <c r="S232" s="23">
         <v>158211</v>
       </c>
-      <c r="T232" s="24">
+      <c r="T232" s="23">
         <v>124624</v>
       </c>
-      <c r="U232" s="24">
+      <c r="U232" s="23">
         <v>200886</v>
       </c>
       <c r="V232" s="7"/>
       <c r="W232" s="7"/>
       <c r="X232" s="7"/>
       <c r="Y232" s="7"/>
-      <c r="AA232" s="9">
-        <f t="shared" si="18"/>
+      <c r="AB232" s="9">
+        <f t="shared" si="115"/>
         <v>1411465</v>
       </c>
-      <c r="AB232" s="9">
-        <f>AA232-B232</f>
+      <c r="AC232" s="9">
+        <f t="shared" ref="AC232" si="128">AB232-B232</f>
         <v>-10</v>
       </c>
     </row>
-    <row r="233" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A233" s="26" t="s">
+    <row r="233" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A233" s="25" t="s">
         <v>263</v>
       </c>
       <c r="B233" s="3"/>
@@ -15724,51 +16076,51 @@
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
-      <c r="L233" s="27">
+      <c r="L233" s="26">
         <v>5642</v>
       </c>
-      <c r="M233" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="N233" s="27">
+      <c r="M233" s="31">
+        <v>1305</v>
+      </c>
+      <c r="N233" s="26">
         <v>16521</v>
       </c>
-      <c r="O233" s="27">
+      <c r="O233" s="26">
         <v>16788</v>
       </c>
-      <c r="P233" s="27">
+      <c r="P233" s="26">
         <v>334</v>
       </c>
-      <c r="Q233" s="27">
+      <c r="Q233" s="26">
         <v>7099</v>
       </c>
-      <c r="R233" s="27">
+      <c r="R233" s="26">
         <v>3483</v>
       </c>
-      <c r="S233" s="27">
+      <c r="S233" s="26">
         <v>7973</v>
       </c>
-      <c r="T233" s="27">
+      <c r="T233" s="26">
         <v>4673</v>
       </c>
-      <c r="U233" s="27">
+      <c r="U233" s="26">
         <v>9954</v>
       </c>
       <c r="V233" s="3"/>
       <c r="W233" s="3"/>
       <c r="X233" s="3"/>
       <c r="Y233" s="3"/>
-      <c r="AA233" s="5">
-        <f t="shared" si="18"/>
-        <v>72467</v>
-      </c>
-      <c r="AB233" s="5">
-        <f>C232-AA233</f>
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="234" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A234" s="26" t="s">
+      <c r="AB233" s="9">
+        <f t="shared" si="115"/>
+        <v>73772</v>
+      </c>
+      <c r="AC233" s="5">
+        <f t="shared" ref="AC233" si="129">C232-AB233</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A234" s="25" t="s">
         <v>264</v>
       </c>
       <c r="B234" s="3"/>
@@ -15781,97 +16133,97 @@
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
-      <c r="L234" s="27">
+      <c r="L234" s="26">
         <v>4568</v>
       </c>
-      <c r="M234" s="27">
+      <c r="M234" s="26">
         <v>1200</v>
       </c>
-      <c r="N234" s="27">
+      <c r="N234" s="26">
         <v>12987</v>
       </c>
-      <c r="O234" s="27">
+      <c r="O234" s="26">
         <v>12737</v>
       </c>
-      <c r="P234" s="27">
+      <c r="P234" s="26">
         <v>336</v>
       </c>
-      <c r="Q234" s="27">
+      <c r="Q234" s="26">
         <v>4727</v>
       </c>
-      <c r="R234" s="27">
+      <c r="R234" s="26">
         <v>3333</v>
       </c>
-      <c r="S234" s="27">
+      <c r="S234" s="26">
         <v>5279</v>
       </c>
-      <c r="T234" s="27">
+      <c r="T234" s="26">
         <v>4518</v>
       </c>
-      <c r="U234" s="27">
+      <c r="U234" s="26">
         <v>8586</v>
       </c>
       <c r="V234" s="3"/>
       <c r="W234" s="3"/>
       <c r="X234" s="3"/>
       <c r="Y234" s="3"/>
-      <c r="AA234" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB234" s="9">
+        <f t="shared" si="115"/>
         <v>58271</v>
       </c>
-      <c r="AB234" s="5">
-        <f>AA234-D232</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:28" s="8" customFormat="1" ht="15">
-      <c r="A235" s="23" t="s">
+      <c r="AC234" s="5">
+        <f t="shared" ref="AC234" si="130">AB234-D232</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A235" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="B235" s="24">
+      <c r="B235" s="23">
         <v>1422681</v>
       </c>
-      <c r="C235" s="24">
+      <c r="C235" s="23">
         <v>67604</v>
       </c>
-      <c r="D235" s="24">
+      <c r="D235" s="23">
         <v>38492</v>
       </c>
-      <c r="E235" s="25" t="s">
+      <c r="E235" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F235" s="25" t="s">
+      <c r="F235" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G235" s="25" t="s">
+      <c r="G235" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="H235" s="24">
+      <c r="H235" s="23">
         <v>1326265</v>
       </c>
-      <c r="I235" s="24">
+      <c r="I235" s="23">
         <v>63453</v>
       </c>
-      <c r="J235" s="24">
+      <c r="J235" s="23">
         <v>35157</v>
       </c>
       <c r="K235" s="3"/>
-      <c r="L235" s="24">
+      <c r="L235" s="23">
         <v>214609</v>
       </c>
-      <c r="M235" s="24">
+      <c r="M235" s="23">
         <v>318785</v>
       </c>
-      <c r="N235" s="24">
+      <c r="N235" s="23">
         <v>366358</v>
       </c>
-      <c r="O235" s="24">
+      <c r="O235" s="23">
         <v>167569</v>
       </c>
-      <c r="P235" s="24">
+      <c r="P235" s="23">
         <v>174104</v>
       </c>
-      <c r="Q235" s="24">
+      <c r="Q235" s="23">
         <v>121338</v>
       </c>
       <c r="R235" s="7"/>
@@ -15882,17 +16234,17 @@
       <c r="W235" s="7"/>
       <c r="X235" s="7"/>
       <c r="Y235" s="7"/>
-      <c r="AA235" s="9">
-        <f t="shared" si="18"/>
+      <c r="AB235" s="9">
+        <f t="shared" si="115"/>
         <v>1362763</v>
       </c>
-      <c r="AB235" s="9">
-        <f>AA235-B235</f>
+      <c r="AC235" s="9">
+        <f t="shared" ref="AC235" si="131">AB235-B235</f>
         <v>-59918</v>
       </c>
     </row>
-    <row r="236" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A236" s="26" t="s">
+    <row r="236" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A236" s="25" t="s">
         <v>266</v>
       </c>
       <c r="B236" s="3"/>
@@ -15905,22 +16257,22 @@
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
-      <c r="L236" s="27">
+      <c r="L236" s="26">
         <v>11309</v>
       </c>
-      <c r="M236" s="27">
+      <c r="M236" s="26">
         <v>17664</v>
       </c>
-      <c r="N236" s="27">
+      <c r="N236" s="26">
         <v>18927</v>
       </c>
-      <c r="O236" s="27">
+      <c r="O236" s="26">
         <v>7219</v>
       </c>
-      <c r="P236" s="27">
+      <c r="P236" s="26">
         <v>6594</v>
       </c>
-      <c r="Q236" s="27">
+      <c r="Q236" s="26">
         <v>5891</v>
       </c>
       <c r="R236" s="3"/>
@@ -15931,17 +16283,17 @@
       <c r="W236" s="3"/>
       <c r="X236" s="3"/>
       <c r="Y236" s="3"/>
-      <c r="AA236" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB236" s="9">
+        <f t="shared" si="115"/>
         <v>67604</v>
       </c>
-      <c r="AB236" s="5">
-        <f>C235-AA236</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A237" s="26" t="s">
+      <c r="AC236" s="5">
+        <f t="shared" ref="AC236" si="132">C235-AB236</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A237" s="25" t="s">
         <v>267</v>
       </c>
       <c r="B237" s="3"/>
@@ -15954,22 +16306,22 @@
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
-      <c r="L237" s="27">
+      <c r="L237" s="26">
         <v>8440</v>
       </c>
-      <c r="M237" s="27">
+      <c r="M237" s="26">
         <v>8247</v>
       </c>
-      <c r="N237" s="27">
+      <c r="N237" s="26">
         <v>9690</v>
       </c>
-      <c r="O237" s="27">
+      <c r="O237" s="26">
         <v>4559</v>
       </c>
-      <c r="P237" s="27">
+      <c r="P237" s="26">
         <v>3095</v>
       </c>
-      <c r="Q237" s="27">
+      <c r="Q237" s="26">
         <v>4461</v>
       </c>
       <c r="R237" s="3"/>
@@ -15980,60 +16332,60 @@
       <c r="W237" s="3"/>
       <c r="X237" s="3"/>
       <c r="Y237" s="3"/>
-      <c r="AA237" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB237" s="9">
+        <f t="shared" si="115"/>
         <v>38492</v>
       </c>
-      <c r="AB237" s="5">
-        <f>AA237-D235</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="1:28" s="8" customFormat="1" ht="15">
-      <c r="A238" s="23" t="s">
+      <c r="AC237" s="5">
+        <f t="shared" ref="AC237" si="133">AB237-D235</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A238" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="B238" s="24">
+      <c r="B238" s="23">
         <v>257753</v>
       </c>
-      <c r="C238" s="24">
+      <c r="C238" s="23">
         <v>8202</v>
       </c>
-      <c r="D238" s="24">
+      <c r="D238" s="23">
         <v>5111</v>
       </c>
-      <c r="E238" s="25" t="s">
+      <c r="E238" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F238" s="25" t="s">
+      <c r="F238" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G238" s="25" t="s">
+      <c r="G238" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="H238" s="24">
+      <c r="H238" s="23">
         <v>255661</v>
       </c>
-      <c r="I238" s="24">
+      <c r="I238" s="23">
         <v>6924</v>
       </c>
-      <c r="J238" s="24">
+      <c r="J238" s="23">
         <v>6467</v>
       </c>
       <c r="K238" s="3"/>
-      <c r="L238" s="24">
+      <c r="L238" s="23">
         <v>150924</v>
       </c>
-      <c r="M238" s="24">
+      <c r="M238" s="23">
         <v>12985</v>
       </c>
-      <c r="N238" s="24">
+      <c r="N238" s="23">
         <v>72855</v>
       </c>
-      <c r="O238" s="24">
+      <c r="O238" s="23">
         <v>6102</v>
       </c>
-      <c r="P238" s="24">
+      <c r="P238" s="23">
         <v>14887</v>
       </c>
       <c r="Q238" s="7"/>
@@ -16045,17 +16397,17 @@
       <c r="W238" s="7"/>
       <c r="X238" s="7"/>
       <c r="Y238" s="7"/>
-      <c r="AA238" s="9">
-        <f t="shared" si="18"/>
+      <c r="AB238" s="9">
+        <f t="shared" si="115"/>
         <v>257753</v>
       </c>
-      <c r="AB238" s="9">
-        <f>AA238-B238</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A239" s="26" t="s">
+      <c r="AC238" s="9">
+        <f t="shared" ref="AC238" si="134">AB238-B238</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A239" s="25" t="s">
         <v>269</v>
       </c>
       <c r="B239" s="3"/>
@@ -16068,19 +16420,19 @@
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
-      <c r="L239" s="27">
+      <c r="L239" s="26">
         <v>4963</v>
       </c>
-      <c r="M239" s="27">
+      <c r="M239" s="26">
         <v>319</v>
       </c>
-      <c r="N239" s="27">
+      <c r="N239" s="26">
         <v>2142</v>
       </c>
-      <c r="O239" s="27">
+      <c r="O239" s="26">
         <v>135</v>
       </c>
-      <c r="P239" s="27">
+      <c r="P239" s="26">
         <v>643</v>
       </c>
       <c r="Q239" s="3"/>
@@ -16092,17 +16444,17 @@
       <c r="W239" s="3"/>
       <c r="X239" s="3"/>
       <c r="Y239" s="3"/>
-      <c r="AA239" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB239" s="9">
+        <f t="shared" si="115"/>
         <v>8202</v>
       </c>
-      <c r="AB239" s="5">
-        <f>C238-AA239</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:28" s="2" customFormat="1" ht="15">
-      <c r="A240" s="26" t="s">
+      <c r="AC239" s="5">
+        <f t="shared" ref="AC239" si="135">C238-AB239</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A240" s="25" t="s">
         <v>270</v>
       </c>
       <c r="B240" s="3"/>
@@ -16115,19 +16467,19 @@
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
-      <c r="L240" s="27">
+      <c r="L240" s="26">
         <v>3105</v>
       </c>
-      <c r="M240" s="27">
+      <c r="M240" s="26">
         <v>265</v>
       </c>
-      <c r="N240" s="27">
+      <c r="N240" s="26">
         <v>1217</v>
       </c>
-      <c r="O240" s="27">
+      <c r="O240" s="26">
         <v>83</v>
       </c>
-      <c r="P240" s="27">
+      <c r="P240" s="26">
         <v>441</v>
       </c>
       <c r="Q240" s="3"/>
@@ -16139,54 +16491,54 @@
       <c r="W240" s="3"/>
       <c r="X240" s="3"/>
       <c r="Y240" s="3"/>
-      <c r="AA240" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB240" s="9">
+        <f t="shared" si="115"/>
         <v>5111</v>
       </c>
-      <c r="AB240" s="5">
-        <f>AA240-D238</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:48" s="8" customFormat="1" ht="15">
-      <c r="A241" s="23" t="s">
+      <c r="AC240" s="5">
+        <f t="shared" ref="AC240" si="136">AB240-D238</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A241" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="B241" s="24">
+      <c r="B241" s="23">
         <v>17051</v>
       </c>
-      <c r="C241" s="24">
+      <c r="C241" s="23">
         <v>342</v>
       </c>
-      <c r="D241" s="24">
+      <c r="D241" s="23">
         <v>335</v>
       </c>
-      <c r="E241" s="25" t="s">
+      <c r="E241" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F241" s="25" t="s">
+      <c r="F241" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G241" s="25" t="s">
+      <c r="G241" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="H241" s="24">
+      <c r="H241" s="23">
         <v>15244</v>
       </c>
-      <c r="I241" s="24">
+      <c r="I241" s="23">
         <v>356</v>
       </c>
-      <c r="J241" s="24">
+      <c r="J241" s="23">
         <v>241</v>
       </c>
       <c r="K241" s="3"/>
-      <c r="L241" s="24">
+      <c r="L241" s="23">
         <v>7546</v>
       </c>
-      <c r="M241" s="24">
+      <c r="M241" s="23">
         <v>4156</v>
       </c>
-      <c r="N241" s="24">
+      <c r="N241" s="23">
         <v>5349</v>
       </c>
       <c r="O241" s="7"/>
@@ -16200,17 +16552,17 @@
       <c r="W241" s="7"/>
       <c r="X241" s="7"/>
       <c r="Y241" s="7"/>
-      <c r="AA241" s="9">
-        <f t="shared" si="18"/>
+      <c r="AB241" s="9">
+        <f t="shared" si="115"/>
         <v>17051</v>
       </c>
-      <c r="AB241" s="9">
-        <f>AA241-B241</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="1:48" s="2" customFormat="1" ht="15">
-      <c r="A242" s="26" t="s">
+      <c r="AC241" s="9">
+        <f t="shared" ref="AC241" si="137">AB241-B241</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A242" s="25" t="s">
         <v>272</v>
       </c>
       <c r="B242" s="3"/>
@@ -16223,13 +16575,13 @@
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
-      <c r="L242" s="27">
+      <c r="L242" s="26">
         <v>163</v>
       </c>
-      <c r="M242" s="27">
+      <c r="M242" s="26">
         <v>67</v>
       </c>
-      <c r="N242" s="27">
+      <c r="N242" s="26">
         <v>112</v>
       </c>
       <c r="O242" s="3"/>
@@ -16243,17 +16595,17 @@
       <c r="W242" s="3"/>
       <c r="X242" s="3"/>
       <c r="Y242" s="3"/>
-      <c r="AA242" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB242" s="9">
+        <f t="shared" si="115"/>
         <v>342</v>
       </c>
-      <c r="AB242" s="5">
-        <f>C241-AA242</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:48" s="2" customFormat="1" ht="15">
-      <c r="A243" s="26" t="s">
+      <c r="AC242" s="5">
+        <f t="shared" ref="AC242" si="138">C241-AB242</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A243" s="25" t="s">
         <v>273</v>
       </c>
       <c r="B243" s="3"/>
@@ -16266,13 +16618,13 @@
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
-      <c r="L243" s="27">
+      <c r="L243" s="26">
         <v>98</v>
       </c>
-      <c r="M243" s="27">
+      <c r="M243" s="26">
         <v>16</v>
       </c>
-      <c r="N243" s="27">
+      <c r="N243" s="26">
         <v>70</v>
       </c>
       <c r="O243" s="3"/>
@@ -16286,44 +16638,44 @@
       <c r="W243" s="3"/>
       <c r="X243" s="3"/>
       <c r="Y243" s="3"/>
-      <c r="AA243" s="5">
-        <f t="shared" si="18"/>
+      <c r="AB243" s="9">
+        <f t="shared" si="115"/>
         <v>184</v>
       </c>
-      <c r="AB243" s="5">
-        <f>AA243-D241</f>
+      <c r="AC243" s="5">
+        <f t="shared" ref="AC243" si="139">AB243-D241</f>
         <v>-151</v>
       </c>
     </row>
-    <row r="244" spans="1:48" s="13" customFormat="1" ht="15">
-      <c r="A244" s="29" t="s">
+    <row r="244" spans="1:49" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A244" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="B244" s="30">
+      <c r="B244" s="29">
         <v>4782652</v>
       </c>
-      <c r="C244" s="30">
+      <c r="C244" s="29">
         <v>209242</v>
       </c>
-      <c r="D244" s="30">
+      <c r="D244" s="29">
         <v>142871</v>
       </c>
-      <c r="E244" s="30">
+      <c r="E244" s="29">
         <v>197816</v>
       </c>
-      <c r="F244" s="30">
+      <c r="F244" s="29">
         <v>6297</v>
       </c>
-      <c r="G244" s="30">
+      <c r="G244" s="29">
         <v>6486</v>
       </c>
-      <c r="H244" s="30">
+      <c r="H244" s="29">
         <v>4545114</v>
       </c>
-      <c r="I244" s="30">
+      <c r="I244" s="29">
         <v>201988</v>
       </c>
-      <c r="J244" s="30">
+      <c r="J244" s="29">
         <v>148026</v>
       </c>
       <c r="K244" s="4"/>
@@ -16341,84 +16693,84 @@
       <c r="W244" s="12"/>
       <c r="X244" s="12"/>
       <c r="Y244" s="12"/>
-      <c r="AA244" s="14"/>
       <c r="AB244" s="14"/>
-      <c r="AD244" s="14">
-        <f t="shared" ref="AD244:AL244" si="19">SUM(B219:B243)</f>
+      <c r="AC244" s="14"/>
+      <c r="AE244" s="14">
+        <f t="shared" ref="AE244:AM244" si="140">SUM(B219:B243)</f>
         <v>4782652</v>
       </c>
-      <c r="AE244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AF244" s="14">
+        <f t="shared" si="140"/>
         <v>212553</v>
       </c>
-      <c r="AF244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AG244" s="14">
+        <f t="shared" si="140"/>
         <v>149650</v>
       </c>
-      <c r="AG244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AH244" s="14">
+        <f t="shared" si="140"/>
         <v>197816</v>
       </c>
-      <c r="AH244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AI244" s="14">
+        <f t="shared" si="140"/>
         <v>6297</v>
       </c>
-      <c r="AI244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AJ244" s="14">
+        <f t="shared" si="140"/>
         <v>6486</v>
       </c>
-      <c r="AJ244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AK244" s="14">
+        <f t="shared" si="140"/>
         <v>4502963</v>
       </c>
-      <c r="AK244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AL244" s="14">
+        <f t="shared" si="140"/>
         <v>212694</v>
       </c>
-      <c r="AL244" s="14">
-        <f t="shared" si="19"/>
+      <c r="AM244" s="14">
+        <f t="shared" si="140"/>
         <v>153249</v>
       </c>
-      <c r="AN244" s="14">
-        <f t="shared" ref="AN244:AV244" si="20">AD244-B244</f>
-        <v>0</v>
-      </c>
       <c r="AO244" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="AO244:AW244" si="141">AE244-B244</f>
+        <v>0</v>
+      </c>
+      <c r="AP244" s="14">
+        <f t="shared" si="141"/>
         <v>3311</v>
       </c>
-      <c r="AP244" s="14">
-        <f t="shared" si="20"/>
+      <c r="AQ244" s="14">
+        <f t="shared" si="141"/>
         <v>6779</v>
       </c>
-      <c r="AQ244" s="14">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="AR244" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="AS244" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="AT244" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="AU244" s="14">
+        <f t="shared" si="141"/>
         <v>-42151</v>
       </c>
-      <c r="AU244" s="14">
-        <f t="shared" si="20"/>
+      <c r="AV244" s="14">
+        <f t="shared" si="141"/>
         <v>10706</v>
       </c>
-      <c r="AV244" s="14">
-        <f t="shared" si="20"/>
+      <c r="AW244" s="14">
+        <f t="shared" si="141"/>
         <v>5223</v>
       </c>
     </row>
-    <row r="245" spans="1:48" s="8" customFormat="1" ht="15">
+    <row r="245" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="6" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="B245" s="7">
         <v>519784</v>
@@ -16462,13 +16814,14 @@
       <c r="W245" s="7"/>
       <c r="X245" s="7"/>
       <c r="Y245" s="7"/>
-      <c r="Z245"/>
-      <c r="AA245" s="9"/>
+      <c r="Z245" s="33"/>
+      <c r="AA245" s="33"/>
       <c r="AB245" s="9"/>
-    </row>
-    <row r="246" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC245" s="9"/>
+    </row>
+    <row r="246" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B246" s="7">
         <v>700000</v>
@@ -16512,13 +16865,14 @@
       <c r="W246" s="7"/>
       <c r="X246" s="7"/>
       <c r="Y246" s="7"/>
-      <c r="Z246"/>
-      <c r="AA246" s="9"/>
+      <c r="Z246" s="33"/>
+      <c r="AA246" s="33"/>
       <c r="AB246" s="9"/>
-    </row>
-    <row r="247" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC246" s="9"/>
+    </row>
+    <row r="247" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B247" s="7">
         <v>712420</v>
@@ -16570,19 +16924,20 @@
       <c r="W247" s="7"/>
       <c r="X247" s="7"/>
       <c r="Y247" s="7"/>
-      <c r="Z247"/>
-      <c r="AA247" s="9">
-        <f t="shared" ref="AA247:AA267" si="21">SUM(L247:Y247)</f>
+      <c r="Z247" s="33"/>
+      <c r="AA247" s="33"/>
+      <c r="AB247" s="9">
+        <f t="shared" ref="AB247:AB249" si="142">SUM(L247:Z247)</f>
         <v>712420</v>
       </c>
-      <c r="AB247" s="9">
-        <f>AA247-B247</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC247" s="9">
+        <f t="shared" ref="AC247" si="143">AB247-B247</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -16617,18 +16972,19 @@
       <c r="X248" s="3"/>
       <c r="Y248" s="3"/>
       <c r="Z248"/>
-      <c r="AA248" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA248"/>
+      <c r="AB248" s="9">
+        <f t="shared" si="142"/>
         <v>3140</v>
       </c>
-      <c r="AB248" s="5">
-        <f>C247-AA248</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC248" s="5">
+        <f t="shared" ref="AC248" si="144">C247-AB248</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -16663,18 +17019,19 @@
       <c r="X249" s="3"/>
       <c r="Y249" s="3"/>
       <c r="Z249"/>
-      <c r="AA249" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA249"/>
+      <c r="AB249" s="9">
+        <f t="shared" si="142"/>
         <v>2663</v>
       </c>
-      <c r="AB249" s="5">
-        <f>AA249-D247</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC249" s="5">
+        <f t="shared" ref="AC249" si="145">AB249-D247</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B250" s="7">
         <v>585903</v>
@@ -16728,19 +17085,20 @@
       <c r="W250" s="7"/>
       <c r="X250" s="7"/>
       <c r="Y250" s="7"/>
-      <c r="Z250"/>
-      <c r="AA250" s="9">
-        <f t="shared" si="21"/>
+      <c r="Z250" s="33"/>
+      <c r="AA250" s="33"/>
+      <c r="AB250" s="9">
+        <f t="shared" ref="AB250:AB267" si="146">SUM(L250:Z250)</f>
         <v>574219</v>
       </c>
-      <c r="AB250" s="9">
-        <f>AA250-B250</f>
+      <c r="AC250" s="9">
+        <f t="shared" ref="AC250" si="147">AB250-B250</f>
         <v>-11684</v>
       </c>
     </row>
-    <row r="251" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="251" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -16777,18 +17135,19 @@
       <c r="X251" s="3"/>
       <c r="Y251" s="3"/>
       <c r="Z251"/>
-      <c r="AA251" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA251"/>
+      <c r="AB251" s="9">
+        <f t="shared" si="146"/>
         <v>8964</v>
       </c>
-      <c r="AB251" s="5">
-        <f>C250-AA251</f>
+      <c r="AC251" s="5">
+        <f t="shared" ref="AC251" si="148">C250-AB251</f>
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="252" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -16825,18 +17184,19 @@
       <c r="X252" s="3"/>
       <c r="Y252" s="3"/>
       <c r="Z252"/>
-      <c r="AA252" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA252"/>
+      <c r="AB252" s="9">
+        <f t="shared" si="146"/>
         <v>7688</v>
       </c>
-      <c r="AB252" s="5">
-        <f>AA252-D250</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC252" s="5">
+        <f t="shared" ref="AC252" si="149">AB252-D250</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B253" s="7">
         <v>679810</v>
@@ -16892,19 +17252,20 @@
       <c r="W253" s="7"/>
       <c r="X253" s="7"/>
       <c r="Y253" s="7"/>
-      <c r="Z253"/>
-      <c r="AA253" s="9">
-        <f t="shared" si="21"/>
+      <c r="Z253" s="33"/>
+      <c r="AA253" s="33"/>
+      <c r="AB253" s="9">
+        <f t="shared" si="146"/>
         <v>658241</v>
       </c>
-      <c r="AB253" s="9">
-        <f>AA253-B253</f>
+      <c r="AC253" s="9">
+        <f t="shared" ref="AC253" si="150">AB253-B253</f>
         <v>-21569</v>
       </c>
     </row>
-    <row r="254" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="254" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -16943,18 +17304,19 @@
       <c r="X254" s="3"/>
       <c r="Y254" s="3"/>
       <c r="Z254"/>
-      <c r="AA254" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA254"/>
+      <c r="AB254" s="9">
+        <f t="shared" si="146"/>
         <v>15285</v>
       </c>
-      <c r="AB254" s="5">
-        <f>C253-AA254</f>
+      <c r="AC254" s="5">
+        <f t="shared" ref="AC254" si="151">C253-AB254</f>
         <v>61</v>
       </c>
     </row>
-    <row r="255" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="255" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -16993,18 +17355,19 @@
       <c r="X255" s="3"/>
       <c r="Y255" s="3"/>
       <c r="Z255"/>
-      <c r="AA255" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA255"/>
+      <c r="AB255" s="9">
+        <f t="shared" si="146"/>
         <v>10650</v>
       </c>
-      <c r="AB255" s="5">
-        <f>AA255-D253</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC255" s="5">
+        <f t="shared" ref="AC255" si="152">AB255-D253</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B256" s="7">
         <v>1143584</v>
@@ -17060,19 +17423,20 @@
       <c r="W256" s="7"/>
       <c r="X256" s="7"/>
       <c r="Y256" s="7"/>
-      <c r="Z256"/>
-      <c r="AA256" s="9">
-        <f t="shared" si="21"/>
+      <c r="Z256" s="33"/>
+      <c r="AA256" s="33"/>
+      <c r="AB256" s="9">
+        <f t="shared" si="146"/>
         <v>1139062</v>
       </c>
-      <c r="AB256" s="9">
-        <f>AA256-B256</f>
+      <c r="AC256" s="9">
+        <f t="shared" ref="AC256" si="153">AB256-B256</f>
         <v>-4522</v>
       </c>
     </row>
-    <row r="257" spans="1:48" s="2" customFormat="1" ht="15">
+    <row r="257" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -17111,18 +17475,19 @@
       <c r="X257" s="3"/>
       <c r="Y257" s="3"/>
       <c r="Z257"/>
-      <c r="AA257" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA257"/>
+      <c r="AB257" s="9">
+        <f t="shared" si="146"/>
         <v>7525</v>
       </c>
-      <c r="AB257" s="5">
-        <f>C256-AA257</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC257" s="5">
+        <f t="shared" ref="AC257" si="154">C256-AB257</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -17161,18 +17526,19 @@
       <c r="X258" s="3"/>
       <c r="Y258" s="3"/>
       <c r="Z258"/>
-      <c r="AA258" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA258"/>
+      <c r="AB258" s="9">
+        <f t="shared" si="146"/>
         <v>4334</v>
       </c>
-      <c r="AB258" s="5">
-        <f>AA258-D256</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC258" s="5">
+        <f t="shared" ref="AC258" si="155">AB258-D256</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B259" s="7">
         <v>397959</v>
@@ -17224,19 +17590,20 @@
       <c r="W259" s="7"/>
       <c r="X259" s="7"/>
       <c r="Y259" s="7"/>
-      <c r="Z259"/>
-      <c r="AA259" s="9">
-        <f t="shared" si="21"/>
+      <c r="Z259" s="33"/>
+      <c r="AA259" s="33"/>
+      <c r="AB259" s="9">
+        <f t="shared" si="146"/>
         <v>397959</v>
       </c>
-      <c r="AB259" s="9">
-        <f>AA259-B259</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC259" s="9">
+        <f t="shared" ref="AC259" si="156">AB259-B259</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -17271,18 +17638,19 @@
       <c r="X260" s="3"/>
       <c r="Y260" s="3"/>
       <c r="Z260"/>
-      <c r="AA260" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA260"/>
+      <c r="AB260" s="9">
+        <f t="shared" si="146"/>
         <v>11648</v>
       </c>
-      <c r="AB260" s="5">
-        <f>C259-AA260</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC260" s="5">
+        <f t="shared" ref="AC260" si="157">C259-AB260</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -17317,18 +17685,19 @@
       <c r="X261" s="3"/>
       <c r="Y261" s="3"/>
       <c r="Z261"/>
-      <c r="AA261" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA261"/>
+      <c r="AB261" s="9">
+        <f t="shared" si="146"/>
         <v>7437</v>
       </c>
-      <c r="AB261" s="5">
-        <f>AA261-D259</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC261" s="5">
+        <f t="shared" ref="AC261" si="158">AB261-D259</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B262" s="7">
         <v>562485</v>
@@ -17380,19 +17749,20 @@
       <c r="W262" s="7"/>
       <c r="X262" s="7"/>
       <c r="Y262" s="7"/>
-      <c r="Z262"/>
-      <c r="AA262" s="9">
-        <f t="shared" si="21"/>
+      <c r="Z262" s="33"/>
+      <c r="AA262" s="33"/>
+      <c r="AB262" s="9">
+        <f t="shared" si="146"/>
         <v>562485</v>
       </c>
-      <c r="AB262" s="9">
-        <f>AA262-B262</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC262" s="9">
+        <f t="shared" ref="AC262" si="159">AB262-B262</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -17427,18 +17797,19 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
       <c r="Z263"/>
-      <c r="AA263" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA263"/>
+      <c r="AB263" s="9">
+        <f t="shared" si="146"/>
         <v>7889</v>
       </c>
-      <c r="AB263" s="5">
-        <f>C262-AA263</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC263" s="5">
+        <f t="shared" ref="AC263" si="160">C262-AB263</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -17473,18 +17844,19 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
       <c r="Z264"/>
-      <c r="AA264" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA264"/>
+      <c r="AB264" s="9">
+        <f t="shared" si="146"/>
         <v>4448</v>
       </c>
-      <c r="AB264" s="5">
-        <f>AA264-D262</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="1:48" s="8" customFormat="1" ht="15">
+      <c r="AC264" s="5">
+        <f t="shared" ref="AC264" si="161">AB264-D262</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:49" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B265" s="7">
         <v>804949</v>
@@ -17538,19 +17910,20 @@
       <c r="W265" s="7"/>
       <c r="X265" s="7"/>
       <c r="Y265" s="7"/>
-      <c r="Z265"/>
-      <c r="AA265" s="9">
-        <f t="shared" si="21"/>
+      <c r="Z265" s="33"/>
+      <c r="AA265" s="33"/>
+      <c r="AB265" s="9">
+        <f t="shared" si="146"/>
         <v>804949</v>
       </c>
-      <c r="AB265" s="9">
-        <f>AA265-B265</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC265" s="9">
+        <f t="shared" ref="AC265" si="162">AB265-B265</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -17587,18 +17960,19 @@
       <c r="X266" s="3"/>
       <c r="Y266" s="3"/>
       <c r="Z266"/>
-      <c r="AA266" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA266"/>
+      <c r="AB266" s="9">
+        <f t="shared" si="146"/>
         <v>48145</v>
       </c>
-      <c r="AB266" s="5">
-        <f>C265-AA266</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:48" s="2" customFormat="1" ht="15">
+      <c r="AC266" s="5">
+        <f t="shared" ref="AC266" si="163">C265-AB266</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:49" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -17635,19 +18009,20 @@
       <c r="X267" s="3"/>
       <c r="Y267" s="3"/>
       <c r="Z267"/>
-      <c r="AA267" s="5">
-        <f t="shared" si="21"/>
+      <c r="AA267"/>
+      <c r="AB267" s="9">
+        <f t="shared" si="146"/>
         <v>36045</v>
       </c>
-      <c r="AB267" s="5">
-        <f>AA267-D265</f>
-        <v>0</v>
-      </c>
-      <c r="AD267" s="5"/>
-    </row>
-    <row r="268" spans="1:48" s="13" customFormat="1" ht="15">
+      <c r="AC267" s="5">
+        <f t="shared" ref="AC267" si="164">AB267-D265</f>
+        <v>0</v>
+      </c>
+      <c r="AE267" s="5"/>
+    </row>
+    <row r="268" spans="1:49" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B268" s="12">
         <v>6106894</v>
@@ -17691,85 +18066,80 @@
       <c r="W268" s="12"/>
       <c r="X268" s="12"/>
       <c r="Y268" s="12"/>
-      <c r="Z268"/>
-      <c r="AA268" s="14"/>
+      <c r="Z268" s="12"/>
+      <c r="AA268" s="12"/>
       <c r="AB268" s="14"/>
-      <c r="AD268" s="14">
-        <f t="shared" ref="AD268:AL268" si="22">SUM(B245:B267)</f>
+      <c r="AC268" s="14"/>
+      <c r="AE268" s="14">
+        <f t="shared" ref="AE268:AM268" si="165">SUM(B245:B267)</f>
         <v>6106894</v>
       </c>
-      <c r="AE268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AF268" s="14">
+        <f t="shared" si="165"/>
         <v>120380</v>
       </c>
-      <c r="AF268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AG268" s="14">
+        <f t="shared" si="165"/>
         <v>85046</v>
       </c>
-      <c r="AG268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AH268" s="14">
+        <f t="shared" si="165"/>
         <v>433543</v>
       </c>
-      <c r="AH268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AI268" s="14">
+        <f t="shared" si="165"/>
         <v>2441</v>
       </c>
-      <c r="AI268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AJ268" s="14">
+        <f t="shared" si="165"/>
         <v>1859</v>
       </c>
-      <c r="AJ268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AK268" s="14">
+        <f t="shared" si="165"/>
         <v>5203911</v>
       </c>
-      <c r="AK268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AL268" s="14">
+        <f t="shared" si="165"/>
         <v>55897</v>
       </c>
-      <c r="AL268" s="14">
-        <f t="shared" si="22"/>
+      <c r="AM268" s="14">
+        <f t="shared" si="165"/>
         <v>38195</v>
       </c>
-      <c r="AN268" s="14">
-        <f t="shared" ref="AN268:AV269" si="23">AD268-B268</f>
-        <v>0</v>
-      </c>
       <c r="AO268" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="AO268:AW269" si="166">AE268-B268</f>
+        <v>0</v>
+      </c>
+      <c r="AP268" s="14">
+        <f t="shared" si="166"/>
         <v>-10400</v>
       </c>
-      <c r="AP268" s="14">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
       <c r="AQ268" s="14">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AR268" s="14" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AS268" s="14" t="e">
-        <f t="shared" si="23"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AT268" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="166"/>
+        <v>0</v>
+      </c>
+      <c r="AR268" s="14">
+        <f t="shared" si="166"/>
+        <v>0</v>
+      </c>
+      <c r="AS268" s="14"/>
+      <c r="AT268" s="14"/>
+      <c r="AU268" s="14">
+        <f t="shared" si="166"/>
         <v>-697285</v>
       </c>
-      <c r="AU268" s="14">
-        <f t="shared" si="23"/>
+      <c r="AV268" s="14">
+        <f t="shared" si="166"/>
         <v>-6820</v>
       </c>
-      <c r="AV268" s="14">
-        <f t="shared" si="23"/>
+      <c r="AW268" s="14">
+        <f t="shared" si="166"/>
         <v>-6032</v>
       </c>
     </row>
-    <row r="269" spans="1:48" s="13" customFormat="1" ht="15">
+    <row r="269" spans="1:49" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B269" s="12">
         <v>116652610</v>
@@ -17813,86 +18183,93 @@
       <c r="W269" s="12"/>
       <c r="X269" s="12"/>
       <c r="Y269" s="12"/>
-      <c r="Z269"/>
-      <c r="AA269" s="14"/>
+      <c r="Z269" s="12"/>
+      <c r="AA269" s="12"/>
       <c r="AB269" s="14"/>
-      <c r="AD269" s="14">
-        <f t="shared" ref="AD269:AL269" si="24">SUM(AD189:AD268)</f>
-        <v>114172516</v>
-      </c>
+      <c r="AC269" s="14"/>
       <c r="AE269" s="14">
-        <f t="shared" si="24"/>
-        <v>5088026</v>
+        <f>SUM(AE189:AE268)</f>
+        <v>116262294</v>
       </c>
       <c r="AF269" s="14">
-        <f t="shared" si="24"/>
-        <v>3655664</v>
+        <f t="shared" ref="AF269:AM269" si="167">SUM(AF189:AF268)</f>
+        <v>5204905</v>
       </c>
       <c r="AG269" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="167"/>
+        <v>3724859</v>
+      </c>
+      <c r="AH269" s="14">
+        <f t="shared" si="167"/>
         <v>8880894</v>
       </c>
-      <c r="AH269" s="14">
-        <f t="shared" si="24"/>
+      <c r="AI269" s="14">
+        <f t="shared" si="167"/>
         <v>305306</v>
       </c>
-      <c r="AI269" s="14">
-        <f t="shared" si="24"/>
+      <c r="AJ269" s="14">
+        <f t="shared" si="167"/>
         <v>242939</v>
       </c>
-      <c r="AJ269" s="14">
-        <f t="shared" si="24"/>
+      <c r="AK269" s="14">
+        <f t="shared" si="167"/>
         <v>109254010</v>
       </c>
-      <c r="AK269" s="14">
-        <f t="shared" si="24"/>
+      <c r="AL269" s="14">
+        <f t="shared" si="167"/>
         <v>4939848</v>
       </c>
-      <c r="AL269" s="14">
-        <f t="shared" si="24"/>
+      <c r="AM269" s="14">
+        <f t="shared" si="167"/>
         <v>3337740</v>
       </c>
-      <c r="AN269" s="14">
-        <f t="shared" si="23"/>
-        <v>-2480094</v>
-      </c>
       <c r="AO269" s="14">
-        <f t="shared" si="23"/>
-        <v>-139092</v>
+        <f t="shared" si="166"/>
+        <v>-390316</v>
       </c>
       <c r="AP269" s="14">
-        <f t="shared" si="23"/>
-        <v>-135197</v>
+        <f t="shared" si="166"/>
+        <v>-22213</v>
       </c>
       <c r="AQ269" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="166"/>
+        <v>-66002</v>
+      </c>
+      <c r="AR269" s="14">
+        <f t="shared" si="166"/>
         <v>-2548667</v>
       </c>
-      <c r="AR269" s="14">
-        <f t="shared" si="23"/>
+      <c r="AS269" s="14">
+        <f t="shared" si="166"/>
         <v>-92245</v>
       </c>
-      <c r="AS269" s="14">
-        <f t="shared" si="23"/>
+      <c r="AT269" s="14">
+        <f t="shared" si="166"/>
         <v>-74848</v>
       </c>
-      <c r="AT269" s="14">
-        <f t="shared" si="23"/>
+      <c r="AU269" s="14">
+        <f t="shared" si="166"/>
         <v>-3147290</v>
       </c>
-      <c r="AU269" s="14">
-        <f t="shared" si="23"/>
+      <c r="AV269" s="14">
+        <f t="shared" si="166"/>
         <v>-102480</v>
       </c>
-      <c r="AV269" s="14">
-        <f t="shared" si="23"/>
+      <c r="AW269" s="14">
+        <f t="shared" si="166"/>
         <v>-68499</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="L1:Y1"/>
+    <mergeCell ref="L1:Z1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E38946-3F77-47FE-8DE8-72DF546ABD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5B8396-6B88-450B-9445-954A985044FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="316">
   <si>
     <t>губ</t>
   </si>
@@ -958,6 +958,30 @@
   </si>
   <si>
     <t>[Астраханская (сумма)]</t>
+  </si>
+  <si>
+    <t>Числа рождений и смертей по отдельным территориям в целом сходятся по контрольным суммам,</t>
+  </si>
+  <si>
+    <t>за вычетом нескольких незначительных расхождений.</t>
+  </si>
+  <si>
+    <t>Исправленные опечатки помечены синим фоном.</t>
+  </si>
+  <si>
+    <t>Число жителей часто расходится, и значительно.</t>
+  </si>
+  <si>
+    <t>Причина расхождения неясна.</t>
+  </si>
+  <si>
+    <t>Ряды итого расходятся по сумме рождений и смертей для земских губерний.</t>
+  </si>
+  <si>
+    <t>Аналогичное расхождение для Сибири и Средней Азии связано с невключением некоторых областей в сумму.</t>
+  </si>
+  <si>
+    <t>Для поступательного расчёта в конечном итого важны только ряды рождений и смертей по отдельным территориям.</t>
   </si>
 </sst>
 </file>
@@ -967,7 +991,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -998,6 +1022,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1051,7 +1080,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1068,7 +1097,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1181,8 +1210,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1350,9 +1383,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12DA313-D41C-46B5-B326-1C471A56B478}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="46" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="46" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="46" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="46" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="46" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="46" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="46" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="46" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="46" t="s">
+        <v>315</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15621,13 +15700,13 @@
         <v>186</v>
       </c>
       <c r="B174" s="7">
-        <v>2057807</v>
+        <v>2087807</v>
       </c>
       <c r="C174" s="7">
         <v>98722</v>
       </c>
-      <c r="D174" s="7">
-        <v>6300</v>
+      <c r="D174" s="48">
+        <v>68008</v>
       </c>
       <c r="E174" s="7">
         <v>82923</v>
@@ -15691,7 +15770,7 @@
       </c>
       <c r="AF174" s="9">
         <f>SUM(N176:AB176)</f>
-        <v>57329</v>
+        <v>68008</v>
       </c>
       <c r="AG174" s="9">
         <f t="shared" ref="AG174:AL174" si="74">E174</f>
@@ -15720,7 +15799,7 @@
       <c r="AM174" s="2"/>
       <c r="AN174" s="9">
         <f>AD174-B174</f>
-        <v>-6714</v>
+        <v>-36714</v>
       </c>
       <c r="AO174" s="9">
         <f>AE174-C174</f>
@@ -15728,25 +15807,25 @@
       </c>
       <c r="AP174" s="9">
         <f>AF174-D174</f>
-        <v>51029</v>
+        <v>0</v>
       </c>
       <c r="AQ174" s="5"/>
       <c r="AR174" s="41">
         <f>C174/B174*1000</f>
-        <v>47.974372718141204</v>
+        <v>47.285022035082747</v>
       </c>
       <c r="AS174" s="41">
         <f>D174/B174*1000</f>
-        <v>3.0615115994843052</v>
+        <v>32.573892127002161</v>
       </c>
       <c r="AT174" s="42"/>
       <c r="AU174" s="41">
         <f>AR174-K174</f>
-        <v>0.5743727181412055</v>
+        <v>-0.11497796491725154</v>
       </c>
       <c r="AV174" s="41">
         <f>AS174-L174</f>
-        <v>-29.538488400515696</v>
+        <v>-2.6107872997840786E-2</v>
       </c>
       <c r="AW174" s="5"/>
     </row>
@@ -15809,8 +15888,8 @@
       <c r="K176" s="28"/>
       <c r="L176" s="28"/>
       <c r="M176" s="3"/>
-      <c r="N176" s="3">
-        <v>1186</v>
+      <c r="N176" s="48">
+        <v>11865</v>
       </c>
       <c r="O176" s="3">
         <v>12393</v>
@@ -16892,7 +16971,7 @@
       </c>
       <c r="AF189" s="14">
         <f t="shared" si="79"/>
-        <v>996068</v>
+        <v>1006747</v>
       </c>
       <c r="AG189" s="14">
         <f t="shared" si="79"/>
@@ -16929,7 +17008,7 @@
       </c>
       <c r="AP189" s="14">
         <f>AF189-D189</f>
-        <v>-1433336</v>
+        <v>-1422657</v>
       </c>
       <c r="AQ189" s="5"/>
       <c r="AR189" s="41">
@@ -17244,7 +17323,7 @@
       </c>
       <c r="AF193" s="14">
         <f t="shared" si="82"/>
-        <v>1914023</v>
+        <v>1924702</v>
       </c>
       <c r="AG193" s="14">
         <f t="shared" si="82"/>
@@ -17281,7 +17360,7 @@
       </c>
       <c r="AP193" s="14">
         <f t="shared" si="83"/>
-        <v>-1433333</v>
+        <v>-1422654</v>
       </c>
       <c r="AQ193" s="5"/>
       <c r="AR193" s="41">
@@ -19990,8 +20069,8 @@
       <c r="B227" s="20">
         <v>565477</v>
       </c>
-      <c r="C227" s="20">
-        <v>16344</v>
+      <c r="C227" s="47">
+        <v>17344</v>
       </c>
       <c r="D227" s="20">
         <v>14410</v>
@@ -20095,7 +20174,7 @@
       </c>
       <c r="AO227" s="9">
         <f>AE227-C227</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP227" s="9">
         <f>AF227-D227</f>
@@ -20104,7 +20183,7 @@
       <c r="AQ227" s="5"/>
       <c r="AR227" s="41">
         <f>C227/B227*1000</f>
-        <v>28.903032307237961</v>
+        <v>30.671450828238815</v>
       </c>
       <c r="AS227" s="41">
         <f>D227/B227*1000</f>
@@ -20113,7 +20192,7 @@
       <c r="AT227" s="42"/>
       <c r="AU227" s="41">
         <f>AR227-K227</f>
-        <v>-9.6967692762039093E-2</v>
+        <v>1.6714508282388145</v>
       </c>
       <c r="AV227" s="41">
         <f>AS227-L227</f>
@@ -20822,7 +20901,7 @@
       <c r="N237" s="23">
         <v>5642</v>
       </c>
-      <c r="O237" s="46">
+      <c r="O237" s="47">
         <v>1305</v>
       </c>
       <c r="P237" s="23">
@@ -23612,7 +23691,7 @@
       </c>
       <c r="AF273" s="14">
         <f t="shared" si="127"/>
-        <v>2364163</v>
+        <v>2374842</v>
       </c>
       <c r="AG273" s="14">
         <f t="shared" si="127"/>
@@ -23649,7 +23728,7 @@
       </c>
       <c r="AP273" s="14">
         <f t="shared" si="125"/>
-        <v>-1426698</v>
+        <v>-1416019</v>
       </c>
       <c r="AQ273" s="5"/>
       <c r="AR273" s="41">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5B8396-6B88-450B-9445-954A985044FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5325D9-8F79-4BC4-88FD-6FFC50C8FFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="317">
   <si>
     <t>губ</t>
   </si>
@@ -982,6 +982,9 @@
   </si>
   <si>
     <t>Для поступательного расчёта в конечном итого важны только ряды рождений и смертей по отдельным территориям.</t>
+  </si>
+  <si>
+    <t>Причина расхождения неясна, но см. 1890-notes.html</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1033,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1084,6 +1087,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1097,7 +1106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1206,16 +1215,25 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,47 +1405,47 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="44" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="44" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="44" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="44" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="44" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="46" t="s">
-        <v>312</v>
+      <c r="A9" s="44" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="44" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="44" t="s">
         <v>315</v>
       </c>
     </row>
@@ -1517,22 +1535,22 @@
         <v>287</v>
       </c>
       <c r="M1" s="17"/>
-      <c r="N1" s="44" t="s">
+      <c r="N1" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
       <c r="AB1" s="35"/>
       <c r="AC1" s="37"/>
       <c r="AD1" s="16" t="s">
@@ -2464,8 +2482,8 @@
       <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="7">
-        <v>1369473</v>
+      <c r="B15" s="50">
+        <v>1364473</v>
       </c>
       <c r="C15" s="7">
         <v>58044</v>
@@ -2574,7 +2592,7 @@
       <c r="AM15" s="2"/>
       <c r="AN15" s="9">
         <f>AD15-B15</f>
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="9">
         <f>AE15-C15</f>
@@ -2587,20 +2605,20 @@
       <c r="AQ15" s="5"/>
       <c r="AR15" s="41">
         <f>C15/B15*1000</f>
-        <v>42.384187201938261</v>
+        <v>42.539500598399528</v>
       </c>
       <c r="AS15" s="41">
         <f>D15/B15*1000</f>
-        <v>25.164424563317422</v>
+        <v>25.256637544311978</v>
       </c>
       <c r="AT15" s="42"/>
       <c r="AU15" s="41">
         <f>AR15-K15</f>
-        <v>-0.11581279806173939</v>
+        <v>3.9500598399527576E-2</v>
       </c>
       <c r="AV15" s="41">
         <f>AS15-L15</f>
-        <v>-3.5575436682577788E-2</v>
+        <v>5.6637544311978871E-2</v>
       </c>
       <c r="AW15" s="5"/>
     </row>
@@ -3977,8 +3995,8 @@
       <c r="R33" s="7">
         <v>124797</v>
       </c>
-      <c r="S33" s="7">
-        <v>94984</v>
+      <c r="S33" s="50">
+        <v>84984</v>
       </c>
       <c r="T33" s="7">
         <v>130436</v>
@@ -4001,7 +4019,7 @@
       <c r="AC33" s="2"/>
       <c r="AD33" s="9">
         <f>SUM(N33:AB33)</f>
-        <v>1425258</v>
+        <v>1415258</v>
       </c>
       <c r="AE33" s="9">
         <f>SUM(N34:AB34)</f>
@@ -4038,7 +4056,7 @@
       <c r="AM33" s="2"/>
       <c r="AN33" s="9">
         <f>AD33-B33</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="9">
         <f>AE33-C33</f>
@@ -4699,7 +4717,7 @@
       <c r="AC42" s="2"/>
       <c r="AD42" s="14">
         <f t="shared" ref="AD42:AL42" si="12">SUM(AD2:AD40)</f>
-        <v>19781355</v>
+        <v>19771355</v>
       </c>
       <c r="AE42" s="14">
         <f t="shared" si="12"/>
@@ -4736,7 +4754,7 @@
       <c r="AM42" s="2"/>
       <c r="AN42" s="14">
         <f>AD42-B42</f>
-        <v>6970</v>
+        <v>-3030</v>
       </c>
       <c r="AO42" s="14">
         <f>AE42-C42</f>
@@ -11278,8 +11296,8 @@
       <c r="A121" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B121" s="7">
-        <v>1290507</v>
+      <c r="B121" s="50">
+        <v>1276110</v>
       </c>
       <c r="C121" s="7">
         <v>55572</v>
@@ -11388,7 +11406,7 @@
       <c r="AM121" s="2"/>
       <c r="AN121" s="9">
         <f>AD121-B121</f>
-        <v>-14397</v>
+        <v>0</v>
       </c>
       <c r="AO121" s="9">
         <f>AE121-C121</f>
@@ -11401,20 +11419,20 @@
       <c r="AQ121" s="5"/>
       <c r="AR121" s="41">
         <f>C121/B121*1000</f>
-        <v>43.062145342876867</v>
+        <v>43.547970002585984</v>
       </c>
       <c r="AS121" s="41">
         <f>D121/B121*1000</f>
-        <v>31.906064825684791</v>
+        <v>32.266027223358485</v>
       </c>
       <c r="AT121" s="42"/>
       <c r="AU121" s="41">
         <f>AR121-K121</f>
-        <v>-5.037854657123134</v>
+        <v>-4.5520299974140173</v>
       </c>
       <c r="AV121" s="41">
         <f>AS121-L121</f>
-        <v>6.0648256847919413E-3</v>
+        <v>0.36602722335848625</v>
       </c>
       <c r="AW121" s="5"/>
     </row>
@@ -11837,7 +11855,7 @@
       </c>
       <c r="AF127" s="9">
         <f>SUM(N129:AB129)</f>
-        <v>84709</v>
+        <v>85609</v>
       </c>
       <c r="AG127" s="10" t="str">
         <f t="shared" ref="AG127:AL127" si="49">E127</f>
@@ -11874,7 +11892,7 @@
       </c>
       <c r="AP127" s="9">
         <f>AF127-D127</f>
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="AQ127" s="5"/>
       <c r="AR127" s="41">
@@ -12000,8 +12018,8 @@
       <c r="W129" s="3">
         <v>5198</v>
       </c>
-      <c r="X129" s="3">
-        <v>4509</v>
+      <c r="X129" s="46">
+        <v>5409</v>
       </c>
       <c r="Y129" s="3">
         <v>3956</v>
@@ -13784,8 +13802,8 @@
       <c r="T150" s="7">
         <v>47191</v>
       </c>
-      <c r="U150" s="7">
-        <v>23645</v>
+      <c r="U150" s="50">
+        <v>93645</v>
       </c>
       <c r="V150" s="7"/>
       <c r="W150" s="7"/>
@@ -13796,7 +13814,7 @@
       <c r="AC150" s="2"/>
       <c r="AD150" s="9">
         <f>SUM(N150:AB150)</f>
-        <v>679176</v>
+        <v>749176</v>
       </c>
       <c r="AE150" s="9">
         <f>SUM(N151:AB151)</f>
@@ -13833,7 +13851,7 @@
       <c r="AM150" s="2"/>
       <c r="AN150" s="9">
         <f>AD150-B150</f>
-        <v>-155142</v>
+        <v>-85142</v>
       </c>
       <c r="AO150" s="9">
         <f>AE150-C150</f>
@@ -14004,8 +14022,8 @@
       <c r="P153" s="7">
         <v>292791</v>
       </c>
-      <c r="Q153" s="7">
-        <v>194683</v>
+      <c r="Q153" s="50">
+        <v>199683</v>
       </c>
       <c r="R153" s="7">
         <v>340792</v>
@@ -14032,7 +14050,7 @@
       <c r="AC153" s="2"/>
       <c r="AD153" s="9">
         <f>SUM(N153:AB153)</f>
-        <v>2428445</v>
+        <v>2433445</v>
       </c>
       <c r="AE153" s="9">
         <f>SUM(N154:AB154)</f>
@@ -14069,7 +14087,7 @@
       <c r="AM153" s="2"/>
       <c r="AN153" s="9">
         <f>AD153-B153</f>
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="AO153" s="9">
         <f>AE153-C153</f>
@@ -14931,8 +14949,8 @@
       <c r="A165" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B165" s="7">
-        <v>2900646</v>
+      <c r="B165" s="50">
+        <v>2871526</v>
       </c>
       <c r="C165" s="7">
         <v>133938</v>
@@ -15043,7 +15061,7 @@
       <c r="AM165" s="2"/>
       <c r="AN165" s="9">
         <f>AD165-B165</f>
-        <v>-29120</v>
+        <v>0</v>
       </c>
       <c r="AO165" s="9">
         <f>AE165-C165</f>
@@ -15056,20 +15074,20 @@
       <c r="AQ165" s="5"/>
       <c r="AR165" s="41">
         <f>C165/B165*1000</f>
-        <v>46.17523131054255</v>
+        <v>46.643491996938216</v>
       </c>
       <c r="AS165" s="41">
         <f>D165/B165*1000</f>
-        <v>36.481183846632788</v>
+        <v>36.85113768776602</v>
       </c>
       <c r="AT165" s="42"/>
       <c r="AU165" s="41">
         <f>AR165-K165</f>
-        <v>-0.32476868945744997</v>
+        <v>0.14349199693821646</v>
       </c>
       <c r="AV165" s="41">
         <f>AS165-L165</f>
-        <v>8.118384663278988E-2</v>
+        <v>0.45113768776602114</v>
       </c>
       <c r="AW165" s="5"/>
     </row>
@@ -15699,13 +15717,13 @@
       <c r="A174" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B174" s="7">
-        <v>2087807</v>
+      <c r="B174" s="50">
+        <v>2051093</v>
       </c>
       <c r="C174" s="7">
         <v>98722</v>
       </c>
-      <c r="D174" s="48">
+      <c r="D174" s="46">
         <v>68008</v>
       </c>
       <c r="E174" s="7">
@@ -15799,7 +15817,7 @@
       <c r="AM174" s="2"/>
       <c r="AN174" s="9">
         <f>AD174-B174</f>
-        <v>-36714</v>
+        <v>0</v>
       </c>
       <c r="AO174" s="9">
         <f>AE174-C174</f>
@@ -15812,20 +15830,20 @@
       <c r="AQ174" s="5"/>
       <c r="AR174" s="41">
         <f>C174/B174*1000</f>
-        <v>47.285022035082747</v>
+        <v>48.131410911158099</v>
       </c>
       <c r="AS174" s="41">
         <f>D174/B174*1000</f>
-        <v>32.573892127002161</v>
+        <v>33.156955827941495</v>
       </c>
       <c r="AT174" s="42"/>
       <c r="AU174" s="41">
         <f>AR174-K174</f>
-        <v>-0.11497796491725154</v>
+        <v>0.73141091115810042</v>
       </c>
       <c r="AV174" s="41">
         <f>AS174-L174</f>
-        <v>-2.6107872997840786E-2</v>
+        <v>0.55695582794149345</v>
       </c>
       <c r="AW174" s="5"/>
     </row>
@@ -15888,7 +15906,7 @@
       <c r="K176" s="28"/>
       <c r="L176" s="28"/>
       <c r="M176" s="3"/>
-      <c r="N176" s="48">
+      <c r="N176" s="46">
         <v>11865</v>
       </c>
       <c r="O176" s="3">
@@ -16435,8 +16453,8 @@
       <c r="Q183" s="7">
         <v>133428</v>
       </c>
-      <c r="R183" s="7">
-        <v>170182</v>
+      <c r="R183" s="50">
+        <v>130182</v>
       </c>
       <c r="S183" s="7">
         <v>148145</v>
@@ -16465,13 +16483,13 @@
       <c r="AA183" s="7">
         <v>166979</v>
       </c>
-      <c r="AB183" s="18">
+      <c r="AB183" s="49">
         <v>178770</v>
       </c>
       <c r="AC183" s="18"/>
       <c r="AD183" s="9">
         <f>SUM(N183:AB183)</f>
-        <v>2284377</v>
+        <v>2244377</v>
       </c>
       <c r="AE183" s="9">
         <f>SUM(N184:AB184)</f>
@@ -16508,7 +16526,7 @@
       <c r="AM183" s="2"/>
       <c r="AN183" s="9">
         <f>AD183-B183</f>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="AO183" s="9">
         <f>AE183-C183</f>
@@ -16963,7 +16981,7 @@
       <c r="AC189" s="2"/>
       <c r="AD189" s="14">
         <f>SUM(AD85:AD187)</f>
-        <v>63890929</v>
+        <v>63925929</v>
       </c>
       <c r="AE189" s="14">
         <f t="shared" ref="AE189:AL189" si="79">SUM(AE145:AE188)</f>
@@ -17000,7 +17018,7 @@
       <c r="AM189" s="2"/>
       <c r="AN189" s="14">
         <f>AD189-B189</f>
-        <v>-778667</v>
+        <v>-743667</v>
       </c>
       <c r="AO189" s="14">
         <f>AE189-C189</f>
@@ -17315,7 +17333,7 @@
       <c r="AC193" s="2"/>
       <c r="AD193" s="14">
         <f>SUM(AD42, AD74, AD84, AD189, AD190)</f>
-        <v>97029642</v>
+        <v>97054642</v>
       </c>
       <c r="AE193" s="14">
         <f t="shared" ref="AE193:AL193" si="82">SUM(AE42, AE74, AE84, AE189, AE190)</f>
@@ -17352,7 +17370,7 @@
       <c r="AM193" s="2"/>
       <c r="AN193" s="14">
         <f t="shared" ref="AN193:AP194" si="83">AD193-B193</f>
-        <v>-777697</v>
+        <v>-752697</v>
       </c>
       <c r="AO193" s="14">
         <f t="shared" si="83"/>
@@ -17410,8 +17428,8 @@
       <c r="A194" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B194" s="7">
-        <v>820308</v>
+      <c r="B194" s="50">
+        <v>735626</v>
       </c>
       <c r="C194" s="7">
         <v>22979</v>
@@ -17512,7 +17530,7 @@
       <c r="AM194" s="2"/>
       <c r="AN194" s="9">
         <f t="shared" si="83"/>
-        <v>-84682</v>
+        <v>0</v>
       </c>
       <c r="AO194" s="9">
         <f t="shared" si="83"/>
@@ -17525,20 +17543,20 @@
       <c r="AQ194" s="5"/>
       <c r="AR194" s="41">
         <f>C194/B194*1000</f>
-        <v>28.012648907483531</v>
+        <v>31.237340713895374</v>
       </c>
       <c r="AS194" s="41">
         <f>D194/B194*1000</f>
-        <v>23.722796803151986</v>
+        <v>26.453659876078333</v>
       </c>
       <c r="AT194" s="42"/>
       <c r="AU194" s="41">
         <f>AR194-K194</f>
-        <v>1.2648907483530536E-2</v>
+        <v>3.2373407138953745</v>
       </c>
       <c r="AV194" s="41">
         <f>AS194-L194</f>
-        <v>2.2796803151987177E-2</v>
+        <v>2.7536598760783342</v>
       </c>
       <c r="AW194" s="5"/>
     </row>
@@ -17880,8 +17898,8 @@
       <c r="A200" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B200" s="7">
-        <v>850623</v>
+      <c r="B200" s="50">
+        <v>767126</v>
       </c>
       <c r="C200" s="7">
         <v>21326</v>
@@ -17984,7 +18002,7 @@
       <c r="AM200" s="2"/>
       <c r="AN200" s="9">
         <f>AD200-B200</f>
-        <v>-83497</v>
+        <v>0</v>
       </c>
       <c r="AO200" s="9">
         <f>AE200-C200</f>
@@ -17997,20 +18015,20 @@
       <c r="AQ200" s="5"/>
       <c r="AR200" s="41">
         <f>C200/B200*1000</f>
-        <v>25.071036169960134</v>
+        <v>27.799865993330954</v>
       </c>
       <c r="AS200" s="41">
         <f>D200/B200*1000</f>
-        <v>18.487626128143724</v>
+        <v>20.499891803953979</v>
       </c>
       <c r="AT200" s="42"/>
       <c r="AU200" s="41">
         <f>AR200-K200</f>
-        <v>-2.8963830039867133E-2</v>
+        <v>2.6998659933309526</v>
       </c>
       <c r="AV200" s="41">
         <f>AS200-L200</f>
-        <v>-1.2373871856276253E-2</v>
+        <v>1.9998918039539788</v>
       </c>
       <c r="AW200" s="5"/>
     </row>
@@ -19476,9 +19494,8 @@
         <v>13837</v>
       </c>
       <c r="AM219" s="2"/>
-      <c r="AN219" s="9">
-        <f>AD219-B219</f>
-        <v>-686671</v>
+      <c r="AN219" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="AO219" s="9">
         <f>AE219-C219</f>
@@ -19846,14 +19863,14 @@
       <c r="A224" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="B224" s="20">
-        <v>480546</v>
+      <c r="B224" s="51">
+        <v>460679</v>
       </c>
       <c r="C224" s="20">
         <v>22847</v>
       </c>
-      <c r="D224" s="20">
-        <v>17185</v>
+      <c r="D224" s="45">
+        <v>17385</v>
       </c>
       <c r="E224" s="20">
         <v>39822</v>
@@ -19946,7 +19963,7 @@
       <c r="AM224" s="2"/>
       <c r="AN224" s="9">
         <f>AD224-B224</f>
-        <v>-19867</v>
+        <v>0</v>
       </c>
       <c r="AO224" s="9">
         <f>AE224-C224</f>
@@ -19954,25 +19971,25 @@
       </c>
       <c r="AP224" s="9">
         <f>AF224-D224</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AQ224" s="5"/>
       <c r="AR224" s="41">
         <f>C224/B224*1000</f>
-        <v>47.5438355537243</v>
+        <v>49.594185973313301</v>
       </c>
       <c r="AS224" s="41">
         <f>D224/B224*1000</f>
-        <v>35.76140473544676</v>
+        <v>37.737774024863299</v>
       </c>
       <c r="AT224" s="42"/>
       <c r="AU224" s="41">
         <f>AR224-K224</f>
-        <v>4.3835553724299814E-2</v>
+        <v>2.0941859733133015</v>
       </c>
       <c r="AV224" s="41">
         <f>AS224-L224</f>
-        <v>6.1404735446757286E-2</v>
+        <v>2.0377740248632961</v>
       </c>
       <c r="AW224" s="5"/>
     </row>
@@ -20069,7 +20086,7 @@
       <c r="B227" s="20">
         <v>565477</v>
       </c>
-      <c r="C227" s="47">
+      <c r="C227" s="45">
         <v>17344</v>
       </c>
       <c r="D227" s="20">
@@ -20901,7 +20918,7 @@
       <c r="N237" s="23">
         <v>5642</v>
       </c>
-      <c r="O237" s="47">
+      <c r="O237" s="45">
         <v>1305</v>
       </c>
       <c r="P237" s="23">
@@ -22193,8 +22210,8 @@
       <c r="A254" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B254" s="7">
-        <v>585903</v>
+      <c r="B254" s="50">
+        <v>574219</v>
       </c>
       <c r="C254" s="7">
         <v>8966</v>
@@ -22292,7 +22309,7 @@
       <c r="AM254" s="2"/>
       <c r="AN254" s="9">
         <f>AD254-B254</f>
-        <v>-11684</v>
+        <v>0</v>
       </c>
       <c r="AO254" s="9">
         <f>AE254-C254</f>
@@ -22305,20 +22322,20 @@
       <c r="AQ254" s="5"/>
       <c r="AR254" s="41">
         <f>C254/B254*1000</f>
-        <v>15.302874366576038</v>
+        <v>15.6142517053598</v>
       </c>
       <c r="AS254" s="41">
         <f>D254/B254*1000</f>
-        <v>13.121625934668367</v>
+        <v>13.38862002128108</v>
       </c>
       <c r="AT254" s="42"/>
       <c r="AU254" s="41">
         <f>AR254-K254</f>
-        <v>2.874366576037346E-3</v>
+        <v>0.31425170535979952</v>
       </c>
       <c r="AV254" s="41">
         <f>AS254-L254</f>
-        <v>2.1625934668367819E-2</v>
+        <v>0.28862002128107989</v>
       </c>
       <c r="AW254" s="5"/>
     </row>
@@ -22412,8 +22429,8 @@
       <c r="A257" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B257" s="7">
-        <v>679810</v>
+      <c r="B257" s="50">
+        <v>658241</v>
       </c>
       <c r="C257" s="7">
         <v>15346</v>
@@ -22513,7 +22530,7 @@
       <c r="AM257" s="2"/>
       <c r="AN257" s="9">
         <f>AD257-B257</f>
-        <v>-21569</v>
+        <v>0</v>
       </c>
       <c r="AO257" s="9">
         <f>AE257-C257</f>
@@ -22526,20 +22543,20 @@
       <c r="AQ257" s="5"/>
       <c r="AR257" s="41">
         <f>C257/B257*1000</f>
-        <v>22.57395448728321</v>
+        <v>23.313649559963597</v>
       </c>
       <c r="AS257" s="41">
         <f>D257/B257*1000</f>
-        <v>15.666142010267576</v>
+        <v>16.179484413763348</v>
       </c>
       <c r="AT257" s="42"/>
       <c r="AU257" s="41">
         <f>AR257-K257</f>
-        <v>7.3954487283209858E-2</v>
+        <v>0.81364955996359711</v>
       </c>
       <c r="AV257" s="41">
         <f>AS257-L257</f>
-        <v>-0.23385798973242444</v>
+        <v>0.27948441376334721</v>
       </c>
       <c r="AW257" s="5"/>
     </row>
@@ -22637,8 +22654,8 @@
       <c r="A260" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B260" s="7">
-        <v>1143584</v>
+      <c r="B260" s="50">
+        <v>1139062</v>
       </c>
       <c r="C260" s="7">
         <v>7525</v>
@@ -22738,7 +22755,7 @@
       <c r="AM260" s="2"/>
       <c r="AN260" s="9">
         <f>AD260-B260</f>
-        <v>-4522</v>
+        <v>0</v>
       </c>
       <c r="AO260" s="9">
         <f>AE260-C260</f>
@@ -22751,11 +22768,11 @@
       <c r="AQ260" s="5"/>
       <c r="AR260" s="41">
         <f>C260/B260*1000</f>
-        <v>6.5801899991605337</v>
+        <v>6.6063129136078631</v>
       </c>
       <c r="AS260" s="41">
         <f>D260/B260*1000</f>
-        <v>3.7898396619749839</v>
+        <v>3.8048850721031866</v>
       </c>
       <c r="AT260" s="42"/>
       <c r="AU260" s="41"/>
@@ -23683,7 +23700,7 @@
       <c r="AC273"/>
       <c r="AD273" s="14">
         <f>SUM(AD193,AD222,AD248,AD272)</f>
-        <v>114902483</v>
+        <v>114927483</v>
       </c>
       <c r="AE273" s="14">
         <f t="shared" ref="AE273:AL273" si="127">SUM(AE193,AE222,AE248,AE272)</f>
@@ -23720,7 +23737,7 @@
       <c r="AM273" s="2"/>
       <c r="AN273" s="14">
         <f t="shared" si="125"/>
-        <v>-1750127</v>
+        <v>-1725127</v>
       </c>
       <c r="AO273" s="14">
         <f t="shared" si="125"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1890.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5325D9-8F79-4BC4-88FD-6FFC50C8FFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EA66B6-1DC7-4E7C-ADF6-F7366A27ECD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="319">
   <si>
     <t>губ</t>
   </si>
@@ -985,6 +985,12 @@
   </si>
   <si>
     <t>Причина расхождения неясна, но см. 1890-notes.html</t>
+  </si>
+  <si>
+    <t>Для Петербургской губернии в 1891 году нет сведений о Павловске, Гатчине, Царском Селе, Петергофе и Кронштадте.</t>
+  </si>
+  <si>
+    <t>Число смертей и рождений по Карсской обл. относятся к одному только Карсскому округу с населением 83209 чел.</t>
   </si>
 </sst>
 </file>
@@ -1222,10 +1228,6 @@
     <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1235,6 +1237,10 @@
     <xf numFmtId="3" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1401,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12DA313-D41C-46B5-B326-1C471A56B478}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -1447,6 +1453,16 @@
     <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="44" t="s">
         <v>315</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -1535,22 +1551,22 @@
         <v>287</v>
       </c>
       <c r="M1" s="17"/>
-      <c r="N1" s="47" t="s">
+      <c r="N1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
+      <c r="AA1" s="51"/>
       <c r="AB1" s="35"/>
       <c r="AC1" s="37"/>
       <c r="AD1" s="16" t="s">
@@ -2482,7 +2498,7 @@
       <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="50">
+      <c r="B15" s="48">
         <v>1364473</v>
       </c>
       <c r="C15" s="7">
@@ -3995,7 +4011,7 @@
       <c r="R33" s="7">
         <v>124797</v>
       </c>
-      <c r="S33" s="50">
+      <c r="S33" s="48">
         <v>84984</v>
       </c>
       <c r="T33" s="7">
@@ -11296,7 +11312,7 @@
       <c r="A121" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B121" s="50">
+      <c r="B121" s="48">
         <v>1276110</v>
       </c>
       <c r="C121" s="7">
@@ -13802,7 +13818,7 @@
       <c r="T150" s="7">
         <v>47191</v>
       </c>
-      <c r="U150" s="50">
+      <c r="U150" s="48">
         <v>93645</v>
       </c>
       <c r="V150" s="7"/>
@@ -14022,7 +14038,7 @@
       <c r="P153" s="7">
         <v>292791</v>
       </c>
-      <c r="Q153" s="50">
+      <c r="Q153" s="48">
         <v>199683</v>
       </c>
       <c r="R153" s="7">
@@ -14949,7 +14965,7 @@
       <c r="A165" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B165" s="50">
+      <c r="B165" s="48">
         <v>2871526</v>
       </c>
       <c r="C165" s="7">
@@ -15717,7 +15733,7 @@
       <c r="A174" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B174" s="50">
+      <c r="B174" s="48">
         <v>2051093</v>
       </c>
       <c r="C174" s="7">
@@ -16453,7 +16469,7 @@
       <c r="Q183" s="7">
         <v>133428</v>
       </c>
-      <c r="R183" s="50">
+      <c r="R183" s="48">
         <v>130182</v>
       </c>
       <c r="S183" s="7">
@@ -16483,7 +16499,7 @@
       <c r="AA183" s="7">
         <v>166979</v>
       </c>
-      <c r="AB183" s="49">
+      <c r="AB183" s="47">
         <v>178770</v>
       </c>
       <c r="AC183" s="18"/>
@@ -17428,7 +17444,7 @@
       <c r="A194" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B194" s="50">
+      <c r="B194" s="48">
         <v>735626</v>
       </c>
       <c r="C194" s="7">
@@ -17898,7 +17914,7 @@
       <c r="A200" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B200" s="50">
+      <c r="B200" s="48">
         <v>767126</v>
       </c>
       <c r="C200" s="7">
@@ -19863,7 +19879,7 @@
       <c r="A224" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="B224" s="51">
+      <c r="B224" s="49">
         <v>460679</v>
       </c>
       <c r="C224" s="20">
@@ -22210,7 +22226,7 @@
       <c r="A254" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B254" s="50">
+      <c r="B254" s="48">
         <v>574219</v>
       </c>
       <c r="C254" s="7">
@@ -22429,7 +22445,7 @@
       <c r="A257" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B257" s="50">
+      <c r="B257" s="48">
         <v>658241</v>
       </c>
       <c r="C257" s="7">
@@ -22654,7 +22670,7 @@
       <c r="A260" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B260" s="50">
+      <c r="B260" s="48">
         <v>1139062</v>
       </c>
       <c r="C260" s="7">
